--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -115,11 +115,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,74 +641,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>81.09999999999999</v>
+        <v>76.59</v>
       </c>
       <c r="C2" t="n">
-        <v>81.58</v>
+        <v>80.03</v>
       </c>
       <c r="D2" t="n">
-        <v>75.52</v>
+        <v>74.59</v>
       </c>
       <c r="E2" t="n">
-        <v>76.05</v>
+        <v>76.79000000000001</v>
       </c>
       <c r="F2" t="n">
-        <v>-4.7</v>
+        <v>0.74</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0582</v>
+        <v>0.0097</v>
       </c>
       <c r="H2" t="n">
-        <v>6.06</v>
+        <v>5.44</v>
       </c>
       <c r="I2" t="n">
-        <v>76.98</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>77.88</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>79.39</v>
+        <v>73.02</v>
       </c>
       <c r="L2" t="n">
-        <v>80.90000000000001</v>
+        <v>77.3</v>
       </c>
       <c r="M2" t="n">
-        <v>82.11</v>
+        <v>79.08</v>
       </c>
       <c r="N2" t="n">
-        <v>83.31999999999999</v>
+        <v>80.86</v>
       </c>
       <c r="O2" t="n">
-        <v>85.14</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
+        <v>87.64</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -717,58 +713,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>76.59</v>
+        <v>75.53</v>
       </c>
       <c r="C3" t="n">
-        <v>80.03</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>74.59</v>
+        <v>73.58</v>
       </c>
       <c r="E3" t="n">
-        <v>76.79000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>0.74</v>
+        <v>-0.19</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0097</v>
+        <v>-0.0025</v>
       </c>
       <c r="H3" t="n">
-        <v>5.44</v>
+        <v>3.41</v>
       </c>
       <c r="I3" t="n">
-        <v>69.45999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>68.73999999999999</v>
+        <v>71.09</v>
       </c>
       <c r="K3" t="n">
-        <v>73.02</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>77.3</v>
+        <v>77.05</v>
       </c>
       <c r="M3" t="n">
-        <v>79.08</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>80.86</v>
+        <v>81.97</v>
       </c>
       <c r="O3" t="n">
-        <v>87.64</v>
+        <v>85.47</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -776,18 +776,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -797,62 +797,62 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>75.53</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>76.98999999999999</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>73.58</v>
+        <v>74.45</v>
       </c>
       <c r="E4" t="n">
-        <v>76.59999999999999</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.19</v>
+        <v>-1.78</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0232</v>
       </c>
       <c r="H4" t="n">
-        <v>3.41</v>
+        <v>4.51</v>
       </c>
       <c r="I4" t="n">
-        <v>69.15000000000001</v>
+        <v>70.17</v>
       </c>
       <c r="J4" t="n">
-        <v>71.09</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>74.06999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>77.05</v>
+        <v>75.94</v>
       </c>
       <c r="M4" t="n">
-        <v>79.51000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="N4" t="n">
-        <v>81.97</v>
+        <v>80.67</v>
       </c>
       <c r="O4" t="n">
-        <v>85.47</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -862,17 +862,19 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -881,58 +883,62 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>78.93000000000001</v>
+        <v>74.14</v>
       </c>
       <c r="C5" t="n">
-        <v>78.95999999999999</v>
+        <v>74.45</v>
       </c>
       <c r="D5" t="n">
-        <v>74.45</v>
+        <v>72.48</v>
       </c>
       <c r="E5" t="n">
-        <v>74.81999999999999</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.78</v>
+        <v>-1.61</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0232</v>
+        <v>-0.0215</v>
       </c>
       <c r="H5" t="n">
-        <v>4.51</v>
+        <v>1.97</v>
       </c>
       <c r="I5" t="n">
-        <v>70.17</v>
+        <v>69.94</v>
       </c>
       <c r="J5" t="n">
-        <v>73.84999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="K5" t="n">
-        <v>74.90000000000001</v>
+        <v>72.56</v>
       </c>
       <c r="L5" t="n">
-        <v>75.94</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>78.3</v>
+        <v>77.08</v>
       </c>
       <c r="N5" t="n">
-        <v>80.67</v>
+        <v>78.39</v>
       </c>
       <c r="O5" t="n">
-        <v>80.40000000000001</v>
+        <v>83.47</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -950,10 +956,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -963,72 +967,76 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74.14</v>
+        <v>73.13</v>
       </c>
       <c r="C6" t="n">
-        <v>74.45</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>72.48</v>
+        <v>69.63</v>
       </c>
       <c r="E6" t="n">
-        <v>73.20999999999999</v>
+        <v>70.34</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.61</v>
+        <v>-2.87</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0215</v>
+        <v>-0.0392</v>
       </c>
       <c r="H6" t="n">
-        <v>1.97</v>
+        <v>3.55</v>
       </c>
       <c r="I6" t="n">
-        <v>69.94</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>69.37</v>
+        <v>71.11</v>
       </c>
       <c r="K6" t="n">
-        <v>72.56</v>
+        <v>72.23</v>
       </c>
       <c r="L6" t="n">
-        <v>75.76000000000001</v>
+        <v>73.34</v>
       </c>
       <c r="M6" t="n">
-        <v>77.08</v>
+        <v>74.19</v>
       </c>
       <c r="N6" t="n">
-        <v>78.39</v>
+        <v>75.05</v>
       </c>
       <c r="O6" t="n">
-        <v>83.47</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
+        <v>76.42</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
@@ -1045,7 +1053,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1055,398 +1063,398 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73.13</v>
+        <v>69.95</v>
       </c>
       <c r="C7" t="n">
-        <v>73.18000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="D7" t="n">
-        <v>69.63</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>70.34</v>
+        <v>71.92</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.87</v>
+        <v>1.58</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0392</v>
+        <v>0.0225</v>
       </c>
       <c r="H7" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I7" t="n">
-        <v>70.51000000000001</v>
+        <v>66.08</v>
       </c>
       <c r="J7" t="n">
-        <v>71.11</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>72.23</v>
+        <v>68.56</v>
       </c>
       <c r="L7" t="n">
-        <v>73.34</v>
+        <v>70.87</v>
       </c>
       <c r="M7" t="n">
-        <v>74.19</v>
+        <v>72.11</v>
       </c>
       <c r="N7" t="n">
-        <v>75.05</v>
+        <v>73.36</v>
       </c>
       <c r="O7" t="n">
-        <v>76.42</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>76.73</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69.95</v>
+        <v>71.44</v>
       </c>
       <c r="C8" t="n">
-        <v>72.5</v>
+        <v>71.86</v>
       </c>
       <c r="D8" t="n">
-        <v>68.90000000000001</v>
+        <v>68.56</v>
       </c>
       <c r="E8" t="n">
-        <v>71.92</v>
+        <v>69.23</v>
       </c>
       <c r="F8" t="n">
-        <v>1.58</v>
+        <v>-2.69</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0225</v>
+        <v>-0.0374</v>
       </c>
       <c r="H8" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="I8" t="n">
-        <v>66.08</v>
+        <v>65.3</v>
       </c>
       <c r="J8" t="n">
-        <v>66.26000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>68.56</v>
+        <v>70.12</v>
       </c>
       <c r="L8" t="n">
-        <v>70.87</v>
+        <v>71.31</v>
       </c>
       <c r="M8" t="n">
-        <v>72.11</v>
+        <v>73.72</v>
       </c>
       <c r="N8" t="n">
-        <v>73.36</v>
+        <v>76.13</v>
       </c>
       <c r="O8" t="n">
-        <v>76.73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71.44</v>
+        <v>70.5</v>
       </c>
       <c r="C9" t="n">
-        <v>71.86</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>68.56</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>69.23</v>
+        <v>70.75</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.69</v>
+        <v>1.52</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0374</v>
+        <v>0.022</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="I9" t="n">
-        <v>65.3</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>68.93000000000001</v>
+        <v>65.44</v>
       </c>
       <c r="K9" t="n">
-        <v>70.12</v>
+        <v>67.58</v>
       </c>
       <c r="L9" t="n">
-        <v>71.31</v>
+        <v>69.72</v>
       </c>
       <c r="M9" t="n">
-        <v>73.72</v>
+        <v>70.88</v>
       </c>
       <c r="N9" t="n">
-        <v>76.13</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>76.09999999999999</v>
+        <v>75.16</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70.5</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>71.15000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>69.31999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="E10" t="n">
-        <v>70.75</v>
+        <v>69.5</v>
       </c>
       <c r="F10" t="n">
-        <v>1.52</v>
+        <v>-1.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.022</v>
+        <v>-0.0177</v>
       </c>
       <c r="H10" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="I10" t="n">
-        <v>65.26000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>65.44</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>67.58</v>
+        <v>69.83</v>
       </c>
       <c r="L10" t="n">
-        <v>69.72</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>70.88</v>
+        <v>71.67</v>
       </c>
       <c r="N10" t="n">
-        <v>72.04000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="O10" t="n">
-        <v>75.16</v>
+        <v>72.98</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+      <c r="Q10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>70.43000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="C11" t="n">
-        <v>71.59999999999999</v>
+        <v>70.19</v>
       </c>
       <c r="D11" t="n">
-        <v>69.22</v>
+        <v>67.92</v>
       </c>
       <c r="E11" t="n">
-        <v>69.5</v>
+        <v>68.58</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0132</v>
       </c>
       <c r="H11" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="I11" t="n">
-        <v>67.48999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="J11" t="n">
-        <v>69.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="K11" t="n">
-        <v>69.83</v>
+        <v>68.31</v>
       </c>
       <c r="L11" t="n">
-        <v>70.48999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="M11" t="n">
-        <v>71.67</v>
+        <v>70.69</v>
       </c>
       <c r="N11" t="n">
-        <v>72.84</v>
+        <v>71.42</v>
       </c>
       <c r="O11" t="n">
-        <v>72.98</v>
+        <v>73.98</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1461,64 +1469,60 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>69.98</v>
+        <v>68.03</v>
       </c>
       <c r="C12" t="n">
-        <v>70.19</v>
+        <v>68.8</v>
       </c>
       <c r="D12" t="n">
-        <v>67.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>68.58</v>
+        <v>68.69</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.0016</v>
       </c>
       <c r="H12" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="I12" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>66.67</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>68.31</v>
+        <v>67.44</v>
       </c>
       <c r="L12" t="n">
-        <v>69.95</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>70.69</v>
+        <v>69.72</v>
       </c>
       <c r="N12" t="n">
-        <v>71.42</v>
+        <v>70.61</v>
       </c>
       <c r="O12" t="n">
-        <v>73.98</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1528,12 +1532,12 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1545,60 +1549,64 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F13" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H13" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I13" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J13" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L13" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M13" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O13" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1606,14 +1614,12 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1625,64 +1631,64 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C14" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E14" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H14" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I14" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L14" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M14" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N14" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,78 +1699,80 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+      <c r="S14" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C15" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D15" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E15" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F15" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H15" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I15" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L15" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M15" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N15" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1775,7 +1783,7 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1787,15 +1795,13 @@
       </c>
       <c r="U15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1805,50 +1811,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C16" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D16" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E16" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F16" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H16" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I16" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J16" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M16" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1856,81 +1862,83 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C17" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D17" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E17" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I17" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K17" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L17" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N17" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O17" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1957,7 +1965,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1971,50 +1979,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C18" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D18" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E18" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I18" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J18" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L18" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M18" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N18" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O18" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2022,83 +2030,83 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D19" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E19" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F19" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H19" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I19" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J19" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K19" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M19" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N19" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O19" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2109,27 +2117,23 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2139,50 +2143,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E20" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H20" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I20" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J20" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K20" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L20" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M20" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N20" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O20" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2193,15 +2197,13 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2209,60 +2211,64 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C21" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D21" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E21" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F21" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I21" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J21" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K21" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L21" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M21" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N21" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O21" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,9 +2279,9 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2287,64 +2293,64 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E22" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H22" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I22" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K22" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L22" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M22" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N22" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,78 +2361,80 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="S22" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D23" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E23" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F23" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I23" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J23" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L23" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M23" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N23" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2434,30 +2442,28 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2467,50 +2473,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C24" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D24" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E24" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F24" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H24" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I24" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K24" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L24" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M24" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O24" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2518,12 +2524,10 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2539,7 +2543,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2549,50 +2553,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C25" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D25" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E25" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F25" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H25" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I25" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J25" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K25" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L25" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M25" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N25" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2603,7 +2607,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2619,7 +2623,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2629,50 +2633,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C26" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D26" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F26" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H26" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I26" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J26" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K26" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L26" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N26" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2683,23 +2687,27 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2709,50 +2717,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C27" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D27" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F27" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H27" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I27" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J27" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M27" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N27" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2760,93 +2768,97 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C28" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D28" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E28" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H28" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I28" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J28" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K28" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L28" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M28" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N28" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
@@ -2863,80 +2875,72 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C29" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E29" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H29" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I29" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J29" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K29" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L29" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O29" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2951,7 +2955,7 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2961,50 +2965,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E30" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H30" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I30" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J30" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K30" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L30" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N30" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3012,28 +3016,30 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -3041,50 +3047,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D31" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E31" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F31" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H31" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I31" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J31" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K31" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L31" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N31" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O31" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3095,78 +3101,78 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C32" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D32" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E32" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H32" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I32" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J32" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K32" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M32" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O32" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3174,24 +3180,30 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3205,145 +3217,145 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D33" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F33" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H33" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I33" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J33" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N33" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O33" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
       </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D34" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E34" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F34" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H34" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I34" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J34" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N34" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O34" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q34" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
@@ -3356,8 +3368,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3365,89 +3379,81 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W34" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C35" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D35" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F35" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H35" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I35" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J35" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L35" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N35" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3455,64 +3461,60 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C36" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H36" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I36" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J36" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K36" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M36" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N36" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O36" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3523,74 +3525,82 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+      <c r="S36" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C37" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D37" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E37" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H37" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I37" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J37" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K37" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M37" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O37" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3601,25 +3611,23 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3633,50 +3641,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C38" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D38" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F38" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H38" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I38" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L38" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M38" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N38" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3687,80 +3695,80 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V38" s="8" t="n">
-        <v/>
-      </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D39" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E39" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F39" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H39" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I39" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J39" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K39" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L39" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M39" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N39" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3771,27 +3779,23 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V39" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="U39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3801,50 +3805,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F40" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H40" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I40" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L40" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N40" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O40" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3855,15 +3859,13 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S40" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3871,73 +3873,83 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C41" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D41" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E41" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F41" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H41" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I41" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J41" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K41" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O41" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>86.3</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3949,148 +3961,144 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W41" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C42" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H42" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I42" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J42" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L42" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M42" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N42" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N42" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O42" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C43" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E43" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F43" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H43" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I43" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K43" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M43" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N43" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4101,80 +4109,82 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T43" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C44" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D44" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F44" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H44" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I44" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J44" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L44" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M44" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N44" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O44" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4185,25 +4195,21 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S44" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4217,50 +4223,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C45" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D45" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F45" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H45" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I45" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J45" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K45" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N45" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4271,78 +4277,82 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="S45" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C46" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D46" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F46" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H46" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I46" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J46" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K46" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N46" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4353,7 +4363,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="S46" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4371,64 +4381,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C47" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D47" t="n">
         <v>85.8</v>
       </c>
-      <c r="C47" t="n">
-        <v>89</v>
-      </c>
-      <c r="D47" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E47" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I47" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J47" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K47" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L47" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N47" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O47" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4436,91 +4446,91 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C48" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E48" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H48" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I48" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J48" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K48" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L48" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M48" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N48" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O48" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
@@ -4529,7 +4539,7 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4541,71 +4551,69 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C49" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D49" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E49" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H49" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I49" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L49" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N49" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
@@ -4627,7 +4635,7 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4637,69 +4645,63 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C50" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D50" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E50" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H50" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I50" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J50" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K50" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L50" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M50" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N50" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O50" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>91.45</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4711,7 +4713,7 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4721,50 +4723,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C51" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D51" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H51" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I51" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K51" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L51" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N51" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O51" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4775,13 +4777,15 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="S51" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4789,60 +4793,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C52" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D52" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E52" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H52" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I52" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J52" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K52" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L52" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N52" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4853,15 +4861,13 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S52" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4869,64 +4875,64 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="10" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C53" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E53" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H53" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I53" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J53" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K53" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L53" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N53" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O53" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4937,78 +4943,80 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
+      <c r="S53" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C54" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D54" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E54" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F54" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H54" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I54" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L54" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M54" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5019,7 +5027,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5039,7 +5047,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5049,50 +5057,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C55" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E55" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F55" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I55" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L55" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M55" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N55" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5103,27 +5111,21 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="S55" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5133,50 +5135,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C56" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D56" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F56" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H56" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I56" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K56" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N56" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O56" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5187,13 +5189,15 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5201,7 +5205,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5211,50 +5215,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C57" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D57" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E57" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F57" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H57" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I57" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J57" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K57" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L57" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M57" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N57" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O57" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5262,18 +5266,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5281,60 +5285,64 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C58" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D58" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E58" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F58" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H58" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I58" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J58" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K58" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M58" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O58" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5342,18 +5350,18 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5361,64 +5369,60 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C59" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F59" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H59" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I59" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K59" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M59" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N59" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O59" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5429,23 +5433,25 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5455,50 +5461,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C60" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D60" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E60" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F60" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H60" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I60" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J60" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K60" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L60" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M60" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N60" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5509,7 +5515,7 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="11" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5521,13 +5527,15 @@
       </c>
       <c r="U60" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5537,50 +5545,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C61" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D61" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E61" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F61" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H61" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I61" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J61" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K61" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M61" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N61" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O61" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5591,140 +5599,56 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>104.32</v>
-      </c>
-      <c r="C62" t="n">
-        <v>104.46</v>
-      </c>
-      <c r="D62" t="n">
-        <v>98.48</v>
-      </c>
-      <c r="E62" t="n">
-        <v>100.05</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-2.43</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.0237</v>
-      </c>
-      <c r="H62" t="n">
-        <v>5.98</v>
-      </c>
-      <c r="I62" t="n">
-        <v>86.7</v>
-      </c>
-      <c r="J62" t="n">
-        <v>95.2</v>
-      </c>
-      <c r="K62" t="n">
-        <v>98.15000000000001</v>
-      </c>
-      <c r="L62" t="n">
-        <v>101.09</v>
-      </c>
-      <c r="M62" t="n">
-        <v>106.82</v>
-      </c>
-      <c r="N62" t="n">
-        <v>112.54</v>
-      </c>
-      <c r="O62" t="n">
-        <v>112.71</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
+      <c r="I62" s="13" t="n">
         <v>92.5</v>
       </c>
-      <c r="J63" s="13" t="n">
+      <c r="J62" s="13" t="n">
         <v>93.36</v>
       </c>
-      <c r="K63" s="13" t="n">
+      <c r="K62" s="13" t="n">
         <v>97.06</v>
       </c>
-      <c r="L63" s="13" t="n">
+      <c r="L62" s="13" t="n">
         <v>100.76</v>
       </c>
-      <c r="M63" s="13" t="n">
+      <c r="M62" s="13" t="n">
         <v>103.04</v>
       </c>
-      <c r="N63" s="13" t="n">
+      <c r="N62" s="13" t="n">
         <v>105.32</v>
       </c>
-      <c r="O63" s="13" t="n">
+      <c r="O62" s="13" t="n">
         <v>110.44</v>
       </c>
     </row>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>76.59</v>
+        <v>75.53</v>
       </c>
       <c r="C2" t="n">
-        <v>80.03</v>
+        <v>76.98999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>74.59</v>
+        <v>73.58</v>
       </c>
       <c r="E2" t="n">
-        <v>76.79000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.74</v>
+        <v>-0.19</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0097</v>
+        <v>-0.0025</v>
       </c>
       <c r="H2" t="n">
-        <v>5.44</v>
+        <v>3.41</v>
       </c>
       <c r="I2" t="n">
-        <v>69.45999999999999</v>
+        <v>69.15000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>68.73999999999999</v>
+        <v>71.09</v>
       </c>
       <c r="K2" t="n">
-        <v>73.02</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>77.3</v>
+        <v>77.05</v>
       </c>
       <c r="M2" t="n">
-        <v>79.08</v>
+        <v>79.51000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>80.86</v>
+        <v>81.97</v>
       </c>
       <c r="O2" t="n">
-        <v>87.64</v>
+        <v>85.47</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,18 +692,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -718,57 +718,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>75.53</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>76.98999999999999</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>73.58</v>
+        <v>74.45</v>
       </c>
       <c r="E3" t="n">
-        <v>76.59999999999999</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.19</v>
+        <v>-1.78</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0232</v>
       </c>
       <c r="H3" t="n">
-        <v>3.41</v>
+        <v>4.51</v>
       </c>
       <c r="I3" t="n">
-        <v>69.15000000000001</v>
+        <v>70.17</v>
       </c>
       <c r="J3" t="n">
-        <v>71.09</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>74.06999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>77.05</v>
+        <v>75.94</v>
       </c>
       <c r="M3" t="n">
-        <v>79.51000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="N3" t="n">
-        <v>81.97</v>
+        <v>80.67</v>
       </c>
       <c r="O3" t="n">
-        <v>85.47</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -778,17 +778,19 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -802,57 +804,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>78.93000000000001</v>
+        <v>74.14</v>
       </c>
       <c r="C4" t="n">
-        <v>78.95999999999999</v>
+        <v>74.45</v>
       </c>
       <c r="D4" t="n">
-        <v>74.45</v>
+        <v>72.48</v>
       </c>
       <c r="E4" t="n">
-        <v>74.81999999999999</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.78</v>
+        <v>-1.61</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0232</v>
+        <v>-0.0215</v>
       </c>
       <c r="H4" t="n">
-        <v>4.51</v>
+        <v>1.97</v>
       </c>
       <c r="I4" t="n">
-        <v>70.17</v>
+        <v>69.94</v>
       </c>
       <c r="J4" t="n">
-        <v>73.84999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="K4" t="n">
-        <v>74.90000000000001</v>
+        <v>72.56</v>
       </c>
       <c r="L4" t="n">
-        <v>75.94</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>78.3</v>
+        <v>77.08</v>
       </c>
       <c r="N4" t="n">
-        <v>80.67</v>
+        <v>78.39</v>
       </c>
       <c r="O4" t="n">
-        <v>80.40000000000001</v>
+        <v>83.47</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -870,10 +872,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -888,67 +888,71 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.14</v>
+        <v>73.13</v>
       </c>
       <c r="C5" t="n">
-        <v>74.45</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>72.48</v>
+        <v>69.63</v>
       </c>
       <c r="E5" t="n">
-        <v>73.20999999999999</v>
+        <v>70.34</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.61</v>
+        <v>-2.87</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0215</v>
+        <v>-0.0392</v>
       </c>
       <c r="H5" t="n">
-        <v>1.97</v>
+        <v>3.55</v>
       </c>
       <c r="I5" t="n">
-        <v>69.94</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>69.37</v>
+        <v>71.11</v>
       </c>
       <c r="K5" t="n">
-        <v>72.56</v>
+        <v>72.23</v>
       </c>
       <c r="L5" t="n">
-        <v>75.76000000000001</v>
+        <v>73.34</v>
       </c>
       <c r="M5" t="n">
-        <v>77.08</v>
+        <v>74.19</v>
       </c>
       <c r="N5" t="n">
-        <v>78.39</v>
+        <v>75.05</v>
       </c>
       <c r="O5" t="n">
-        <v>83.47</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
+        <v>76.42</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
@@ -965,88 +969,80 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W5" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73.13</v>
+        <v>69.95</v>
       </c>
       <c r="C6" t="n">
-        <v>73.18000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="D6" t="n">
-        <v>69.63</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>70.34</v>
+        <v>71.92</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.87</v>
+        <v>1.58</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0392</v>
+        <v>0.0225</v>
       </c>
       <c r="H6" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I6" t="n">
-        <v>70.51000000000001</v>
+        <v>66.08</v>
       </c>
       <c r="J6" t="n">
-        <v>71.11</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>72.23</v>
+        <v>68.56</v>
       </c>
       <c r="L6" t="n">
-        <v>73.34</v>
+        <v>70.87</v>
       </c>
       <c r="M6" t="n">
-        <v>74.19</v>
+        <v>72.11</v>
       </c>
       <c r="N6" t="n">
-        <v>75.05</v>
+        <v>73.36</v>
       </c>
       <c r="O6" t="n">
-        <v>76.42</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>76.73</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1058,75 +1054,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.95</v>
+        <v>71.44</v>
       </c>
       <c r="C7" t="n">
-        <v>72.5</v>
+        <v>71.86</v>
       </c>
       <c r="D7" t="n">
-        <v>68.90000000000001</v>
+        <v>68.56</v>
       </c>
       <c r="E7" t="n">
-        <v>71.92</v>
+        <v>69.23</v>
       </c>
       <c r="F7" t="n">
-        <v>1.58</v>
+        <v>-2.69</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0225</v>
+        <v>-0.0374</v>
       </c>
       <c r="H7" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="I7" t="n">
-        <v>66.08</v>
+        <v>65.3</v>
       </c>
       <c r="J7" t="n">
-        <v>66.26000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>68.56</v>
+        <v>70.12</v>
       </c>
       <c r="L7" t="n">
-        <v>70.87</v>
+        <v>71.31</v>
       </c>
       <c r="M7" t="n">
-        <v>72.11</v>
+        <v>73.72</v>
       </c>
       <c r="N7" t="n">
-        <v>73.36</v>
+        <v>76.13</v>
       </c>
       <c r="O7" t="n">
-        <v>76.73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1138,81 +1140,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>71.44</v>
+        <v>70.5</v>
       </c>
       <c r="C8" t="n">
-        <v>71.86</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>68.56</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>69.23</v>
+        <v>70.75</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.69</v>
+        <v>1.52</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0374</v>
+        <v>0.022</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="I8" t="n">
-        <v>65.3</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>68.93000000000001</v>
+        <v>65.44</v>
       </c>
       <c r="K8" t="n">
-        <v>70.12</v>
+        <v>67.58</v>
       </c>
       <c r="L8" t="n">
-        <v>71.31</v>
+        <v>69.72</v>
       </c>
       <c r="M8" t="n">
-        <v>73.72</v>
+        <v>70.88</v>
       </c>
       <c r="N8" t="n">
-        <v>76.13</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>76.09999999999999</v>
+        <v>75.16</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1224,75 +1220,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70.5</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>71.15000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>69.31999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="E9" t="n">
-        <v>70.75</v>
+        <v>69.5</v>
       </c>
       <c r="F9" t="n">
-        <v>1.52</v>
+        <v>-1.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.022</v>
+        <v>-0.0177</v>
       </c>
       <c r="H9" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="I9" t="n">
-        <v>65.26000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>65.44</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>67.58</v>
+        <v>69.83</v>
       </c>
       <c r="L9" t="n">
-        <v>69.72</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>70.88</v>
+        <v>71.67</v>
       </c>
       <c r="N9" t="n">
-        <v>72.04000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="O9" t="n">
-        <v>75.16</v>
+        <v>72.98</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="Q9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1306,71 +1308,69 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>70.43000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="C10" t="n">
-        <v>71.59999999999999</v>
+        <v>70.19</v>
       </c>
       <c r="D10" t="n">
-        <v>69.22</v>
+        <v>67.92</v>
       </c>
       <c r="E10" t="n">
-        <v>69.5</v>
+        <v>68.58</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0132</v>
       </c>
       <c r="H10" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="I10" t="n">
-        <v>67.48999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="J10" t="n">
-        <v>69.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="K10" t="n">
-        <v>69.83</v>
+        <v>68.31</v>
       </c>
       <c r="L10" t="n">
-        <v>70.48999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="M10" t="n">
-        <v>71.67</v>
+        <v>70.69</v>
       </c>
       <c r="N10" t="n">
-        <v>72.84</v>
+        <v>71.42</v>
       </c>
       <c r="O10" t="n">
-        <v>72.98</v>
+        <v>73.98</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1390,59 +1390,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>69.98</v>
+        <v>68.03</v>
       </c>
       <c r="C11" t="n">
-        <v>70.19</v>
+        <v>68.8</v>
       </c>
       <c r="D11" t="n">
-        <v>67.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>68.58</v>
+        <v>68.69</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.0016</v>
       </c>
       <c r="H11" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="I11" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>66.67</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>68.31</v>
+        <v>67.44</v>
       </c>
       <c r="L11" t="n">
-        <v>69.95</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>70.69</v>
+        <v>69.72</v>
       </c>
       <c r="N11" t="n">
-        <v>71.42</v>
+        <v>70.61</v>
       </c>
       <c r="O11" t="n">
-        <v>73.98</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1452,12 +1448,12 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1474,55 +1470,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F12" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H12" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I12" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J12" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L12" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M12" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O12" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1530,14 +1530,12 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1556,57 +1554,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C13" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E13" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H13" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I13" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L13" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M13" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N13" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1619,76 +1617,78 @@
       </c>
       <c r="S13" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W13" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C14" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D14" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E14" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F14" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H14" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I14" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L14" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N14" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1711,13 +1711,11 @@
       </c>
       <c r="U14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1729,50 +1727,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C15" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D15" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E15" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F15" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H15" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I15" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J15" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M15" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1780,24 +1778,22 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1806,55 +1802,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C16" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D16" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E16" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I16" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K16" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L16" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N16" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O16" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1895,50 +1895,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C17" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D17" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E17" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I17" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J17" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L17" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M17" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N17" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O17" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1946,83 +1946,83 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D18" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E18" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F18" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H18" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I18" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J18" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K18" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M18" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N18" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O18" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2040,18 +2040,14 @@
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2063,50 +2059,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E19" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H19" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I19" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J19" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K19" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L19" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M19" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N19" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O19" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2119,13 +2115,11 @@
       </c>
       <c r="S19" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2138,55 +2132,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C20" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D20" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E20" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F20" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I20" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J20" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K20" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L20" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M20" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N20" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O20" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2197,9 +2195,9 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2218,57 +2216,57 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E21" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H21" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I21" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K21" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L21" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M21" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N21" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2279,78 +2277,80 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
+      <c r="S21" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D22" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E22" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F22" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I22" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L22" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M22" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N22" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,8 +2358,10 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S22" s="11" t="inlineStr">
         <is>
@@ -2368,18 +2370,14 @@
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2391,50 +2389,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C23" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D23" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E23" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F23" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H23" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I23" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K23" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L23" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M23" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O23" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2442,10 +2440,8 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="11" t="inlineStr">
         <is>
@@ -2473,50 +2469,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C24" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D24" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E24" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F24" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H24" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I24" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J24" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K24" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L24" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M24" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N24" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2553,50 +2549,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C25" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D25" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F25" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H25" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I25" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J25" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K25" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L25" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N25" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2614,14 +2610,18 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2633,50 +2633,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C26" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D26" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F26" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H26" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I26" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J26" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M26" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N26" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2684,93 +2684,97 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
+      </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C27" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D27" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E27" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H27" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I27" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J27" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K27" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L27" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M27" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N27" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
@@ -2787,78 +2791,70 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C28" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E28" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H28" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I28" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J28" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K28" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L28" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O28" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S28" s="7" t="inlineStr">
@@ -2885,50 +2881,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E29" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H29" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I29" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J29" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K29" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L29" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N29" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2936,28 +2932,30 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -2965,50 +2963,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D30" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E30" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F30" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H30" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I30" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J30" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K30" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L30" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N30" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O30" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3019,20 +3017,16 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3042,55 +3036,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C31" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D31" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E31" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H31" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I31" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J31" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K31" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M31" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O31" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3098,19 +3096,25 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3129,76 +3133,74 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D32" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F32" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H32" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I32" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J32" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N32" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O32" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
       </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S32" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3210,64 +3212,66 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D33" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E33" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H33" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I33" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J33" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N33" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O33" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q33" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
@@ -3280,8 +3284,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3289,89 +3295,81 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W33" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C34" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D34" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F34" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H34" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I34" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J34" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L34" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N34" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3384,59 +3382,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C35" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H35" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I35" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J35" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K35" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M35" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N35" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O35" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3447,16 +3441,20 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+      <c r="S35" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3466,55 +3464,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C36" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D36" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E36" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H36" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I36" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J36" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K36" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M36" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O36" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3532,13 +3534,11 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3557,50 +3557,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C37" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D37" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F37" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H37" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I37" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L37" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M37" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N37" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3618,73 +3618,73 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W37" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D38" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E38" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F38" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H38" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I38" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J38" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K38" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L38" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M38" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N38" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3702,18 +3702,14 @@
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V38" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V38" s="8" t="n">
+        <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
@@ -3725,50 +3721,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F39" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H39" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I39" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L39" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N39" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O39" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3781,13 +3777,11 @@
       </c>
       <c r="S39" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3800,68 +3794,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C40" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D40" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E40" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F40" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H40" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I40" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J40" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K40" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O40" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>86.3</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3873,88 +3877,80 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W40" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C41" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H41" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I41" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J41" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L41" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M41" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N41" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N41" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O41" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3966,55 +3962,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C42" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E42" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F42" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H42" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I42" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K42" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M42" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N42" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4032,12 +4032,14 @@
       </c>
       <c r="T42" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
@@ -4048,57 +4050,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C43" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D43" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F43" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H43" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I43" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J43" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L43" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M43" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N43" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O43" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4111,18 +4113,14 @@
       </c>
       <c r="S43" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4141,50 +4139,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C44" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D44" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F44" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H44" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I44" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J44" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K44" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N44" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4197,14 +4195,18 @@
       </c>
       <c r="S44" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4216,57 +4218,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C45" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D45" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F45" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H45" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I45" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J45" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K45" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N45" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4302,57 +4304,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C46" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D46" t="n">
         <v>85.8</v>
       </c>
-      <c r="C46" t="n">
-        <v>89</v>
-      </c>
-      <c r="D46" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E46" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F46" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I46" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J46" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K46" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L46" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N46" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O46" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4360,24 +4362,22 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
@@ -4388,63 +4388,65 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C47" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E47" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H47" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I47" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J47" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K47" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L47" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M47" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N47" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O47" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
@@ -4453,7 +4455,7 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4470,66 +4472,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C48" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D48" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E48" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H48" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I48" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L48" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N48" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
@@ -4561,69 +4561,63 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C49" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D49" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E49" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H49" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I49" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J49" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K49" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L49" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M49" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N49" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O49" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>91.45</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4645,50 +4639,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C50" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D50" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H50" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I50" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K50" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L50" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N50" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O50" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4699,13 +4693,15 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="S50" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4718,55 +4714,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C51" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D51" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E51" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H51" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I51" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J51" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K51" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L51" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N51" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4779,13 +4779,11 @@
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4800,57 +4798,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C52" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E52" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H52" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I52" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J52" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K52" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L52" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N52" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O52" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4863,76 +4861,78 @@
       </c>
       <c r="S52" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W52" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C53" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D53" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E53" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F53" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H53" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I53" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L53" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M53" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4973,50 +4973,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C54" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E54" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F54" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H54" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I54" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L54" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M54" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N54" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5029,23 +5029,17 @@
       </c>
       <c r="S54" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
@@ -5057,50 +5051,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C55" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D55" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F55" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H55" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I55" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K55" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N55" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O55" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5116,8 +5110,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5135,50 +5131,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C56" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D56" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E56" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F56" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H56" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I56" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J56" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K56" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L56" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M56" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N56" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O56" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5186,18 +5182,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S56" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5210,55 +5206,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C57" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D57" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E57" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F57" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H57" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I57" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J57" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K57" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M57" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O57" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5266,18 +5266,18 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R57" s="6" t="n">
+        <v/>
       </c>
       <c r="S57" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5290,59 +5290,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C58" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D58" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F58" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H58" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I58" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K58" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M58" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O58" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5360,11 +5356,13 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5379,50 +5377,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C59" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D59" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E59" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F59" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H59" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I59" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J59" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K59" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L59" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M59" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N59" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O59" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5445,11 +5443,13 @@
       </c>
       <c r="U59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
@@ -5461,50 +5461,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C60" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D60" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E60" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F60" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H60" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I60" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J60" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K60" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M60" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N60" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O60" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5515,80 +5515,78 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C61" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D61" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E61" t="n">
-        <v>100.05</v>
+        <v>101.89</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.43</v>
+        <v>1.84</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0184</v>
       </c>
       <c r="H61" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I61" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J61" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K61" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L61" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M61" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N61" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O61" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5599,13 +5597,15 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="S61" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5618,11 +5618,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5631,25 +5627,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>93.36</v>
+        <v>97.05</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>97.06</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>100.76</v>
+        <v>102.31</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>103.04</v>
+        <v>104.1</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>105.32</v>
+        <v>105.88</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5547,25 +5547,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C61" t="n">
-        <v>104.95</v>
+        <v>102.85</v>
       </c>
       <c r="D61" t="n">
-        <v>100.53</v>
+        <v>101.83</v>
       </c>
       <c r="E61" t="n">
-        <v>101.89</v>
+        <v>102.48</v>
       </c>
       <c r="F61" t="n">
-        <v>1.84</v>
+        <v>2.43</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0184</v>
+        <v>0.0243</v>
       </c>
       <c r="H61" t="n">
-        <v>4.42</v>
+        <v>1.02</v>
       </c>
       <c r="I61" t="n">
         <v>92.5</v>
@@ -5599,12 +5599,12 @@
       </c>
       <c r="S61" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="U61" s="8" t="n">
@@ -5618,7 +5618,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5627,25 +5631,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>96.11</v>
+        <v>100.81</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>97.05</v>
+        <v>101.53</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>99.68000000000001</v>
+        <v>101.97</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>102.31</v>
+        <v>102.41</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>104.1</v>
+        <v>102.99</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>105.88</v>
+        <v>103.57</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>109.37</v>
+        <v>103.87</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5550,22 +5550,22 @@
         <v>102.01</v>
       </c>
       <c r="C61" t="n">
-        <v>102.85</v>
+        <v>102.98</v>
       </c>
       <c r="D61" t="n">
         <v>101.83</v>
       </c>
       <c r="E61" t="n">
-        <v>102.48</v>
+        <v>102.73</v>
       </c>
       <c r="F61" t="n">
-        <v>2.43</v>
+        <v>2.68</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0243</v>
+        <v>0.0268</v>
       </c>
       <c r="H61" t="n">
-        <v>1.02</v>
+        <v>1.15</v>
       </c>
       <c r="I61" t="n">
         <v>92.5</v>
@@ -5631,25 +5631,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>100.81</v>
+        <v>100.68</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>101.53</v>
+        <v>101.74</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>101.97</v>
+        <v>102.16</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>102.41</v>
+        <v>102.57</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>102.99</v>
+        <v>103.31</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>103.57</v>
+        <v>104.04</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>103.87</v>
+        <v>104.13</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5550,22 +5550,22 @@
         <v>102.01</v>
       </c>
       <c r="C61" t="n">
-        <v>102.98</v>
+        <v>103.16</v>
       </c>
       <c r="D61" t="n">
         <v>101.83</v>
       </c>
       <c r="E61" t="n">
-        <v>102.73</v>
+        <v>102.9</v>
       </c>
       <c r="F61" t="n">
-        <v>2.68</v>
+        <v>2.85</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0268</v>
+        <v>0.0285</v>
       </c>
       <c r="H61" t="n">
-        <v>1.15</v>
+        <v>1.33</v>
       </c>
       <c r="I61" t="n">
         <v>92.5</v>
@@ -5631,25 +5631,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>100.68</v>
+        <v>100.5</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>101.74</v>
+        <v>101.77</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>102.16</v>
+        <v>102.24</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>102.57</v>
+        <v>102.7</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>103.31</v>
+        <v>103.57</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>104.04</v>
+        <v>104.43</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>104.13</v>
+        <v>104.49</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5547,25 +5547,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>102.01</v>
+        <v>102.25</v>
       </c>
       <c r="C61" t="n">
-        <v>103.16</v>
+        <v>104.95</v>
       </c>
       <c r="D61" t="n">
-        <v>101.83</v>
+        <v>100.53</v>
       </c>
       <c r="E61" t="n">
-        <v>102.9</v>
+        <v>101.39</v>
       </c>
       <c r="F61" t="n">
-        <v>2.85</v>
+        <v>1.34</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0285</v>
+        <v>0.0134</v>
       </c>
       <c r="H61" t="n">
-        <v>1.33</v>
+        <v>4.42</v>
       </c>
       <c r="I61" t="n">
         <v>92.5</v>
@@ -5599,56 +5599,136 @@
       </c>
       <c r="S61" s="11" t="inlineStr">
         <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>102.01</v>
+      </c>
+      <c r="C62" t="n">
+        <v>103.16</v>
+      </c>
+      <c r="D62" t="n">
+        <v>101.83</v>
+      </c>
+      <c r="E62" t="n">
+        <v>102.98</v>
+      </c>
+      <c r="F62" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0157</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="I62" t="n">
+        <v>96.11</v>
+      </c>
+      <c r="J62" t="n">
+        <v>96.3</v>
+      </c>
+      <c r="K62" t="n">
+        <v>99.18000000000001</v>
+      </c>
+      <c r="L62" t="n">
+        <v>102.06</v>
+      </c>
+      <c r="M62" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="N62" t="n">
+        <v>105.13</v>
+      </c>
+      <c r="O62" t="n">
+        <v>109.37</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="11" t="inlineStr">
+        <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
+      <c r="X62" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
+      <c r="I63" s="13" t="n">
         <v>100.5</v>
       </c>
-      <c r="J62" s="13" t="n">
-        <v>101.77</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>102.24</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>102.7</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>103.57</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>104.43</v>
-      </c>
-      <c r="O62" s="13" t="n">
+      <c r="J63" s="13" t="n">
+        <v>101.89</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>102.32</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>102.74</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>103.65</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="O63" s="13" t="n">
         <v>104.49</v>
       </c>
     </row>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>75.53</v>
+        <v>78.93000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>76.98999999999999</v>
+        <v>78.95999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>73.58</v>
+        <v>74.45</v>
       </c>
       <c r="E2" t="n">
-        <v>76.59999999999999</v>
+        <v>74.81999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.19</v>
+        <v>-1.78</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0232</v>
       </c>
       <c r="H2" t="n">
-        <v>3.41</v>
+        <v>4.51</v>
       </c>
       <c r="I2" t="n">
-        <v>69.15000000000001</v>
+        <v>70.17</v>
       </c>
       <c r="J2" t="n">
-        <v>71.09</v>
+        <v>73.84999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>74.06999999999999</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>77.05</v>
+        <v>75.94</v>
       </c>
       <c r="M2" t="n">
-        <v>79.51000000000001</v>
+        <v>78.3</v>
       </c>
       <c r="N2" t="n">
-        <v>81.97</v>
+        <v>80.67</v>
       </c>
       <c r="O2" t="n">
-        <v>85.47</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -694,17 +694,19 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -718,57 +720,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78.93000000000001</v>
+        <v>74.14</v>
       </c>
       <c r="C3" t="n">
-        <v>78.95999999999999</v>
+        <v>74.45</v>
       </c>
       <c r="D3" t="n">
-        <v>74.45</v>
+        <v>72.48</v>
       </c>
       <c r="E3" t="n">
-        <v>74.81999999999999</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.78</v>
+        <v>-1.61</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0232</v>
+        <v>-0.0215</v>
       </c>
       <c r="H3" t="n">
-        <v>4.51</v>
+        <v>1.97</v>
       </c>
       <c r="I3" t="n">
-        <v>70.17</v>
+        <v>69.94</v>
       </c>
       <c r="J3" t="n">
-        <v>73.84999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="K3" t="n">
-        <v>74.90000000000001</v>
+        <v>72.56</v>
       </c>
       <c r="L3" t="n">
-        <v>75.94</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>78.3</v>
+        <v>77.08</v>
       </c>
       <c r="N3" t="n">
-        <v>80.67</v>
+        <v>78.39</v>
       </c>
       <c r="O3" t="n">
-        <v>80.40000000000001</v>
+        <v>83.47</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -786,10 +788,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -804,67 +804,71 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74.14</v>
+        <v>73.13</v>
       </c>
       <c r="C4" t="n">
-        <v>74.45</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>72.48</v>
+        <v>69.63</v>
       </c>
       <c r="E4" t="n">
-        <v>73.20999999999999</v>
+        <v>70.34</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.61</v>
+        <v>-2.87</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0215</v>
+        <v>-0.0392</v>
       </c>
       <c r="H4" t="n">
-        <v>1.97</v>
+        <v>3.55</v>
       </c>
       <c r="I4" t="n">
-        <v>69.94</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>69.37</v>
+        <v>71.11</v>
       </c>
       <c r="K4" t="n">
-        <v>72.56</v>
+        <v>72.23</v>
       </c>
       <c r="L4" t="n">
-        <v>75.76000000000001</v>
+        <v>73.34</v>
       </c>
       <c r="M4" t="n">
-        <v>77.08</v>
+        <v>74.19</v>
       </c>
       <c r="N4" t="n">
-        <v>78.39</v>
+        <v>75.05</v>
       </c>
       <c r="O4" t="n">
-        <v>83.47</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
+        <v>76.42</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
@@ -881,88 +885,80 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W4" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.13</v>
+        <v>69.95</v>
       </c>
       <c r="C5" t="n">
-        <v>73.18000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="D5" t="n">
-        <v>69.63</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>70.34</v>
+        <v>71.92</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.87</v>
+        <v>1.58</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0392</v>
+        <v>0.0225</v>
       </c>
       <c r="H5" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I5" t="n">
-        <v>70.51000000000001</v>
+        <v>66.08</v>
       </c>
       <c r="J5" t="n">
-        <v>71.11</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>72.23</v>
+        <v>68.56</v>
       </c>
       <c r="L5" t="n">
-        <v>73.34</v>
+        <v>70.87</v>
       </c>
       <c r="M5" t="n">
-        <v>74.19</v>
+        <v>72.11</v>
       </c>
       <c r="N5" t="n">
-        <v>75.05</v>
+        <v>73.36</v>
       </c>
       <c r="O5" t="n">
-        <v>76.42</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>76.73</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -974,75 +970,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69.95</v>
+        <v>71.44</v>
       </c>
       <c r="C6" t="n">
-        <v>72.5</v>
+        <v>71.86</v>
       </c>
       <c r="D6" t="n">
-        <v>68.90000000000001</v>
+        <v>68.56</v>
       </c>
       <c r="E6" t="n">
-        <v>71.92</v>
+        <v>69.23</v>
       </c>
       <c r="F6" t="n">
-        <v>1.58</v>
+        <v>-2.69</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0225</v>
+        <v>-0.0374</v>
       </c>
       <c r="H6" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="I6" t="n">
-        <v>66.08</v>
+        <v>65.3</v>
       </c>
       <c r="J6" t="n">
-        <v>66.26000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>68.56</v>
+        <v>70.12</v>
       </c>
       <c r="L6" t="n">
-        <v>70.87</v>
+        <v>71.31</v>
       </c>
       <c r="M6" t="n">
-        <v>72.11</v>
+        <v>73.72</v>
       </c>
       <c r="N6" t="n">
-        <v>73.36</v>
+        <v>76.13</v>
       </c>
       <c r="O6" t="n">
-        <v>76.73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1054,81 +1056,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>71.44</v>
+        <v>70.5</v>
       </c>
       <c r="C7" t="n">
-        <v>71.86</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>68.56</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>69.23</v>
+        <v>70.75</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.69</v>
+        <v>1.52</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0374</v>
+        <v>0.022</v>
       </c>
       <c r="H7" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="I7" t="n">
-        <v>65.3</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>68.93000000000001</v>
+        <v>65.44</v>
       </c>
       <c r="K7" t="n">
-        <v>70.12</v>
+        <v>67.58</v>
       </c>
       <c r="L7" t="n">
-        <v>71.31</v>
+        <v>69.72</v>
       </c>
       <c r="M7" t="n">
-        <v>73.72</v>
+        <v>70.88</v>
       </c>
       <c r="N7" t="n">
-        <v>76.13</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>76.09999999999999</v>
+        <v>75.16</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1140,75 +1136,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70.5</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>71.15000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>69.31999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="E8" t="n">
-        <v>70.75</v>
+        <v>69.5</v>
       </c>
       <c r="F8" t="n">
-        <v>1.52</v>
+        <v>-1.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.022</v>
+        <v>-0.0177</v>
       </c>
       <c r="H8" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="I8" t="n">
-        <v>65.26000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>65.44</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>67.58</v>
+        <v>69.83</v>
       </c>
       <c r="L8" t="n">
-        <v>69.72</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>70.88</v>
+        <v>71.67</v>
       </c>
       <c r="N8" t="n">
-        <v>72.04000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="O8" t="n">
-        <v>75.16</v>
+        <v>72.98</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+      <c r="Q8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1222,71 +1224,69 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>70.43000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="C9" t="n">
-        <v>71.59999999999999</v>
+        <v>70.19</v>
       </c>
       <c r="D9" t="n">
-        <v>69.22</v>
+        <v>67.92</v>
       </c>
       <c r="E9" t="n">
-        <v>69.5</v>
+        <v>68.58</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0132</v>
       </c>
       <c r="H9" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="I9" t="n">
-        <v>67.48999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="J9" t="n">
-        <v>69.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="K9" t="n">
-        <v>69.83</v>
+        <v>68.31</v>
       </c>
       <c r="L9" t="n">
-        <v>70.48999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="M9" t="n">
-        <v>71.67</v>
+        <v>70.69</v>
       </c>
       <c r="N9" t="n">
-        <v>72.84</v>
+        <v>71.42</v>
       </c>
       <c r="O9" t="n">
-        <v>72.98</v>
+        <v>73.98</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1306,59 +1306,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>69.98</v>
+        <v>68.03</v>
       </c>
       <c r="C10" t="n">
-        <v>70.19</v>
+        <v>68.8</v>
       </c>
       <c r="D10" t="n">
-        <v>67.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>68.58</v>
+        <v>68.69</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.0016</v>
       </c>
       <c r="H10" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="I10" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>66.67</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>68.31</v>
+        <v>67.44</v>
       </c>
       <c r="L10" t="n">
-        <v>69.95</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>70.69</v>
+        <v>69.72</v>
       </c>
       <c r="N10" t="n">
-        <v>71.42</v>
+        <v>70.61</v>
       </c>
       <c r="O10" t="n">
-        <v>73.98</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1368,12 +1364,12 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1390,55 +1386,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E11" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F11" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H11" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I11" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J11" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L11" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M11" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N11" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O11" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,14 +1446,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1472,57 +1470,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C12" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E12" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H12" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I12" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L12" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M12" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N12" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1535,76 +1533,78 @@
       </c>
       <c r="S12" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W12" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W12" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C13" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D13" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E13" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F13" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H13" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I13" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L13" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N13" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1627,13 +1627,11 @@
       </c>
       <c r="U13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1645,50 +1643,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C14" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D14" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E14" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F14" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H14" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I14" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J14" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M14" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1696,24 +1694,22 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
@@ -1722,55 +1718,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C15" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D15" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E15" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I15" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K15" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L15" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N15" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O15" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1811,50 +1811,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C16" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D16" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E16" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I16" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J16" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L16" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M16" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N16" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O16" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1862,83 +1862,83 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
-      </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D17" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E17" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F17" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H17" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I17" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J17" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K17" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M17" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N17" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O17" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1956,18 +1956,14 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1979,50 +1975,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E18" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H18" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I18" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J18" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K18" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L18" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M18" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N18" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O18" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2035,13 +2031,11 @@
       </c>
       <c r="S18" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2054,55 +2048,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C19" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D19" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E19" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F19" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I19" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J19" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K19" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L19" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M19" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N19" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O19" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2113,9 +2111,9 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2134,57 +2132,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E20" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H20" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I20" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K20" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L20" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M20" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N20" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2195,78 +2193,80 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
+      <c r="S20" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D21" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E21" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F21" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H21" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I21" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J21" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L21" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M21" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N21" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,8 +2274,10 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="11" t="inlineStr">
         <is>
@@ -2284,18 +2286,14 @@
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2307,50 +2305,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C22" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D22" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E22" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F22" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H22" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I22" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K22" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L22" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M22" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O22" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,10 +2356,8 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="11" t="inlineStr">
         <is>
@@ -2389,50 +2385,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C23" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D23" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E23" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F23" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H23" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I23" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J23" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K23" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L23" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M23" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N23" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2469,50 +2465,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C24" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D24" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F24" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H24" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I24" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J24" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K24" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L24" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N24" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2530,14 +2526,18 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -2549,50 +2549,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C25" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D25" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F25" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H25" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I25" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J25" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M25" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N25" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2600,93 +2600,97 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
+      </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C26" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D26" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E26" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H26" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I26" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J26" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K26" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L26" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M26" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N26" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
@@ -2703,78 +2707,70 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W26" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C27" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E27" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H27" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I27" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J27" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K27" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L27" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O27" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
@@ -2801,50 +2797,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E28" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I28" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J28" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K28" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L28" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N28" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2852,28 +2848,30 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2881,50 +2879,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D29" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E29" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F29" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H29" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I29" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J29" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K29" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L29" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N29" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O29" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2935,20 +2933,16 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2958,55 +2952,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C30" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D30" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E30" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H30" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I30" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J30" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K30" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M30" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O30" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3014,19 +3012,25 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3045,76 +3049,74 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D31" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F31" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H31" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I31" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J31" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N31" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O31" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S31" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3126,64 +3128,66 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D32" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E32" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F32" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H32" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I32" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J32" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N32" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O32" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q32" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
@@ -3196,8 +3200,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3205,89 +3211,81 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W32" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C33" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D33" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F33" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H33" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I33" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J33" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L33" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N33" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3300,59 +3298,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C34" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H34" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I34" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J34" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K34" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M34" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N34" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O34" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3363,16 +3357,20 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="S34" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3382,55 +3380,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C35" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D35" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E35" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H35" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I35" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J35" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K35" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M35" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O35" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3448,13 +3450,11 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3473,50 +3473,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C36" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D36" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F36" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H36" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I36" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L36" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M36" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N36" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3534,73 +3534,73 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W36" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W36" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D37" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E37" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F37" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H37" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I37" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J37" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K37" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L37" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M37" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N37" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3618,18 +3618,14 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V37" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V37" s="8" t="n">
+        <v/>
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
@@ -3641,50 +3637,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F38" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H38" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I38" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L38" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N38" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O38" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3697,13 +3693,11 @@
       </c>
       <c r="S38" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3716,68 +3710,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C39" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D39" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E39" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F39" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H39" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I39" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J39" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K39" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O39" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>86.3</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3789,88 +3793,80 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W39" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C40" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H40" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I40" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J40" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L40" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M40" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N40" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N40" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O40" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3882,55 +3878,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C41" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E41" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F41" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H41" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I41" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K41" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M41" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N41" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3948,12 +3948,14 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
@@ -3964,57 +3966,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C42" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D42" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F42" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H42" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I42" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J42" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L42" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M42" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N42" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O42" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4027,18 +4029,14 @@
       </c>
       <c r="S42" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4057,50 +4055,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C43" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D43" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F43" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H43" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I43" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J43" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K43" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N43" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4113,14 +4111,18 @@
       </c>
       <c r="S43" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4132,57 +4134,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C44" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D44" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F44" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H44" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I44" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J44" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K44" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N44" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4218,57 +4220,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C45" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D45" t="n">
         <v>85.8</v>
       </c>
-      <c r="C45" t="n">
-        <v>89</v>
-      </c>
-      <c r="D45" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E45" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F45" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I45" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J45" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K45" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L45" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N45" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O45" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4276,24 +4278,22 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
@@ -4304,63 +4304,65 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C46" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D46" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E46" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H46" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I46" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J46" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K46" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L46" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M46" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N46" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O46" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
@@ -4369,7 +4371,7 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4386,66 +4388,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C47" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D47" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E47" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H47" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I47" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L47" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N47" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
@@ -4477,69 +4477,63 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C48" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D48" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E48" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H48" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I48" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J48" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K48" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L48" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M48" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N48" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O48" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>91.45</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4561,50 +4555,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C49" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D49" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H49" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I49" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K49" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L49" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N49" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O49" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4615,13 +4609,15 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="S49" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4634,55 +4630,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C50" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D50" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E50" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H50" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I50" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J50" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K50" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L50" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N50" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4695,13 +4695,11 @@
       </c>
       <c r="S50" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4716,57 +4714,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C51" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E51" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H51" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I51" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J51" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K51" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L51" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N51" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O51" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4779,76 +4777,78 @@
       </c>
       <c r="S51" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C52" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D52" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E52" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F52" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H52" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I52" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L52" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M52" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4889,50 +4889,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E53" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F53" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H53" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I53" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K53" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L53" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M53" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N53" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4945,23 +4945,17 @@
       </c>
       <c r="S53" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
@@ -4973,50 +4967,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C54" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D54" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F54" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H54" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I54" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K54" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N54" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O54" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5032,8 +5026,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5051,50 +5047,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C55" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D55" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E55" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F55" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H55" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I55" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J55" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K55" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L55" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M55" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N55" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O55" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5102,18 +5098,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5126,55 +5122,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C56" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D56" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E56" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F56" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H56" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I56" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J56" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K56" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M56" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O56" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5182,18 +5182,18 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5206,59 +5206,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C57" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D57" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F57" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H57" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I57" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K57" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M57" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O57" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5276,11 +5272,13 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5295,50 +5293,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C58" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D58" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E58" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F58" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H58" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I58" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J58" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K58" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L58" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M58" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N58" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O58" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5361,11 +5359,13 @@
       </c>
       <c r="U58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5377,50 +5377,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C59" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D59" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E59" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F59" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H59" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I59" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J59" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K59" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M59" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N59" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O59" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5431,80 +5431,78 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C60" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D60" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E60" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H60" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I60" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J60" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K60" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L60" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M60" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N60" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O60" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5515,13 +5513,15 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+      <c r="S60" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5534,59 +5534,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C61" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D61" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E61" t="n">
-        <v>101.39</v>
+        <v>105.48</v>
       </c>
       <c r="F61" t="n">
-        <v>1.34</v>
+        <v>4.09</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0403</v>
       </c>
       <c r="H61" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I61" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J61" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K61" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M61" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N61" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O61" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5599,7 +5595,7 @@
       </c>
       <c r="S61" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
@@ -5607,8 +5603,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5621,115 +5619,31 @@
       <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>102.01</v>
-      </c>
-      <c r="C62" t="n">
-        <v>103.16</v>
-      </c>
-      <c r="D62" t="n">
-        <v>101.83</v>
-      </c>
-      <c r="E62" t="n">
-        <v>102.98</v>
-      </c>
-      <c r="F62" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0157</v>
-      </c>
-      <c r="H62" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="I62" t="n">
-        <v>96.11</v>
-      </c>
-      <c r="J62" t="n">
-        <v>96.3</v>
-      </c>
-      <c r="K62" t="n">
-        <v>99.18000000000001</v>
-      </c>
-      <c r="L62" t="n">
-        <v>102.06</v>
-      </c>
-      <c r="M62" t="n">
-        <v>103.6</v>
-      </c>
-      <c r="N62" t="n">
-        <v>105.13</v>
-      </c>
-      <c r="O62" t="n">
-        <v>109.37</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>100.5</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>101.89</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>102.32</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>102.74</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>103.65</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>104.55</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>104.49</v>
+      <c r="I62" s="13" t="n">
+        <v>95.67</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>100.69</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>102.71</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>104.73</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>108.25</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>111.77</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>112.29</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5543,25 +5543,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C61" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D61" t="n">
-        <v>101.21</v>
+        <v>104.69</v>
       </c>
       <c r="E61" t="n">
-        <v>105.48</v>
+        <v>105.28</v>
       </c>
       <c r="F61" t="n">
-        <v>4.09</v>
+        <v>3.89</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0403</v>
+        <v>0.0384</v>
       </c>
       <c r="H61" t="n">
-        <v>5.54</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I61" t="n">
         <v>96.11</v>
@@ -5625,25 +5625,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>95.67</v>
+        <v>103.75</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>100.69</v>
+        <v>104.4</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>102.71</v>
+        <v>104.81</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>104.73</v>
+        <v>105.22</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>108.25</v>
+        <v>105.75</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>111.77</v>
+        <v>106.28</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>112.29</v>
+        <v>106.57</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5543,25 +5543,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>105.48</v>
+        <v>102.01</v>
       </c>
       <c r="C61" t="n">
-        <v>105.63</v>
+        <v>106.75</v>
       </c>
       <c r="D61" t="n">
-        <v>104.69</v>
+        <v>101.21</v>
       </c>
       <c r="E61" t="n">
-        <v>105.28</v>
+        <v>105.83</v>
       </c>
       <c r="F61" t="n">
-        <v>3.89</v>
+        <v>4.44</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0384</v>
+        <v>0.0438</v>
       </c>
       <c r="H61" t="n">
-        <v>0.9399999999999999</v>
+        <v>5.54</v>
       </c>
       <c r="I61" t="n">
         <v>96.11</v>
@@ -5619,31 +5619,113 @@
       <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>105.48</v>
+      </c>
+      <c r="C62" t="n">
+        <v>105.63</v>
+      </c>
+      <c r="D62" t="n">
+        <v>104.23</v>
+      </c>
+      <c r="E62" t="n">
+        <v>104.82</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-1.01</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>-0.0095</v>
+      </c>
+      <c r="H62" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="I62" t="n">
+        <v>95.67</v>
+      </c>
+      <c r="J62" t="n">
+        <v>101.22</v>
+      </c>
+      <c r="K62" t="n">
+        <v>103.06</v>
+      </c>
+      <c r="L62" t="n">
+        <v>104.91</v>
+      </c>
+      <c r="M62" t="n">
+        <v>108.6</v>
+      </c>
+      <c r="N62" t="n">
+        <v>112.3</v>
+      </c>
+      <c r="O62" t="n">
+        <v>112.29</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>103.75</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>104.4</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>104.81</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>105.22</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>105.75</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>106.28</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>106.57</v>
+      <c r="I63" s="13" t="n">
+        <v>102.83</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>103.37</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>104.12</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>104.88</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>105.52</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>106.16</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>107.03</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5631,19 +5631,19 @@
         <v>105.63</v>
       </c>
       <c r="D62" t="n">
-        <v>104.23</v>
+        <v>102.85</v>
       </c>
       <c r="E62" t="n">
-        <v>104.82</v>
+        <v>103.27</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.01</v>
+        <v>-2.56</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0242</v>
       </c>
       <c r="H62" t="n">
-        <v>1.4</v>
+        <v>2.78</v>
       </c>
       <c r="I62" t="n">
         <v>95.67</v>
@@ -5672,12 +5672,14 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5707,25 +5709,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>102.83</v>
+        <v>100.07</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>103.37</v>
+        <v>100</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>104.12</v>
+        <v>101.88</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>104.88</v>
+        <v>103.75</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>105.52</v>
+        <v>104.66</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>106.16</v>
+        <v>105.56</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>107.03</v>
+        <v>108.41</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5634,13 +5634,13 @@
         <v>102.85</v>
       </c>
       <c r="E62" t="n">
-        <v>103.27</v>
+        <v>103.22</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.56</v>
+        <v>-2.61</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0242</v>
+        <v>-0.0247</v>
       </c>
       <c r="H62" t="n">
         <v>2.78</v>
@@ -5712,19 +5712,19 @@
         <v>100.07</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>100</v>
+        <v>99.93000000000001</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>101.88</v>
+        <v>101.83</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>103.75</v>
+        <v>103.73</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>104.66</v>
+        <v>104.61</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>105.56</v>
+        <v>105.49</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>108.41</v>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5634,13 +5634,13 @@
         <v>102.85</v>
       </c>
       <c r="E62" t="n">
-        <v>103.22</v>
+        <v>103.55</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.61</v>
+        <v>-2.28</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0247</v>
+        <v>-0.0215</v>
       </c>
       <c r="H62" t="n">
         <v>2.78</v>
@@ -5712,19 +5712,19 @@
         <v>100.07</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>99.93000000000001</v>
+        <v>100.43</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>101.83</v>
+        <v>102.16</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>103.73</v>
+        <v>103.9</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>104.61</v>
+        <v>104.94</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>105.49</v>
+        <v>105.99</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>108.41</v>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>78.93000000000001</v>
+        <v>74.14</v>
       </c>
       <c r="C2" t="n">
-        <v>78.95999999999999</v>
+        <v>74.45</v>
       </c>
       <c r="D2" t="n">
-        <v>74.45</v>
+        <v>72.48</v>
       </c>
       <c r="E2" t="n">
-        <v>74.81999999999999</v>
+        <v>73.20999999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.78</v>
+        <v>-1.61</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0232</v>
+        <v>-0.0215</v>
       </c>
       <c r="H2" t="n">
-        <v>4.51</v>
+        <v>1.97</v>
       </c>
       <c r="I2" t="n">
-        <v>70.17</v>
+        <v>69.94</v>
       </c>
       <c r="J2" t="n">
-        <v>73.84999999999999</v>
+        <v>69.37</v>
       </c>
       <c r="K2" t="n">
-        <v>74.90000000000001</v>
+        <v>72.56</v>
       </c>
       <c r="L2" t="n">
-        <v>75.94</v>
+        <v>75.76000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>78.3</v>
+        <v>77.08</v>
       </c>
       <c r="N2" t="n">
-        <v>80.67</v>
+        <v>78.39</v>
       </c>
       <c r="O2" t="n">
-        <v>80.40000000000001</v>
+        <v>83.47</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -702,10 +702,8 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -720,67 +718,71 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.14</v>
+        <v>73.13</v>
       </c>
       <c r="C3" t="n">
-        <v>74.45</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>72.48</v>
+        <v>69.63</v>
       </c>
       <c r="E3" t="n">
-        <v>73.20999999999999</v>
+        <v>70.34</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.61</v>
+        <v>-2.87</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0215</v>
+        <v>-0.0392</v>
       </c>
       <c r="H3" t="n">
-        <v>1.97</v>
+        <v>3.55</v>
       </c>
       <c r="I3" t="n">
-        <v>69.94</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>69.37</v>
+        <v>71.11</v>
       </c>
       <c r="K3" t="n">
-        <v>72.56</v>
+        <v>72.23</v>
       </c>
       <c r="L3" t="n">
-        <v>75.76000000000001</v>
+        <v>73.34</v>
       </c>
       <c r="M3" t="n">
-        <v>77.08</v>
+        <v>74.19</v>
       </c>
       <c r="N3" t="n">
-        <v>78.39</v>
+        <v>75.05</v>
       </c>
       <c r="O3" t="n">
-        <v>83.47</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+        <v>76.42</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
@@ -797,88 +799,80 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>73.13</v>
+        <v>69.95</v>
       </c>
       <c r="C4" t="n">
-        <v>73.18000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="D4" t="n">
-        <v>69.63</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>70.34</v>
+        <v>71.92</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.87</v>
+        <v>1.58</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0392</v>
+        <v>0.0225</v>
       </c>
       <c r="H4" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I4" t="n">
-        <v>70.51000000000001</v>
+        <v>66.08</v>
       </c>
       <c r="J4" t="n">
-        <v>71.11</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>72.23</v>
+        <v>68.56</v>
       </c>
       <c r="L4" t="n">
-        <v>73.34</v>
+        <v>70.87</v>
       </c>
       <c r="M4" t="n">
-        <v>74.19</v>
+        <v>72.11</v>
       </c>
       <c r="N4" t="n">
-        <v>75.05</v>
+        <v>73.36</v>
       </c>
       <c r="O4" t="n">
-        <v>76.42</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>76.73</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -890,75 +884,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69.95</v>
+        <v>71.44</v>
       </c>
       <c r="C5" t="n">
-        <v>72.5</v>
+        <v>71.86</v>
       </c>
       <c r="D5" t="n">
-        <v>68.90000000000001</v>
+        <v>68.56</v>
       </c>
       <c r="E5" t="n">
-        <v>71.92</v>
+        <v>69.23</v>
       </c>
       <c r="F5" t="n">
-        <v>1.58</v>
+        <v>-2.69</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0225</v>
+        <v>-0.0374</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="I5" t="n">
-        <v>66.08</v>
+        <v>65.3</v>
       </c>
       <c r="J5" t="n">
-        <v>66.26000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>68.56</v>
+        <v>70.12</v>
       </c>
       <c r="L5" t="n">
-        <v>70.87</v>
+        <v>71.31</v>
       </c>
       <c r="M5" t="n">
-        <v>72.11</v>
+        <v>73.72</v>
       </c>
       <c r="N5" t="n">
-        <v>73.36</v>
+        <v>76.13</v>
       </c>
       <c r="O5" t="n">
-        <v>76.73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -970,81 +970,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71.44</v>
+        <v>70.5</v>
       </c>
       <c r="C6" t="n">
-        <v>71.86</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>68.56</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>69.23</v>
+        <v>70.75</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.69</v>
+        <v>1.52</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0374</v>
+        <v>0.022</v>
       </c>
       <c r="H6" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="I6" t="n">
-        <v>65.3</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>68.93000000000001</v>
+        <v>65.44</v>
       </c>
       <c r="K6" t="n">
-        <v>70.12</v>
+        <v>67.58</v>
       </c>
       <c r="L6" t="n">
-        <v>71.31</v>
+        <v>69.72</v>
       </c>
       <c r="M6" t="n">
-        <v>73.72</v>
+        <v>70.88</v>
       </c>
       <c r="N6" t="n">
-        <v>76.13</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>76.09999999999999</v>
+        <v>75.16</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1056,75 +1050,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70.5</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>71.15000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>69.31999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="E7" t="n">
-        <v>70.75</v>
+        <v>69.5</v>
       </c>
       <c r="F7" t="n">
-        <v>1.52</v>
+        <v>-1.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.022</v>
+        <v>-0.0177</v>
       </c>
       <c r="H7" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="I7" t="n">
-        <v>65.26000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>65.44</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>67.58</v>
+        <v>69.83</v>
       </c>
       <c r="L7" t="n">
-        <v>69.72</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>70.88</v>
+        <v>71.67</v>
       </c>
       <c r="N7" t="n">
-        <v>72.04000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="O7" t="n">
-        <v>75.16</v>
+        <v>72.98</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="Q7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1138,71 +1138,69 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>70.43000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="C8" t="n">
-        <v>71.59999999999999</v>
+        <v>70.19</v>
       </c>
       <c r="D8" t="n">
-        <v>69.22</v>
+        <v>67.92</v>
       </c>
       <c r="E8" t="n">
-        <v>69.5</v>
+        <v>68.58</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0132</v>
       </c>
       <c r="H8" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="I8" t="n">
-        <v>67.48999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="J8" t="n">
-        <v>69.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="K8" t="n">
-        <v>69.83</v>
+        <v>68.31</v>
       </c>
       <c r="L8" t="n">
-        <v>70.48999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="M8" t="n">
-        <v>71.67</v>
+        <v>70.69</v>
       </c>
       <c r="N8" t="n">
-        <v>72.84</v>
+        <v>71.42</v>
       </c>
       <c r="O8" t="n">
-        <v>72.98</v>
+        <v>73.98</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1222,59 +1220,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>69.98</v>
+        <v>68.03</v>
       </c>
       <c r="C9" t="n">
-        <v>70.19</v>
+        <v>68.8</v>
       </c>
       <c r="D9" t="n">
-        <v>67.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>68.58</v>
+        <v>68.69</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.0016</v>
       </c>
       <c r="H9" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="I9" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>66.67</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>68.31</v>
+        <v>67.44</v>
       </c>
       <c r="L9" t="n">
-        <v>69.95</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>70.69</v>
+        <v>69.72</v>
       </c>
       <c r="N9" t="n">
-        <v>71.42</v>
+        <v>70.61</v>
       </c>
       <c r="O9" t="n">
-        <v>73.98</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1284,12 +1278,12 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1306,55 +1300,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D10" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E10" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F10" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H10" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I10" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J10" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L10" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M10" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O10" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1362,14 +1360,12 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1388,57 +1384,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C11" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E11" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H11" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I11" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L11" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M11" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N11" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1451,76 +1447,78 @@
       </c>
       <c r="S11" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W11" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W11" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C12" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D12" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E12" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F12" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H12" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I12" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L12" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N12" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1543,13 +1541,11 @@
       </c>
       <c r="U12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1561,50 +1557,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C13" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D13" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E13" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F13" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H13" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I13" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J13" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M13" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1612,24 +1608,22 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
@@ -1638,55 +1632,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C14" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D14" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E14" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I14" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K14" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L14" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N14" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O14" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1727,50 +1725,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C15" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D15" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E15" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I15" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J15" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L15" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M15" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N15" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O15" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1778,83 +1776,83 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
-      </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D16" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E16" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F16" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H16" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I16" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J16" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K16" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M16" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N16" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O16" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1872,18 +1870,14 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1895,50 +1889,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E17" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H17" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I17" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J17" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K17" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L17" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M17" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N17" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O17" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1951,13 +1945,11 @@
       </c>
       <c r="S17" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1970,55 +1962,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C18" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D18" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E18" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F18" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I18" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J18" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K18" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L18" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M18" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N18" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O18" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2029,9 +2025,9 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2050,57 +2046,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E19" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H19" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I19" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K19" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L19" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M19" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N19" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2111,78 +2107,80 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
+      <c r="S19" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D20" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E20" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F20" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H20" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I20" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J20" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L20" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M20" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N20" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,8 +2188,10 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S20" s="11" t="inlineStr">
         <is>
@@ -2200,18 +2200,14 @@
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2223,50 +2219,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C21" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D21" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E21" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F21" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H21" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I21" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K21" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L21" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M21" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O21" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,10 +2270,8 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="11" t="inlineStr">
         <is>
@@ -2305,50 +2299,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C22" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D22" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E22" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F22" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H22" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I22" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J22" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K22" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L22" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M22" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N22" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2385,50 +2379,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C23" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D23" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F23" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H23" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I23" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J23" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K23" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L23" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N23" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2446,14 +2440,18 @@
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2465,50 +2463,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C24" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D24" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F24" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H24" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I24" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J24" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M24" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N24" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2516,93 +2514,97 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
+      </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C25" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D25" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E25" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H25" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I25" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J25" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K25" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L25" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M25" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N25" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
@@ -2619,78 +2621,70 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W25" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C26" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E26" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H26" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I26" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J26" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K26" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L26" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O26" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
@@ -2717,50 +2711,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E27" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I27" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J27" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K27" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L27" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M27" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N27" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2768,28 +2762,30 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2797,50 +2793,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D28" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E28" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F28" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H28" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I28" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J28" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K28" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L28" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N28" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O28" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2851,20 +2847,16 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2874,55 +2866,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C29" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D29" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E29" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H29" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I29" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J29" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K29" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M29" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O29" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2930,19 +2926,25 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2961,76 +2963,74 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D30" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F30" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H30" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I30" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J30" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N30" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O30" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S30" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3042,64 +3042,66 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D31" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E31" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F31" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H31" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I31" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J31" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N31" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O31" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q31" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
@@ -3112,8 +3114,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3121,89 +3125,81 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W31" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C32" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D32" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F32" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H32" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I32" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J32" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L32" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N32" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3216,59 +3212,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C33" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H33" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I33" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J33" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K33" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M33" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N33" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O33" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3279,16 +3271,20 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+      <c r="S33" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3298,55 +3294,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C34" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D34" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E34" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H34" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I34" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J34" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K34" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M34" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O34" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3364,13 +3364,11 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3389,50 +3387,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C35" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D35" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F35" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H35" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I35" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L35" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M35" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N35" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3450,73 +3448,73 @@
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W35" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W35" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D36" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E36" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F36" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H36" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I36" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J36" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K36" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L36" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M36" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N36" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3534,18 +3532,14 @@
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V36" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V36" s="8" t="n">
+        <v/>
       </c>
       <c r="W36" s="9" t="inlineStr">
         <is>
@@ -3557,50 +3551,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F37" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H37" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I37" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L37" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N37" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O37" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3613,13 +3607,11 @@
       </c>
       <c r="S37" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3632,68 +3624,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C38" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D38" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E38" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F38" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H38" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I38" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J38" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K38" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O38" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>86.3</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3705,88 +3707,80 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W38" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C39" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H39" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I39" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J39" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L39" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M39" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N39" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N39" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O39" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3798,55 +3792,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C40" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E40" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F40" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H40" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I40" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M40" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N40" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3864,12 +3862,14 @@
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
@@ -3880,57 +3880,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C41" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D41" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F41" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H41" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I41" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L41" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M41" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N41" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O41" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3943,18 +3943,14 @@
       </c>
       <c r="S41" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3973,50 +3969,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C42" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D42" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F42" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H42" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I42" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J42" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K42" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N42" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4029,14 +4025,18 @@
       </c>
       <c r="S42" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4048,57 +4048,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C43" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D43" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F43" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H43" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I43" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J43" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K43" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N43" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4134,57 +4134,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C44" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D44" t="n">
         <v>85.8</v>
       </c>
-      <c r="C44" t="n">
-        <v>89</v>
-      </c>
-      <c r="D44" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E44" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F44" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I44" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J44" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K44" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L44" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N44" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O44" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4192,24 +4192,22 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4220,63 +4218,65 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C45" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D45" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E45" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H45" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I45" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J45" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K45" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L45" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M45" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N45" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O45" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4302,66 +4302,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C46" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D46" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E46" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H46" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I46" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L46" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N46" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
@@ -4393,69 +4391,63 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C47" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D47" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E47" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H47" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I47" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J47" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K47" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L47" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M47" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N47" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O47" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>91.45</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4477,50 +4469,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C48" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D48" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H48" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I48" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K48" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L48" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N48" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O48" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4531,13 +4523,15 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="S48" s="11" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4550,55 +4544,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C49" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D49" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E49" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H49" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I49" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J49" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K49" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L49" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N49" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4611,13 +4609,11 @@
       </c>
       <c r="S49" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4632,57 +4628,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C50" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E50" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H50" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I50" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J50" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K50" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L50" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N50" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O50" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4695,76 +4691,78 @@
       </c>
       <c r="S50" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C51" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D51" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E51" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F51" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H51" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I51" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L51" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M51" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4805,50 +4803,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E52" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F52" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H52" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I52" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K52" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L52" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M52" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N52" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4861,23 +4859,17 @@
       </c>
       <c r="S52" s="11" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
@@ -4889,50 +4881,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C53" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D53" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F53" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H53" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I53" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K53" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N53" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O53" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4948,8 +4940,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4967,50 +4961,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C54" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D54" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E54" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F54" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H54" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I54" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J54" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K54" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L54" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M54" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N54" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O54" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5018,18 +5012,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S54" s="11" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5042,55 +5036,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C55" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D55" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E55" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F55" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H55" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I55" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J55" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K55" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O55" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5098,18 +5096,18 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5122,59 +5120,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C56" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D56" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F56" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H56" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I56" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K56" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M56" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O56" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5192,11 +5186,13 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5211,50 +5207,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C57" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D57" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E57" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F57" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H57" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I57" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J57" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K57" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L57" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M57" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N57" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O57" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5277,11 +5273,13 @@
       </c>
       <c r="U57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5293,50 +5291,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C58" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D58" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E58" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F58" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H58" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I58" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J58" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K58" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M58" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N58" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O58" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5347,80 +5345,78 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C59" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D59" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E59" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H59" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I59" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J59" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K59" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L59" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M59" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N59" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O59" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5431,13 +5427,15 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+      <c r="S59" s="11" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5450,59 +5448,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C60" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D60" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E60" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F60" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H60" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I60" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J60" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K60" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M60" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N60" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O60" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5515,7 +5509,7 @@
       </c>
       <c r="S60" s="11" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
@@ -5523,8 +5517,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U60" s="8" t="n">
-        <v/>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5539,74 +5535,74 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>102.01</v>
+        <v>102.18</v>
       </c>
       <c r="C61" t="n">
-        <v>106.75</v>
+        <v>102.24</v>
       </c>
       <c r="D61" t="n">
-        <v>101.21</v>
+        <v>101.87</v>
       </c>
       <c r="E61" t="n">
-        <v>105.83</v>
+        <v>102.13</v>
       </c>
       <c r="F61" t="n">
-        <v>4.44</v>
+        <v>-3.7</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.035</v>
       </c>
       <c r="H61" t="n">
-        <v>5.54</v>
+        <v>0.37</v>
       </c>
       <c r="I61" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J61" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K61" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L61" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M61" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N61" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O61" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5616,118 +5612,38 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>105.48</v>
-      </c>
-      <c r="C62" t="n">
-        <v>105.63</v>
-      </c>
-      <c r="D62" t="n">
-        <v>102.85</v>
-      </c>
-      <c r="E62" t="n">
-        <v>103.55</v>
-      </c>
-      <c r="F62" t="n">
-        <v>-2.28</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>-0.0215</v>
-      </c>
-      <c r="H62" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="I62" t="n">
-        <v>95.67</v>
-      </c>
-      <c r="J62" t="n">
-        <v>101.22</v>
-      </c>
-      <c r="K62" t="n">
-        <v>103.06</v>
-      </c>
-      <c r="L62" t="n">
-        <v>104.91</v>
-      </c>
-      <c r="M62" t="n">
-        <v>108.6</v>
-      </c>
-      <c r="N62" t="n">
-        <v>112.3</v>
-      </c>
-      <c r="O62" t="n">
-        <v>112.29</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>100.07</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>100.43</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>102.16</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>103.9</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>104.94</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>105.99</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>108.41</v>
+      <c r="I62" s="13" t="n">
+        <v>101.5</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>101.8</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>101.94</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>102.09</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>102.31</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>102.54</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>102.61</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5545,19 +5545,19 @@
         <v>102.24</v>
       </c>
       <c r="D61" t="n">
-        <v>101.87</v>
+        <v>101.07</v>
       </c>
       <c r="E61" t="n">
-        <v>102.13</v>
+        <v>101.18</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.7</v>
+        <v>-4.65</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.035</v>
+        <v>-0.0439</v>
       </c>
       <c r="H61" t="n">
-        <v>0.37</v>
+        <v>1.17</v>
       </c>
       <c r="I61" t="n">
         <v>95.67</v>
@@ -5607,16 +5607,12 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W61" s="10" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5625,25 +5621,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>101.5</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>101.8</v>
+        <v>99.77</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>101.94</v>
+        <v>100.6</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>102.09</v>
+        <v>101.42</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>102.31</v>
+        <v>101.76</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>102.54</v>
+        <v>102.11</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>102.61</v>
+        <v>103.41</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5539,25 +5539,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>102.18</v>
+        <v>105.48</v>
       </c>
       <c r="C61" t="n">
-        <v>102.24</v>
+        <v>105.63</v>
       </c>
       <c r="D61" t="n">
-        <v>101.07</v>
+        <v>100.97</v>
       </c>
       <c r="E61" t="n">
-        <v>101.18</v>
+        <v>102.43</v>
       </c>
       <c r="F61" t="n">
-        <v>-4.65</v>
+        <v>-3.4</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0439</v>
+        <v>-0.0321</v>
       </c>
       <c r="H61" t="n">
-        <v>1.17</v>
+        <v>4.66</v>
       </c>
       <c r="I61" t="n">
         <v>95.67</v>
@@ -5585,14 +5585,14 @@
       </c>
       <c r="Q61" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5607,39 +5607,127 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>101.06</v>
+      </c>
+      <c r="C62" t="n">
+        <v>101.16</v>
+      </c>
+      <c r="D62" t="n">
+        <v>100.88</v>
+      </c>
+      <c r="E62" t="n">
+        <v>100.98</v>
+      </c>
+      <c r="F62" t="n">
+        <v>-1.45</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>-0.0142</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="I62" t="n">
+        <v>96.31</v>
+      </c>
+      <c r="J62" t="n">
+        <v>97.34</v>
+      </c>
+      <c r="K62" t="n">
+        <v>100.1</v>
+      </c>
+      <c r="L62" t="n">
+        <v>102.86</v>
+      </c>
+      <c r="M62" t="n">
+        <v>104.76</v>
+      </c>
+      <c r="N62" t="n">
+        <v>106.65</v>
+      </c>
+      <c r="O62" t="n">
+        <v>110.29</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>99.90000000000001</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>99.77</v>
-      </c>
-      <c r="K62" s="13" t="n">
+      <c r="I63" s="13" t="n">
         <v>100.6</v>
       </c>
-      <c r="L62" s="13" t="n">
-        <v>101.42</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>101.76</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>102.11</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>103.41</v>
+      <c r="J63" s="13" t="n">
+        <v>100.68</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>100.84</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>101</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>101.12</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>101.24</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>101.44</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5628,22 +5628,22 @@
         <v>101.06</v>
       </c>
       <c r="C62" t="n">
-        <v>101.16</v>
+        <v>101.33</v>
       </c>
       <c r="D62" t="n">
         <v>100.88</v>
       </c>
       <c r="E62" t="n">
-        <v>100.98</v>
+        <v>101.09</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.45</v>
+        <v>-1.34</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0142</v>
+        <v>-0.0131</v>
       </c>
       <c r="H62" t="n">
-        <v>0.28</v>
+        <v>0.45</v>
       </c>
       <c r="I62" t="n">
         <v>96.31</v>
@@ -5709,25 +5709,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>100.6</v>
+        <v>100.43</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>100.68</v>
+        <v>100.63</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>100.84</v>
+        <v>100.86</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>101</v>
+        <v>101.1</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>101.12</v>
+        <v>101.31</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>101.24</v>
+        <v>101.53</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>101.44</v>
+        <v>101.78</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5631,19 +5624,19 @@
         <v>101.33</v>
       </c>
       <c r="D62" t="n">
-        <v>100.88</v>
+        <v>100.76</v>
       </c>
       <c r="E62" t="n">
-        <v>101.09</v>
+        <v>100.9</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.34</v>
+        <v>-1.53</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0131</v>
+        <v>-0.0149</v>
       </c>
       <c r="H62" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="I62" t="n">
         <v>96.31</v>
@@ -5700,34 +5693,6 @@
         <is>
           <t>強警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>100.43</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>100.63</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>100.86</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>101.1</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>101.31</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>101.53</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>101.78</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5627,13 +5627,13 @@
         <v>100.76</v>
       </c>
       <c r="E62" t="n">
-        <v>100.9</v>
+        <v>100.89</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.53</v>
+        <v>-1.54</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0149</v>
+        <v>-0.015</v>
       </c>
       <c r="H62" t="n">
         <v>0.57</v>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,60 +634,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>74.14</v>
+        <v>73.13</v>
       </c>
       <c r="C2" t="n">
-        <v>74.45</v>
+        <v>73.18000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>72.48</v>
+        <v>69.63</v>
       </c>
       <c r="E2" t="n">
-        <v>73.20999999999999</v>
+        <v>70.34</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.61</v>
+        <v>-2.87</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0215</v>
+        <v>-0.0392</v>
       </c>
       <c r="H2" t="n">
-        <v>1.97</v>
+        <v>3.55</v>
       </c>
       <c r="I2" t="n">
-        <v>69.94</v>
+        <v>70.51000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>69.37</v>
+        <v>71.11</v>
       </c>
       <c r="K2" t="n">
-        <v>72.56</v>
+        <v>72.23</v>
       </c>
       <c r="L2" t="n">
-        <v>75.76000000000001</v>
+        <v>73.34</v>
       </c>
       <c r="M2" t="n">
-        <v>77.08</v>
+        <v>74.19</v>
       </c>
       <c r="N2" t="n">
-        <v>78.39</v>
+        <v>75.05</v>
       </c>
       <c r="O2" t="n">
-        <v>83.47</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>76.42</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -706,410 +710,406 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73.13</v>
+        <v>69.95</v>
       </c>
       <c r="C3" t="n">
-        <v>73.18000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="D3" t="n">
-        <v>69.63</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>70.34</v>
+        <v>71.92</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.87</v>
+        <v>1.58</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0392</v>
+        <v>0.0225</v>
       </c>
       <c r="H3" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I3" t="n">
-        <v>70.51000000000001</v>
+        <v>66.08</v>
       </c>
       <c r="J3" t="n">
-        <v>71.11</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>72.23</v>
+        <v>68.56</v>
       </c>
       <c r="L3" t="n">
-        <v>73.34</v>
+        <v>70.87</v>
       </c>
       <c r="M3" t="n">
-        <v>74.19</v>
+        <v>72.11</v>
       </c>
       <c r="N3" t="n">
-        <v>75.05</v>
+        <v>73.36</v>
       </c>
       <c r="O3" t="n">
-        <v>76.42</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>76.73</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="10" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69.95</v>
+        <v>71.44</v>
       </c>
       <c r="C4" t="n">
-        <v>72.5</v>
+        <v>71.86</v>
       </c>
       <c r="D4" t="n">
-        <v>68.90000000000001</v>
+        <v>68.56</v>
       </c>
       <c r="E4" t="n">
-        <v>71.92</v>
+        <v>69.23</v>
       </c>
       <c r="F4" t="n">
-        <v>1.58</v>
+        <v>-2.69</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0225</v>
+        <v>-0.0374</v>
       </c>
       <c r="H4" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="I4" t="n">
-        <v>66.08</v>
+        <v>65.3</v>
       </c>
       <c r="J4" t="n">
-        <v>66.26000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>68.56</v>
+        <v>70.12</v>
       </c>
       <c r="L4" t="n">
-        <v>70.87</v>
+        <v>71.31</v>
       </c>
       <c r="M4" t="n">
-        <v>72.11</v>
+        <v>73.72</v>
       </c>
       <c r="N4" t="n">
-        <v>73.36</v>
+        <v>76.13</v>
       </c>
       <c r="O4" t="n">
-        <v>76.73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+      <c r="Q4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="10" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71.44</v>
+        <v>70.5</v>
       </c>
       <c r="C5" t="n">
-        <v>71.86</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>68.56</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>69.23</v>
+        <v>70.75</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.69</v>
+        <v>1.52</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0374</v>
+        <v>0.022</v>
       </c>
       <c r="H5" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="I5" t="n">
-        <v>65.3</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>68.93000000000001</v>
+        <v>65.44</v>
       </c>
       <c r="K5" t="n">
-        <v>70.12</v>
+        <v>67.58</v>
       </c>
       <c r="L5" t="n">
-        <v>71.31</v>
+        <v>69.72</v>
       </c>
       <c r="M5" t="n">
-        <v>73.72</v>
+        <v>70.88</v>
       </c>
       <c r="N5" t="n">
-        <v>76.13</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>76.09999999999999</v>
+        <v>75.16</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="10" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70.5</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>71.15000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>69.31999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="E6" t="n">
-        <v>70.75</v>
+        <v>69.5</v>
       </c>
       <c r="F6" t="n">
-        <v>1.52</v>
+        <v>-1.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.022</v>
+        <v>-0.0177</v>
       </c>
       <c r="H6" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="I6" t="n">
-        <v>65.26000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>65.44</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>67.58</v>
+        <v>69.83</v>
       </c>
       <c r="L6" t="n">
-        <v>69.72</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>70.88</v>
+        <v>71.67</v>
       </c>
       <c r="N6" t="n">
-        <v>72.04000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="O6" t="n">
-        <v>75.16</v>
+        <v>72.98</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+      <c r="Q6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="10" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>70.43000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="C7" t="n">
-        <v>71.59999999999999</v>
+        <v>70.19</v>
       </c>
       <c r="D7" t="n">
-        <v>69.22</v>
+        <v>67.92</v>
       </c>
       <c r="E7" t="n">
-        <v>69.5</v>
+        <v>68.58</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0132</v>
       </c>
       <c r="H7" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="I7" t="n">
-        <v>67.48999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="J7" t="n">
-        <v>69.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="K7" t="n">
-        <v>69.83</v>
+        <v>68.31</v>
       </c>
       <c r="L7" t="n">
-        <v>70.48999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="M7" t="n">
-        <v>71.67</v>
+        <v>70.69</v>
       </c>
       <c r="N7" t="n">
-        <v>72.84</v>
+        <v>71.42</v>
       </c>
       <c r="O7" t="n">
-        <v>72.98</v>
+        <v>73.98</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1124,64 +1124,60 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="10" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>69.98</v>
+        <v>68.03</v>
       </c>
       <c r="C8" t="n">
-        <v>70.19</v>
+        <v>68.8</v>
       </c>
       <c r="D8" t="n">
-        <v>67.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>68.58</v>
+        <v>68.69</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.0016</v>
       </c>
       <c r="H8" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="I8" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>66.67</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>68.31</v>
+        <v>67.44</v>
       </c>
       <c r="L8" t="n">
-        <v>69.95</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>70.69</v>
+        <v>69.72</v>
       </c>
       <c r="N8" t="n">
-        <v>71.42</v>
+        <v>70.61</v>
       </c>
       <c r="O8" t="n">
-        <v>73.98</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,12 +1187,12 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1208,60 +1204,64 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="10" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E9" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F9" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H9" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I9" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J9" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L9" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M9" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O9" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1269,14 +1269,12 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1288,64 +1286,64 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="10" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C10" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E10" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H10" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I10" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L10" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M10" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N10" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1356,78 +1354,80 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W10" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W10" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C11" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D11" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E11" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F11" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H11" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I11" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L11" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M11" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N11" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1438,7 +1438,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="11" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1450,15 +1450,13 @@
       </c>
       <c r="U11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="V11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1468,50 +1466,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C12" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D12" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E12" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F12" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H12" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I12" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J12" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L12" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M12" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1519,81 +1517,83 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C13" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D13" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E13" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I13" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K13" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L13" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N13" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O13" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1620,7 +1620,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1634,50 +1634,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C14" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D14" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E14" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I14" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J14" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L14" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M14" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N14" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O14" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1685,83 +1685,83 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D15" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E15" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F15" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H15" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I15" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J15" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K15" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M15" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N15" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O15" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1772,27 +1772,23 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="11" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1802,50 +1798,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E16" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H16" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I16" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J16" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K16" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L16" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M16" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N16" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O16" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1856,15 +1852,13 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1872,60 +1866,64 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C17" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D17" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E17" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F17" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I17" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J17" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K17" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L17" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M17" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N17" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O17" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1936,9 +1934,9 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1950,64 +1948,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E18" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H18" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I18" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K18" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L18" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M18" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N18" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2018,78 +2016,80 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D19" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E19" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F19" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H19" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I19" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J19" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L19" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M19" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N19" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2097,30 +2097,28 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="11" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2130,50 +2128,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C20" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D20" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E20" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F20" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H20" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I20" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K20" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L20" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M20" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O20" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2181,12 +2179,10 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="11" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2202,7 +2198,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2212,50 +2208,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C21" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D21" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E21" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F21" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H21" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I21" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J21" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K21" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L21" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M21" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N21" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2266,7 +2262,7 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="11" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2282,7 +2278,7 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2292,50 +2288,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C22" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D22" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F22" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H22" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I22" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J22" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K22" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L22" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N22" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2346,23 +2342,27 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="11" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2372,50 +2372,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C23" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D23" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F23" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H23" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I23" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J23" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M23" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N23" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2423,93 +2423,97 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C24" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D24" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E24" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H24" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I24" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J24" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K24" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L24" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M24" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N24" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S24" s="7" t="inlineStr">
@@ -2528,78 +2532,70 @@
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C25" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E25" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H25" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I25" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J25" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K25" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L25" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O25" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2614,7 +2610,7 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="10" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2624,50 +2620,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E26" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I26" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J26" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K26" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L26" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N26" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2675,28 +2671,30 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2704,50 +2702,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D27" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E27" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F27" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H27" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I27" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J27" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K27" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L27" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N27" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O27" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2758,78 +2756,78 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C28" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D28" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E28" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H28" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I28" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J28" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K28" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M28" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O28" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2837,24 +2835,30 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2868,145 +2872,145 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D29" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F29" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H29" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I29" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J29" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N29" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O29" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D30" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E30" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F30" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H30" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I30" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J30" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N30" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O30" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q30" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
@@ -3019,8 +3023,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3030,87 +3036,79 @@
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C31" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D31" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F31" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H31" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I31" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J31" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L31" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N31" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3118,64 +3116,60 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="10" t="inlineStr">
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C32" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H32" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I32" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J32" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K32" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M32" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N32" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O32" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3186,74 +3180,82 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="10" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C33" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D33" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E33" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H33" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I33" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J33" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K33" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M33" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O33" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3264,25 +3266,23 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="11" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="10" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3296,50 +3296,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C34" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D34" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F34" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H34" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I34" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L34" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M34" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N34" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3350,80 +3350,80 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="11" t="inlineStr">
+      <c r="S34" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D35" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E35" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F35" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H35" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I35" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J35" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K35" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L35" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M35" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N35" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3434,27 +3434,23 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="11" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3464,50 +3460,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F36" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H36" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I36" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L36" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N36" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O36" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3518,15 +3514,13 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3534,73 +3528,83 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C37" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D37" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E37" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F37" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H37" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I37" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J37" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K37" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O37" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>86.3</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3614,146 +3618,142 @@
       </c>
       <c r="W37" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C38" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H38" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I38" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J38" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L38" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M38" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N38" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N38" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O38" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="10" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C39" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E39" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F39" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H39" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I39" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K39" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M39" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N39" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3764,80 +3764,82 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="11" t="inlineStr">
+      <c r="S39" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="10" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C40" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D40" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F40" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H40" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I40" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J40" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L40" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M40" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N40" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O40" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3848,25 +3850,21 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="10" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3880,50 +3878,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C41" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D41" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F41" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H41" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I41" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J41" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K41" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N41" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3934,78 +3932,82 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="10" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C42" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D42" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F42" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H42" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I42" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J42" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K42" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N42" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4016,7 +4018,7 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="11" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4034,64 +4036,64 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="10" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C43" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D43" t="n">
         <v>85.8</v>
       </c>
-      <c r="C43" t="n">
-        <v>89</v>
-      </c>
-      <c r="D43" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E43" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F43" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I43" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J43" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K43" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L43" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N43" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O43" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4099,91 +4101,91 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="10" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C44" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D44" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E44" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H44" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I44" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J44" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K44" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L44" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M44" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N44" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O44" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
@@ -4192,7 +4194,7 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4204,71 +4206,69 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="10" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C45" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D45" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E45" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H45" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I45" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L45" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N45" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
@@ -4290,7 +4290,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="10" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4300,69 +4300,63 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C46" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D46" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E46" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H46" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I46" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J46" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K46" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L46" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M46" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N46" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O46" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>91.45</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4374,7 +4368,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="10" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4384,50 +4378,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C47" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D47" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H47" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I47" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K47" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L47" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N47" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O47" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4438,13 +4432,15 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4452,60 +4448,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="10" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C48" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D48" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E48" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H48" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I48" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J48" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K48" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L48" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N48" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4516,15 +4516,13 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4532,64 +4530,64 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="10" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C49" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E49" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H49" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I49" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J49" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K49" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L49" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N49" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O49" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4600,78 +4598,80 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="10" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C50" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D50" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E50" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F50" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H50" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I50" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L50" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M50" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4682,7 +4682,7 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="11" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4702,7 +4702,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4712,50 +4712,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E51" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F51" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H51" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I51" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K51" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L51" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M51" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N51" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O51" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4766,27 +4766,21 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4796,50 +4790,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C52" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D52" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F52" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H52" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I52" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K52" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N52" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O52" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4850,13 +4844,15 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="11" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4864,7 +4860,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4874,50 +4870,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C53" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D53" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E53" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F53" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H53" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I53" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J53" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K53" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L53" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M53" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N53" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O53" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4925,18 +4921,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="11" t="inlineStr">
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4944,60 +4940,64 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C54" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D54" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E54" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F54" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H54" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I54" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J54" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K54" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O54" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5005,18 +5005,18 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5024,64 +5024,60 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C55" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D55" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F55" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H55" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I55" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K55" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M55" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O55" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5092,23 +5088,25 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="11" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5118,50 +5116,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C56" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D56" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E56" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F56" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H56" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I56" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J56" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K56" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L56" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M56" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N56" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5172,7 +5170,7 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="11" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5184,13 +5182,15 @@
       </c>
       <c r="U56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5200,50 +5200,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C57" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D57" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E57" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F57" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H57" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I57" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J57" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K57" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M57" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N57" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O57" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5254,80 +5254,78 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C58" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D58" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E58" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H58" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I58" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J58" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K58" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L58" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M58" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N58" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O58" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5338,13 +5336,15 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5352,64 +5352,60 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C59" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D59" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E59" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F59" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H59" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I59" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J59" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K59" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M59" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N59" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O59" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5420,9 +5416,9 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="11" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
@@ -5430,13 +5426,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U59" s="8" t="n">
-        <v/>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5446,149 +5444,151 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C60" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D60" t="n">
-        <v>101.21</v>
+        <v>100.97</v>
       </c>
       <c r="E60" t="n">
-        <v>105.83</v>
+        <v>102.43</v>
       </c>
       <c r="F60" t="n">
-        <v>4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0321</v>
       </c>
       <c r="H60" t="n">
-        <v>5.54</v>
+        <v>4.66</v>
       </c>
       <c r="I60" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J60" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K60" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L60" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M60" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N60" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O60" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="11" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
+      <c r="Q60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U60" s="8" t="inlineStr">
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>105.48</v>
+        <v>102.18</v>
       </c>
       <c r="C61" t="n">
-        <v>105.63</v>
+        <v>102.47</v>
       </c>
       <c r="D61" t="n">
-        <v>100.97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>102.43</v>
+        <v>101.91</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.4</v>
+        <v>-0.52</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0051</v>
       </c>
       <c r="H61" t="n">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="I61" t="n">
-        <v>95.67</v>
+        <v>96.31</v>
       </c>
       <c r="J61" t="n">
-        <v>101.22</v>
+        <v>97.34</v>
       </c>
       <c r="K61" t="n">
-        <v>103.06</v>
+        <v>100.1</v>
       </c>
       <c r="L61" t="n">
-        <v>104.91</v>
+        <v>102.86</v>
       </c>
       <c r="M61" t="n">
-        <v>108.6</v>
+        <v>104.76</v>
       </c>
       <c r="N61" t="n">
-        <v>112.3</v>
+        <v>106.65</v>
       </c>
       <c r="O61" t="n">
-        <v>112.29</v>
+        <v>110.29</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5600,7 +5600,7 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5614,50 +5614,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>101.06</v>
       </c>
       <c r="C62" t="n">
-        <v>101.33</v>
+        <v>103.48</v>
       </c>
       <c r="D62" t="n">
-        <v>100.76</v>
+        <v>99.19</v>
       </c>
       <c r="E62" t="n">
-        <v>100.89</v>
+        <v>100.3</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.54</v>
+        <v>-1.61</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.015</v>
+        <v>-0.0158</v>
       </c>
       <c r="H62" t="n">
-        <v>0.57</v>
+        <v>4.29</v>
       </c>
       <c r="I62" t="n">
-        <v>96.31</v>
+        <v>95.73</v>
       </c>
       <c r="J62" t="n">
-        <v>97.34</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>100.1</v>
+        <v>100.23</v>
       </c>
       <c r="L62" t="n">
-        <v>102.86</v>
+        <v>101.35</v>
       </c>
       <c r="M62" t="n">
-        <v>104.76</v>
+        <v>103.6</v>
       </c>
       <c r="N62" t="n">
-        <v>106.65</v>
+        <v>105.84</v>
       </c>
       <c r="O62" t="n">
-        <v>110.29</v>
+        <v>105.84</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5684,12 +5684,98 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>96.75</v>
+      </c>
+      <c r="C63" t="n">
+        <v>97.22</v>
+      </c>
+      <c r="D63" t="n">
+        <v>96.67</v>
+      </c>
+      <c r="E63" t="n">
+        <v>96.08</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-4.22</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0421</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="I63" t="n">
+        <v>94.90000000000001</v>
+      </c>
+      <c r="J63" t="n">
+        <v>95.48999999999999</v>
+      </c>
+      <c r="K63" t="n">
+        <v>98.16</v>
+      </c>
+      <c r="L63" t="n">
+        <v>100.82</v>
+      </c>
+      <c r="M63" t="n">
+        <v>102.45</v>
+      </c>
+      <c r="N63" t="n">
+        <v>104.07</v>
+      </c>
+      <c r="O63" t="n">
+        <v>107.77</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,74 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>73.13</v>
+        <v>69.95</v>
       </c>
       <c r="C2" t="n">
-        <v>73.18000000000001</v>
+        <v>72.5</v>
       </c>
       <c r="D2" t="n">
-        <v>69.63</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>70.34</v>
+        <v>71.92</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.87</v>
+        <v>1.58</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0392</v>
+        <v>0.0225</v>
       </c>
       <c r="H2" t="n">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I2" t="n">
-        <v>70.51000000000001</v>
+        <v>66.08</v>
       </c>
       <c r="J2" t="n">
-        <v>71.11</v>
+        <v>66.26000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>72.23</v>
+        <v>68.56</v>
       </c>
       <c r="L2" t="n">
-        <v>73.34</v>
+        <v>70.87</v>
       </c>
       <c r="M2" t="n">
-        <v>74.19</v>
+        <v>72.11</v>
       </c>
       <c r="N2" t="n">
-        <v>75.05</v>
+        <v>73.36</v>
       </c>
       <c r="O2" t="n">
-        <v>76.42</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>76.73</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -710,77 +706,83 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.95</v>
+        <v>71.44</v>
       </c>
       <c r="C3" t="n">
-        <v>72.5</v>
+        <v>71.86</v>
       </c>
       <c r="D3" t="n">
-        <v>68.90000000000001</v>
+        <v>68.56</v>
       </c>
       <c r="E3" t="n">
-        <v>71.92</v>
+        <v>69.23</v>
       </c>
       <c r="F3" t="n">
-        <v>1.58</v>
+        <v>-2.69</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0225</v>
+        <v>-0.0374</v>
       </c>
       <c r="H3" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="I3" t="n">
-        <v>66.08</v>
+        <v>65.3</v>
       </c>
       <c r="J3" t="n">
-        <v>66.26000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>68.56</v>
+        <v>70.12</v>
       </c>
       <c r="L3" t="n">
-        <v>70.87</v>
+        <v>71.31</v>
       </c>
       <c r="M3" t="n">
-        <v>72.11</v>
+        <v>73.72</v>
       </c>
       <c r="N3" t="n">
-        <v>73.36</v>
+        <v>76.13</v>
       </c>
       <c r="O3" t="n">
-        <v>76.73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -790,84 +792,82 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71.44</v>
+        <v>70.5</v>
       </c>
       <c r="C4" t="n">
-        <v>71.86</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>68.56</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>69.23</v>
+        <v>70.75</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.69</v>
+        <v>1.52</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0374</v>
+        <v>0.022</v>
       </c>
       <c r="H4" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="I4" t="n">
-        <v>65.3</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>68.93000000000001</v>
+        <v>65.44</v>
       </c>
       <c r="K4" t="n">
-        <v>70.12</v>
+        <v>67.58</v>
       </c>
       <c r="L4" t="n">
-        <v>71.31</v>
+        <v>69.72</v>
       </c>
       <c r="M4" t="n">
-        <v>73.72</v>
+        <v>70.88</v>
       </c>
       <c r="N4" t="n">
-        <v>76.13</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>76.09999999999999</v>
+        <v>75.16</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -876,77 +876,83 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.5</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>71.15000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>69.31999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="E5" t="n">
-        <v>70.75</v>
+        <v>69.5</v>
       </c>
       <c r="F5" t="n">
-        <v>1.52</v>
+        <v>-1.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.022</v>
+        <v>-0.0177</v>
       </c>
       <c r="H5" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="I5" t="n">
-        <v>65.26000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>65.44</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>67.58</v>
+        <v>69.83</v>
       </c>
       <c r="L5" t="n">
-        <v>69.72</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>70.88</v>
+        <v>71.67</v>
       </c>
       <c r="N5" t="n">
-        <v>72.04000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="O5" t="n">
-        <v>75.16</v>
+        <v>72.98</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -956,7 +962,7 @@
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -968,65 +974,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>70.43000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="C6" t="n">
-        <v>71.59999999999999</v>
+        <v>70.19</v>
       </c>
       <c r="D6" t="n">
-        <v>69.22</v>
+        <v>67.92</v>
       </c>
       <c r="E6" t="n">
-        <v>69.5</v>
+        <v>68.58</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0132</v>
       </c>
       <c r="H6" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="I6" t="n">
-        <v>67.48999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="J6" t="n">
-        <v>69.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="K6" t="n">
-        <v>69.83</v>
+        <v>68.31</v>
       </c>
       <c r="L6" t="n">
-        <v>70.48999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="M6" t="n">
-        <v>71.67</v>
+        <v>70.69</v>
       </c>
       <c r="N6" t="n">
-        <v>72.84</v>
+        <v>71.42</v>
       </c>
       <c r="O6" t="n">
-        <v>72.98</v>
+        <v>73.98</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1042,62 +1046,62 @@
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>69.98</v>
+        <v>68.03</v>
       </c>
       <c r="C7" t="n">
-        <v>70.19</v>
+        <v>68.8</v>
       </c>
       <c r="D7" t="n">
-        <v>67.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>68.58</v>
+        <v>68.69</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.0016</v>
       </c>
       <c r="H7" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="I7" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>66.67</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>68.31</v>
+        <v>67.44</v>
       </c>
       <c r="L7" t="n">
-        <v>69.95</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>70.69</v>
+        <v>69.72</v>
       </c>
       <c r="N7" t="n">
-        <v>71.42</v>
+        <v>70.61</v>
       </c>
       <c r="O7" t="n">
-        <v>73.98</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,12 +1111,12 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1126,58 +1130,62 @@
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D8" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E8" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F8" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H8" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I8" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J8" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L8" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M8" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O8" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,14 +1193,12 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="n">
+        <v/>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1206,7 +1212,7 @@
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -1218,50 +1224,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C9" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E9" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H9" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I9" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L9" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M9" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N9" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,78 +1278,80 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C10" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D10" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E10" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F10" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H10" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I10" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L10" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N10" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,7 +1362,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1366,15 +1374,13 @@
       </c>
       <c r="U10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="V10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1384,50 +1390,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C11" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D11" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E11" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F11" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H11" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I11" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J11" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M11" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1435,81 +1441,83 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C12" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D12" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E12" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I12" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K12" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L12" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N12" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O12" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1522,7 +1530,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1536,7 +1544,7 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1550,50 +1558,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C13" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D13" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E13" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I13" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J13" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L13" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M13" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N13" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O13" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1601,83 +1609,83 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D14" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E14" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F14" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H14" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I14" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J14" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K14" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M14" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N14" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O14" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1688,27 +1696,23 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1718,50 +1722,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E15" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H15" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I15" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J15" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K15" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L15" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M15" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N15" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O15" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1772,15 +1776,13 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1788,60 +1790,64 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C16" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D16" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E16" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F16" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I16" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J16" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K16" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L16" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M16" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N16" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O16" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1854,7 +1860,7 @@
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1866,64 +1872,64 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E17" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H17" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I17" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K17" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L17" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M17" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N17" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1936,76 +1942,78 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W17" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D18" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E18" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F18" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I18" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J18" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L18" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M18" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N18" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2013,30 +2021,28 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2046,50 +2052,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C19" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D19" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E19" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F19" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H19" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I19" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K19" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L19" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M19" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O19" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2097,12 +2103,10 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2118,7 +2122,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2128,50 +2132,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C20" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D20" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E20" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F20" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H20" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I20" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J20" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K20" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L20" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M20" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N20" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2182,7 +2186,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2198,7 +2202,7 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2208,50 +2212,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C21" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D21" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F21" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H21" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I21" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J21" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K21" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L21" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N21" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2262,23 +2266,27 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2288,50 +2296,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C22" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D22" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F22" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H22" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I22" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J22" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M22" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N22" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2339,96 +2347,100 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C23" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D23" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E23" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H23" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I23" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J23" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K23" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L23" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M23" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N23" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2444,79 +2456,71 @@
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C24" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E24" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H24" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I24" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J24" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K24" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L24" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O24" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2530,7 +2534,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2540,50 +2544,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E25" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H25" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I25" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J25" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K25" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L25" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N25" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2591,28 +2595,30 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2620,50 +2626,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C26" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D26" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E26" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F26" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H26" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I26" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J26" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K26" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L26" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N26" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O26" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2676,76 +2682,76 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C27" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D27" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E27" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H27" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I27" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J27" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K27" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M27" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O27" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2753,24 +2759,30 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2784,56 +2796,58 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D28" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F28" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H28" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I28" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J28" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N28" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O28" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
@@ -2842,87 +2856,85 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D29" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E29" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H29" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I29" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J29" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N29" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O29" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q29" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
@@ -2930,13 +2942,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2946,87 +2960,79 @@
       </c>
       <c r="W29" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C30" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D30" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F30" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H30" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I30" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J30" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L30" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N30" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3034,64 +3040,60 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C31" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H31" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I31" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J31" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K31" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M31" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N31" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O31" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3104,72 +3106,80 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C32" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D32" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E32" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H32" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I32" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J32" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K32" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M32" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O32" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3180,25 +3190,23 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3212,50 +3220,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C33" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D33" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F33" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H33" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I33" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L33" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M33" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N33" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3266,80 +3274,80 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V33" s="8" t="n">
-        <v/>
-      </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D34" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E34" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F34" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H34" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I34" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J34" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K34" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L34" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M34" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N34" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3350,27 +3358,23 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3380,50 +3384,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F35" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H35" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I35" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L35" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N35" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O35" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3434,15 +3438,13 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3450,73 +3452,83 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C36" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D36" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E36" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F36" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H36" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I36" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J36" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K36" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O36" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>86.3</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3530,146 +3542,142 @@
       </c>
       <c r="W36" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C37" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H37" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I37" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J37" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L37" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M37" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N37" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N37" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O37" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C38" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E38" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F38" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H38" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I38" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M38" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N38" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3680,80 +3688,82 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
+      <c r="S38" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C39" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D39" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F39" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H39" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I39" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J39" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L39" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M39" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N39" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O39" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3764,25 +3774,21 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3796,50 +3802,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C40" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D40" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F40" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H40" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I40" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J40" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K40" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N40" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3850,78 +3856,82 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C41" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D41" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E41" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F41" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H41" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I41" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J41" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K41" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N41" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3932,7 +3942,7 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3950,64 +3960,64 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C42" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D42" t="n">
         <v>85.8</v>
       </c>
-      <c r="C42" t="n">
-        <v>89</v>
-      </c>
-      <c r="D42" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E42" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F42" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I42" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J42" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K42" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L42" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N42" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O42" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4015,100 +4025,100 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C43" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E43" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H43" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I43" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J43" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K43" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L43" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M43" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N43" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O43" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4120,71 +4130,69 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C44" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D44" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E44" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H44" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I44" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L44" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N44" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
@@ -4192,7 +4200,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="7" t="inlineStr">
+      <c r="S44" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4206,7 +4214,7 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4216,69 +4224,63 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C45" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D45" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E45" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H45" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I45" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J45" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K45" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L45" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M45" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N45" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O45" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>91.45</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4290,7 +4292,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4300,50 +4302,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C46" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D46" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H46" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I46" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K46" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L46" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N46" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O46" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4356,11 +4358,13 @@
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4368,60 +4372,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C47" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D47" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E47" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H47" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I47" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J47" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K47" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L47" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N47" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4432,15 +4440,13 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4448,64 +4454,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C48" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E48" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H48" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I48" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J48" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K48" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L48" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N48" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O48" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4516,78 +4522,80 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C49" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D49" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E49" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F49" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H49" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I49" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L49" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M49" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4598,7 +4606,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4618,7 +4626,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4628,50 +4636,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E50" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F50" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H50" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I50" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L50" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M50" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N50" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O50" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4682,27 +4690,21 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4712,50 +4714,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C51" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D51" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F51" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H51" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I51" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K51" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N51" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O51" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4766,13 +4768,15 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4780,7 +4784,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4790,50 +4794,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C52" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D52" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E52" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F52" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H52" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I52" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J52" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K52" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L52" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M52" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N52" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O52" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4841,18 +4845,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4860,60 +4864,64 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D53" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E53" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F53" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H53" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I53" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J53" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K53" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O53" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4921,18 +4929,18 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4940,64 +4948,60 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C54" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D54" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E54" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F54" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H54" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I54" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K54" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M54" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O54" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5008,23 +5012,25 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5034,50 +5040,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C55" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D55" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E55" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F55" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H55" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I55" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J55" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K55" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L55" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M55" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N55" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O55" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5088,7 +5094,7 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5100,13 +5106,15 @@
       </c>
       <c r="U55" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5116,50 +5124,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C56" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D56" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E56" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F56" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H56" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I56" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J56" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K56" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M56" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N56" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O56" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5172,78 +5180,76 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W56" s="11" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C57" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D57" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E57" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H57" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I57" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J57" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K57" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L57" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M57" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N57" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O57" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5256,11 +5262,13 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5268,64 +5276,60 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C58" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D58" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E58" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F58" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H58" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I58" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J58" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K58" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L58" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M58" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N58" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O58" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5336,9 +5340,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5346,13 +5350,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5362,149 +5368,151 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C59" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D59" t="n">
-        <v>101.21</v>
+        <v>100.97</v>
       </c>
       <c r="E59" t="n">
-        <v>105.83</v>
+        <v>102.43</v>
       </c>
       <c r="F59" t="n">
-        <v>4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0321</v>
       </c>
       <c r="H59" t="n">
-        <v>5.54</v>
+        <v>4.66</v>
       </c>
       <c r="I59" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J59" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K59" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L59" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M59" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N59" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O59" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>105.48</v>
+        <v>102.18</v>
       </c>
       <c r="C60" t="n">
-        <v>105.63</v>
+        <v>102.47</v>
       </c>
       <c r="D60" t="n">
-        <v>100.97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>102.43</v>
+        <v>101.91</v>
       </c>
       <c r="F60" t="n">
-        <v>-3.4</v>
+        <v>-0.52</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0051</v>
       </c>
       <c r="H60" t="n">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="I60" t="n">
-        <v>95.67</v>
+        <v>96.31</v>
       </c>
       <c r="J60" t="n">
-        <v>101.22</v>
+        <v>97.34</v>
       </c>
       <c r="K60" t="n">
-        <v>103.06</v>
+        <v>100.1</v>
       </c>
       <c r="L60" t="n">
-        <v>104.91</v>
+        <v>102.86</v>
       </c>
       <c r="M60" t="n">
-        <v>108.6</v>
+        <v>104.76</v>
       </c>
       <c r="N60" t="n">
-        <v>112.3</v>
+        <v>106.65</v>
       </c>
       <c r="O60" t="n">
-        <v>112.29</v>
+        <v>110.29</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5516,7 +5524,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5530,50 +5538,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>102.18</v>
+        <v>101.06</v>
       </c>
       <c r="C61" t="n">
-        <v>102.47</v>
+        <v>103.48</v>
       </c>
       <c r="D61" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E61" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F61" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G61" s="5" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I61" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="J61" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E61" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="F61" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="G61" s="5" t="n">
-        <v>-0.0051</v>
-      </c>
-      <c r="H61" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="I61" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="J61" t="n">
-        <v>97.34</v>
-      </c>
       <c r="K61" t="n">
-        <v>100.1</v>
+        <v>100.23</v>
       </c>
       <c r="L61" t="n">
-        <v>102.86</v>
+        <v>101.35</v>
       </c>
       <c r="M61" t="n">
-        <v>104.76</v>
+        <v>103.6</v>
       </c>
       <c r="N61" t="n">
-        <v>106.65</v>
+        <v>105.84</v>
       </c>
       <c r="O61" t="n">
-        <v>110.29</v>
+        <v>105.84</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5583,12 +5591,12 @@
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5600,77 +5608,81 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>101.06</v>
+        <v>91.95</v>
       </c>
       <c r="C62" t="n">
-        <v>103.48</v>
+        <v>92.04000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>99.19</v>
+        <v>91.79000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>100.3</v>
+        <v>91.8</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.61</v>
+        <v>-8.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0158</v>
+        <v>-0.0847</v>
       </c>
       <c r="H62" t="n">
-        <v>4.29</v>
+        <v>0.25</v>
       </c>
       <c r="I62" t="n">
-        <v>95.73</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>99.09999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="K62" t="n">
-        <v>100.23</v>
+        <v>98.16</v>
       </c>
       <c r="L62" t="n">
-        <v>101.35</v>
+        <v>100.82</v>
       </c>
       <c r="M62" t="n">
-        <v>103.6</v>
+        <v>102.45</v>
       </c>
       <c r="N62" t="n">
-        <v>105.84</v>
+        <v>104.07</v>
       </c>
       <c r="O62" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
+        <v>107.77</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5686,100 +5698,10 @@
       </c>
       <c r="W62" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>96.75</v>
-      </c>
-      <c r="C63" t="n">
-        <v>97.22</v>
-      </c>
-      <c r="D63" t="n">
-        <v>96.67</v>
-      </c>
-      <c r="E63" t="n">
-        <v>96.08</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-4.22</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0421</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.55</v>
-      </c>
-      <c r="I63" t="n">
-        <v>94.90000000000001</v>
-      </c>
-      <c r="J63" t="n">
-        <v>95.48999999999999</v>
-      </c>
-      <c r="K63" t="n">
-        <v>98.16</v>
-      </c>
-      <c r="L63" t="n">
-        <v>100.82</v>
-      </c>
-      <c r="M63" t="n">
-        <v>102.45</v>
-      </c>
-      <c r="N63" t="n">
-        <v>104.07</v>
-      </c>
-      <c r="O63" t="n">
-        <v>107.77</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="11" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5626,25 +5626,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>91.95</v>
+        <v>101</v>
       </c>
       <c r="C62" t="n">
-        <v>92.04000000000001</v>
+        <v>101.08</v>
       </c>
       <c r="D62" t="n">
-        <v>91.79000000000001</v>
+        <v>94.22</v>
       </c>
       <c r="E62" t="n">
-        <v>91.8</v>
+        <v>95.78</v>
       </c>
       <c r="F62" t="n">
-        <v>-8.5</v>
+        <v>-4.52</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0847</v>
+        <v>-0.0451</v>
       </c>
       <c r="H62" t="n">
-        <v>0.25</v>
+        <v>6.86</v>
       </c>
       <c r="I62" t="n">
         <v>94.90000000000001</v>
@@ -5669,19 +5669,19 @@
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5696,12 +5696,100 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>91.95</v>
+      </c>
+      <c r="C63" t="n">
+        <v>93.84</v>
+      </c>
+      <c r="D63" t="n">
+        <v>89.16</v>
+      </c>
+      <c r="E63" t="n">
+        <v>90.51000000000001</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-5.27</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.055</v>
+      </c>
+      <c r="H63" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="I63" t="n">
+        <v>87.36</v>
+      </c>
+      <c r="J63" t="n">
+        <v>87.98</v>
+      </c>
+      <c r="K63" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="L63" t="n">
+        <v>96.72</v>
+      </c>
+      <c r="M63" t="n">
+        <v>99.20999999999999</v>
+      </c>
+      <c r="N63" t="n">
+        <v>101.7</v>
+      </c>
+      <c r="O63" t="n">
+        <v>107.94</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5723,13 +5723,13 @@
         <v>89.16</v>
       </c>
       <c r="E63" t="n">
-        <v>90.51000000000001</v>
+        <v>91.27</v>
       </c>
       <c r="F63" t="n">
-        <v>-5.27</v>
+        <v>-4.51</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>-0.055</v>
+        <v>-0.0471</v>
       </c>
       <c r="H63" t="n">
         <v>4.68</v>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,69 +634,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69.95</v>
+        <v>71.44</v>
       </c>
       <c r="C2" t="n">
-        <v>72.5</v>
+        <v>71.86</v>
       </c>
       <c r="D2" t="n">
-        <v>68.90000000000001</v>
+        <v>68.56</v>
       </c>
       <c r="E2" t="n">
-        <v>71.92</v>
+        <v>69.23</v>
       </c>
       <c r="F2" t="n">
-        <v>1.58</v>
+        <v>-2.69</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0225</v>
+        <v>-0.0374</v>
       </c>
       <c r="H2" t="n">
-        <v>3.6</v>
+        <v>3.3</v>
       </c>
       <c r="I2" t="n">
-        <v>66.08</v>
+        <v>65.3</v>
       </c>
       <c r="J2" t="n">
-        <v>66.26000000000001</v>
+        <v>68.93000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>68.56</v>
+        <v>70.12</v>
       </c>
       <c r="L2" t="n">
-        <v>70.87</v>
+        <v>71.31</v>
       </c>
       <c r="M2" t="n">
-        <v>72.11</v>
+        <v>73.72</v>
       </c>
       <c r="N2" t="n">
-        <v>73.36</v>
+        <v>76.13</v>
       </c>
       <c r="O2" t="n">
-        <v>76.73</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -711,79 +713,77 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>71.44</v>
+        <v>70.5</v>
       </c>
       <c r="C3" t="n">
-        <v>71.86</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>68.56</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>69.23</v>
+        <v>70.75</v>
       </c>
       <c r="F3" t="n">
-        <v>-2.69</v>
+        <v>1.52</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0374</v>
+        <v>0.022</v>
       </c>
       <c r="H3" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="I3" t="n">
-        <v>65.3</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>68.93000000000001</v>
+        <v>65.44</v>
       </c>
       <c r="K3" t="n">
-        <v>70.12</v>
+        <v>67.58</v>
       </c>
       <c r="L3" t="n">
-        <v>71.31</v>
+        <v>69.72</v>
       </c>
       <c r="M3" t="n">
-        <v>73.72</v>
+        <v>70.88</v>
       </c>
       <c r="N3" t="n">
-        <v>76.13</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>76.09999999999999</v>
+        <v>75.16</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -797,76 +797,78 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.5</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>71.15000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>69.31999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="E4" t="n">
-        <v>70.75</v>
+        <v>69.5</v>
       </c>
       <c r="F4" t="n">
-        <v>1.52</v>
+        <v>-1.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.022</v>
+        <v>-0.0177</v>
       </c>
       <c r="H4" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="I4" t="n">
-        <v>65.26000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>65.44</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>67.58</v>
+        <v>69.83</v>
       </c>
       <c r="L4" t="n">
-        <v>69.72</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>70.88</v>
+        <v>71.67</v>
       </c>
       <c r="N4" t="n">
-        <v>72.04000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="O4" t="n">
-        <v>75.16</v>
+        <v>72.98</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -881,72 +883,70 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>70.43000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="C5" t="n">
-        <v>71.59999999999999</v>
+        <v>70.19</v>
       </c>
       <c r="D5" t="n">
-        <v>69.22</v>
+        <v>67.92</v>
       </c>
       <c r="E5" t="n">
-        <v>69.5</v>
+        <v>68.58</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0132</v>
       </c>
       <c r="H5" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="I5" t="n">
-        <v>67.48999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="J5" t="n">
-        <v>69.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="K5" t="n">
-        <v>69.83</v>
+        <v>68.31</v>
       </c>
       <c r="L5" t="n">
-        <v>70.48999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="M5" t="n">
-        <v>71.67</v>
+        <v>70.69</v>
       </c>
       <c r="N5" t="n">
-        <v>72.84</v>
+        <v>71.42</v>
       </c>
       <c r="O5" t="n">
-        <v>72.98</v>
+        <v>73.98</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -967,57 +967,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>69.98</v>
+        <v>68.03</v>
       </c>
       <c r="C6" t="n">
-        <v>70.19</v>
+        <v>68.8</v>
       </c>
       <c r="D6" t="n">
-        <v>67.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>68.58</v>
+        <v>68.69</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.0016</v>
       </c>
       <c r="H6" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="I6" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>66.67</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>68.31</v>
+        <v>67.44</v>
       </c>
       <c r="L6" t="n">
-        <v>69.95</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>70.69</v>
+        <v>69.72</v>
       </c>
       <c r="N6" t="n">
-        <v>71.42</v>
+        <v>70.61</v>
       </c>
       <c r="O6" t="n">
-        <v>73.98</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1027,12 +1027,12 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1051,57 +1051,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D7" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F7" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H7" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I7" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J7" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L7" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M7" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O7" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1109,14 +1109,12 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1135,57 +1133,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C8" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E8" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H8" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I8" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L8" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M8" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N8" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1196,78 +1194,80 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C9" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D9" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E9" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F9" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H9" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I9" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L9" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N9" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1278,7 +1278,7 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1290,13 +1290,11 @@
       </c>
       <c r="U9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1308,50 +1306,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C10" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D10" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E10" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F10" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H10" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I10" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J10" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L10" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M10" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1359,23 +1357,21 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
@@ -1385,55 +1381,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C11" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D11" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E11" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I11" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K11" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L11" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N11" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O11" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1446,7 +1446,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="10" t="inlineStr">
+      <c r="S11" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1474,50 +1474,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C12" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D12" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E12" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I12" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J12" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L12" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M12" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N12" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O12" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,83 +1525,83 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
-      </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D13" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E13" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F13" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H13" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I13" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J13" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K13" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M13" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N13" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O13" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1612,25 +1612,21 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1642,50 +1638,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E14" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H14" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I14" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J14" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K14" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L14" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M14" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N14" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O14" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1696,15 +1692,13 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1717,55 +1711,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C15" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D15" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E15" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F15" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H15" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I15" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J15" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K15" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L15" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M15" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N15" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O15" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1778,7 +1776,7 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1797,57 +1795,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C16" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E16" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H16" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I16" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K16" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L16" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M16" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N16" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,76 +1858,78 @@
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D17" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E17" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F17" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I17" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J17" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L17" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M17" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N17" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,28 +1937,26 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1970,50 +1968,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C18" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D18" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E18" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F18" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H18" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I18" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K18" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L18" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M18" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O18" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2021,12 +2019,10 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2052,50 +2048,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C19" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D19" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E19" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F19" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H19" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I19" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J19" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K19" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L19" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M19" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N19" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,7 +2102,7 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2132,50 +2128,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C20" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D20" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F20" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H20" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I20" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J20" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K20" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L20" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N20" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2186,21 +2182,25 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2212,50 +2212,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C21" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D21" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F21" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H21" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I21" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J21" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M21" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N21" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2263,96 +2263,100 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C22" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D22" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E22" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H22" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I22" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J22" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K22" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L22" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M22" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N22" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2366,81 +2370,73 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C23" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E23" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H23" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I23" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J23" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K23" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L23" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O23" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2464,50 +2460,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D24" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E24" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H24" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I24" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J24" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K24" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L24" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N24" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2515,28 +2511,30 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2544,50 +2542,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C25" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D25" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E25" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F25" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H25" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I25" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J25" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K25" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L25" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N25" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O25" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2600,18 +2598,14 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2621,55 +2615,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C26" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D26" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E26" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H26" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I26" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J26" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K26" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M26" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O26" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2677,19 +2675,25 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2708,56 +2712,58 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D27" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F27" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H27" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I27" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J27" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N27" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O27" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
@@ -2766,18 +2772,14 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2789,64 +2791,66 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D28" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E28" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H28" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I28" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J28" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N28" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O28" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q28" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
@@ -2854,13 +2858,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2868,89 +2874,81 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C29" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D29" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F29" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H29" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I29" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J29" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L29" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N29" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2963,59 +2961,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C30" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H30" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I30" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J30" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K30" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M30" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N30" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O30" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3028,14 +3022,18 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3045,55 +3043,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C31" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D31" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E31" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H31" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I31" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J31" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K31" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M31" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O31" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3104,20 +3106,18 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3136,50 +3136,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C32" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D32" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F32" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H32" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I32" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L32" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M32" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N32" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3190,80 +3190,80 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W32" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W32" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D33" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E33" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F33" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H33" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I33" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J33" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K33" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L33" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M33" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N33" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3274,25 +3274,21 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
+      <c r="S33" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3304,50 +3300,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F34" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H34" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I34" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L34" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N34" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O34" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3358,15 +3354,13 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3379,68 +3373,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C35" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D35" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E35" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F35" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H35" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I35" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J35" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K35" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O35" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+        <v>86.3</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3452,88 +3456,80 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C36" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H36" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I36" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J36" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L36" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M36" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N36" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N36" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O36" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3545,55 +3541,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C37" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E37" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F37" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H37" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I37" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K37" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M37" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3604,19 +3604,21 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
+      <c r="S37" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3627,57 +3629,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C38" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D38" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F38" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H38" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I38" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J38" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L38" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M38" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N38" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O38" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3688,20 +3690,16 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3720,50 +3718,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C39" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D39" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F39" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H39" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I39" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J39" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K39" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N39" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3774,16 +3772,20 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3795,57 +3797,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C40" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D40" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E40" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F40" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H40" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I40" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J40" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K40" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N40" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3856,7 +3858,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3881,57 +3883,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C41" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D41" t="n">
         <v>85.8</v>
       </c>
-      <c r="C41" t="n">
-        <v>89</v>
-      </c>
-      <c r="D41" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E41" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F41" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I41" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J41" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K41" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L41" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N41" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O41" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3939,23 +3941,21 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3967,72 +3967,74 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C42" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E42" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H42" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I42" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J42" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K42" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L42" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M42" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N42" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O42" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4049,66 +4051,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C43" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D43" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E43" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H43" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I43" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L43" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N43" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
@@ -4116,7 +4116,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4140,69 +4140,63 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C44" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D44" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E44" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H44" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I44" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J44" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K44" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L44" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M44" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N44" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O44" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>91.45</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4224,50 +4218,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C45" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D45" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H45" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I45" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K45" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L45" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N45" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O45" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4280,11 +4274,13 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4297,55 +4293,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C46" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D46" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E46" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H46" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I46" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J46" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K46" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L46" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N46" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4356,15 +4356,13 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4379,57 +4377,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C47" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E47" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H47" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I47" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J47" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K47" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L47" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N47" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O47" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4440,78 +4438,80 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C48" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D48" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E48" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F48" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H48" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I48" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L48" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M48" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4522,7 +4522,7 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4552,50 +4552,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E49" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F49" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H49" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I49" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L49" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M49" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N49" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O49" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4606,25 +4606,19 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
@@ -4636,50 +4630,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C50" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D50" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E50" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F50" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H50" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I50" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K50" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N50" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O50" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4690,13 +4684,15 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
+      <c r="S50" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4714,50 +4710,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C51" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D51" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E51" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F51" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H51" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I51" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J51" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K51" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L51" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M51" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N51" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O51" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4765,18 +4761,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4789,55 +4785,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D52" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E52" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F52" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H52" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I52" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J52" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K52" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O52" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4845,18 +4845,18 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4869,59 +4869,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C53" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D53" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E53" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F53" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H53" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I53" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J53" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K53" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M53" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O53" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4932,18 +4928,20 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4958,50 +4956,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C54" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D54" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E54" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F54" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H54" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I54" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J54" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K54" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L54" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M54" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N54" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5012,7 +5010,7 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5024,11 +5022,13 @@
       </c>
       <c r="U54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
@@ -5040,50 +5040,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C55" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D55" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E55" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F55" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H55" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I55" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J55" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K55" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M55" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N55" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O55" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5096,78 +5096,76 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C56" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D56" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E56" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H56" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I56" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J56" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K56" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L56" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M56" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N56" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O56" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5180,11 +5178,13 @@
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5197,59 +5197,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C57" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D57" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E57" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F57" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H57" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I57" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J57" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K57" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M57" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N57" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O57" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5260,9 +5256,9 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
@@ -5270,8 +5266,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5286,74 +5284,74 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C58" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D58" t="n">
-        <v>101.21</v>
+        <v>100.97</v>
       </c>
       <c r="E58" t="n">
-        <v>105.83</v>
+        <v>102.43</v>
       </c>
       <c r="F58" t="n">
-        <v>4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0321</v>
       </c>
       <c r="H58" t="n">
-        <v>5.54</v>
+        <v>4.66</v>
       </c>
       <c r="I58" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J58" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K58" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L58" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M58" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N58" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O58" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5363,72 +5361,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>105.48</v>
+        <v>102.18</v>
       </c>
       <c r="C59" t="n">
-        <v>105.63</v>
+        <v>102.47</v>
       </c>
       <c r="D59" t="n">
-        <v>100.97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>102.43</v>
+        <v>101.91</v>
       </c>
       <c r="F59" t="n">
-        <v>-3.4</v>
+        <v>-0.52</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0051</v>
       </c>
       <c r="H59" t="n">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="I59" t="n">
-        <v>95.67</v>
+        <v>96.31</v>
       </c>
       <c r="J59" t="n">
-        <v>101.22</v>
+        <v>97.34</v>
       </c>
       <c r="K59" t="n">
-        <v>103.06</v>
+        <v>100.1</v>
       </c>
       <c r="L59" t="n">
-        <v>104.91</v>
+        <v>102.86</v>
       </c>
       <c r="M59" t="n">
-        <v>108.6</v>
+        <v>104.76</v>
       </c>
       <c r="N59" t="n">
-        <v>112.3</v>
+        <v>106.65</v>
       </c>
       <c r="O59" t="n">
-        <v>112.29</v>
+        <v>110.29</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5454,50 +5454,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>102.18</v>
+        <v>101.06</v>
       </c>
       <c r="C60" t="n">
-        <v>102.47</v>
+        <v>103.48</v>
       </c>
       <c r="D60" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E60" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F60" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="H60" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I60" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="J60" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E60" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="F60" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="G60" s="5" t="n">
-        <v>-0.0051</v>
-      </c>
-      <c r="H60" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="I60" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="J60" t="n">
-        <v>97.34</v>
-      </c>
       <c r="K60" t="n">
-        <v>100.1</v>
+        <v>100.23</v>
       </c>
       <c r="L60" t="n">
-        <v>102.86</v>
+        <v>101.35</v>
       </c>
       <c r="M60" t="n">
-        <v>104.76</v>
+        <v>103.6</v>
       </c>
       <c r="N60" t="n">
-        <v>106.65</v>
+        <v>105.84</v>
       </c>
       <c r="O60" t="n">
-        <v>110.29</v>
+        <v>105.84</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5507,12 +5507,12 @@
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5531,70 +5531,74 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>101.06</v>
+        <v>101</v>
       </c>
       <c r="C61" t="n">
-        <v>103.48</v>
+        <v>101.08</v>
       </c>
       <c r="D61" t="n">
-        <v>99.19</v>
+        <v>94.22</v>
       </c>
       <c r="E61" t="n">
-        <v>100.3</v>
+        <v>95.78</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.61</v>
+        <v>-4.52</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0158</v>
+        <v>-0.0451</v>
       </c>
       <c r="H61" t="n">
-        <v>4.29</v>
+        <v>6.86</v>
       </c>
       <c r="I61" t="n">
-        <v>95.73</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>99.09999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="K61" t="n">
-        <v>100.23</v>
+        <v>98.16</v>
       </c>
       <c r="L61" t="n">
-        <v>101.35</v>
+        <v>100.82</v>
       </c>
       <c r="M61" t="n">
-        <v>103.6</v>
+        <v>102.45</v>
       </c>
       <c r="N61" t="n">
-        <v>105.84</v>
+        <v>104.07</v>
       </c>
       <c r="O61" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
+        <v>107.77</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5615,74 +5619,72 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>101</v>
+        <v>89.89</v>
       </c>
       <c r="C62" t="n">
-        <v>101.08</v>
+        <v>90</v>
       </c>
       <c r="D62" t="n">
-        <v>94.22</v>
+        <v>89.84</v>
       </c>
       <c r="E62" t="n">
-        <v>95.78</v>
+        <v>89.88</v>
       </c>
       <c r="F62" t="n">
-        <v>-4.52</v>
+        <v>-5.9</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0616</v>
       </c>
       <c r="H62" t="n">
-        <v>6.86</v>
+        <v>0.16</v>
       </c>
       <c r="I62" t="n">
-        <v>94.90000000000001</v>
+        <v>87.36</v>
       </c>
       <c r="J62" t="n">
-        <v>95.48999999999999</v>
+        <v>87.98</v>
       </c>
       <c r="K62" t="n">
-        <v>98.16</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>100.82</v>
+        <v>96.72</v>
       </c>
       <c r="M62" t="n">
-        <v>102.45</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="N62" t="n">
-        <v>104.07</v>
+        <v>101.7</v>
       </c>
       <c r="O62" t="n">
-        <v>107.77</v>
-      </c>
-      <c r="P62" s="6" t="inlineStr">
+        <v>107.94</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5702,90 +5704,6 @@
         </is>
       </c>
       <c r="X62" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>91.95</v>
-      </c>
-      <c r="C63" t="n">
-        <v>93.84</v>
-      </c>
-      <c r="D63" t="n">
-        <v>89.16</v>
-      </c>
-      <c r="E63" t="n">
-        <v>91.27</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-4.51</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0471</v>
-      </c>
-      <c r="H63" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="I63" t="n">
-        <v>87.36</v>
-      </c>
-      <c r="J63" t="n">
-        <v>87.98</v>
-      </c>
-      <c r="K63" t="n">
-        <v>92.34999999999999</v>
-      </c>
-      <c r="L63" t="n">
-        <v>96.72</v>
-      </c>
-      <c r="M63" t="n">
-        <v>99.20999999999999</v>
-      </c>
-      <c r="N63" t="n">
-        <v>101.7</v>
-      </c>
-      <c r="O63" t="n">
-        <v>107.94</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5633,22 +5633,22 @@
         <v>89.89</v>
       </c>
       <c r="C62" t="n">
-        <v>90</v>
+        <v>90.38</v>
       </c>
       <c r="D62" t="n">
-        <v>89.84</v>
+        <v>89.47</v>
       </c>
       <c r="E62" t="n">
-        <v>89.88</v>
+        <v>90.2</v>
       </c>
       <c r="F62" t="n">
-        <v>-5.9</v>
+        <v>-5.58</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0616</v>
+        <v>-0.0583</v>
       </c>
       <c r="H62" t="n">
-        <v>0.16</v>
+        <v>0.91</v>
       </c>
       <c r="I62" t="n">
         <v>87.36</v>
@@ -5674,14 +5674,12 @@
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S62" s="7" t="inlineStr">

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5639,13 +5639,13 @@
         <v>89.47</v>
       </c>
       <c r="E62" t="n">
-        <v>90.2</v>
+        <v>90.22</v>
       </c>
       <c r="F62" t="n">
-        <v>-5.58</v>
+        <v>-5.56</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0583</v>
+        <v>-0.058</v>
       </c>
       <c r="H62" t="n">
         <v>0.91</v>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5639,13 +5639,13 @@
         <v>89.47</v>
       </c>
       <c r="E62" t="n">
-        <v>90.22</v>
+        <v>89.92</v>
       </c>
       <c r="F62" t="n">
-        <v>-5.56</v>
+        <v>-5.86</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.058</v>
+        <v>-0.0612</v>
       </c>
       <c r="H62" t="n">
         <v>0.91</v>
@@ -5674,12 +5674,14 @@
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R62" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S62" s="7" t="inlineStr">

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -5639,13 +5639,13 @@
         <v>89.47</v>
       </c>
       <c r="E62" t="n">
-        <v>89.92</v>
+        <v>89.70999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>-5.86</v>
+        <v>-6.07</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0612</v>
+        <v>-0.0634</v>
       </c>
       <c r="H62" t="n">
         <v>0.91</v>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5630,25 +5630,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>89.89</v>
+        <v>95.39</v>
       </c>
       <c r="C62" t="n">
-        <v>90.38</v>
+        <v>97.42</v>
       </c>
       <c r="D62" t="n">
-        <v>89.47</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>89.70999999999999</v>
+        <v>94.59</v>
       </c>
       <c r="F62" t="n">
-        <v>-6.07</v>
+        <v>-1.19</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0634</v>
+        <v>-0.0124</v>
       </c>
       <c r="H62" t="n">
-        <v>0.91</v>
+        <v>5.02</v>
       </c>
       <c r="I62" t="n">
         <v>87.36</v>
@@ -5674,36 +5674,118 @@
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>89.89</v>
+      </c>
+      <c r="C63" t="n">
+        <v>91.36</v>
+      </c>
+      <c r="D63" t="n">
+        <v>88.70999999999999</v>
+      </c>
+      <c r="E63" t="n">
+        <v>91.08</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-3.51</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0371</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="I63" t="n">
+        <v>87.38</v>
+      </c>
+      <c r="J63" t="n">
+        <v>89.41</v>
+      </c>
+      <c r="K63" t="n">
+        <v>92.08</v>
+      </c>
+      <c r="L63" t="n">
+        <v>94.75</v>
+      </c>
+      <c r="M63" t="n">
+        <v>97.09999999999999</v>
+      </c>
+      <c r="N63" t="n">
+        <v>99.45</v>
+      </c>
+      <c r="O63" t="n">
+        <v>102.44</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="S63" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
+      <c r="X63" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,72 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>71.44</v>
+        <v>70.5</v>
       </c>
       <c r="C2" t="n">
-        <v>71.86</v>
+        <v>71.15000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>68.56</v>
+        <v>69.31999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>69.23</v>
+        <v>70.75</v>
       </c>
       <c r="F2" t="n">
-        <v>-2.69</v>
+        <v>1.52</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0374</v>
+        <v>0.022</v>
       </c>
       <c r="H2" t="n">
-        <v>3.3</v>
+        <v>1.83</v>
       </c>
       <c r="I2" t="n">
-        <v>65.3</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>68.93000000000001</v>
+        <v>65.44</v>
       </c>
       <c r="K2" t="n">
-        <v>70.12</v>
+        <v>67.58</v>
       </c>
       <c r="L2" t="n">
-        <v>71.31</v>
+        <v>69.72</v>
       </c>
       <c r="M2" t="n">
-        <v>73.72</v>
+        <v>70.88</v>
       </c>
       <c r="N2" t="n">
-        <v>76.13</v>
+        <v>72.04000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>76.09999999999999</v>
+        <v>75.16</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -713,76 +711,78 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70.5</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>71.15000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>69.31999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="E3" t="n">
-        <v>70.75</v>
+        <v>69.5</v>
       </c>
       <c r="F3" t="n">
-        <v>1.52</v>
+        <v>-1.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.022</v>
+        <v>-0.0177</v>
       </c>
       <c r="H3" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="I3" t="n">
-        <v>65.26000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>65.44</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>67.58</v>
+        <v>69.83</v>
       </c>
       <c r="L3" t="n">
-        <v>69.72</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>70.88</v>
+        <v>71.67</v>
       </c>
       <c r="N3" t="n">
-        <v>72.04000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="O3" t="n">
-        <v>75.16</v>
+        <v>72.98</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -797,72 +797,70 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70.43000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="C4" t="n">
-        <v>71.59999999999999</v>
+        <v>70.19</v>
       </c>
       <c r="D4" t="n">
-        <v>69.22</v>
+        <v>67.92</v>
       </c>
       <c r="E4" t="n">
-        <v>69.5</v>
+        <v>68.58</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0132</v>
       </c>
       <c r="H4" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="I4" t="n">
-        <v>67.48999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="J4" t="n">
-        <v>69.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="K4" t="n">
-        <v>69.83</v>
+        <v>68.31</v>
       </c>
       <c r="L4" t="n">
-        <v>70.48999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="M4" t="n">
-        <v>71.67</v>
+        <v>70.69</v>
       </c>
       <c r="N4" t="n">
-        <v>72.84</v>
+        <v>71.42</v>
       </c>
       <c r="O4" t="n">
-        <v>72.98</v>
+        <v>73.98</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -883,57 +881,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>69.98</v>
+        <v>68.03</v>
       </c>
       <c r="C5" t="n">
-        <v>70.19</v>
+        <v>68.8</v>
       </c>
       <c r="D5" t="n">
-        <v>67.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E5" t="n">
-        <v>68.58</v>
+        <v>68.69</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.0016</v>
       </c>
       <c r="H5" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="I5" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>66.67</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>68.31</v>
+        <v>67.44</v>
       </c>
       <c r="L5" t="n">
-        <v>69.95</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>70.69</v>
+        <v>69.72</v>
       </c>
       <c r="N5" t="n">
-        <v>71.42</v>
+        <v>70.61</v>
       </c>
       <c r="O5" t="n">
-        <v>73.98</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -943,12 +941,12 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -967,57 +965,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D6" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F6" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H6" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I6" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J6" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L6" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M6" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O6" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,14 +1023,12 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1051,57 +1047,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C7" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E7" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H7" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I7" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K7" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L7" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M7" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N7" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1112,78 +1108,80 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C8" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D8" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E8" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F8" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H8" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I8" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L8" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N8" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1194,7 +1192,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1206,13 +1204,11 @@
       </c>
       <c r="U8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1224,50 +1220,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C9" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D9" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E9" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H9" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I9" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J9" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M9" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1275,23 +1271,21 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1301,55 +1295,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C10" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D10" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E10" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I10" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K10" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L10" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N10" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O10" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1362,7 +1360,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1390,50 +1388,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C11" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D11" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E11" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I11" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J11" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L11" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M11" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N11" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O11" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1441,83 +1439,83 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
-      </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D12" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E12" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F12" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H12" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I12" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J12" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K12" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L12" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M12" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N12" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O12" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1528,25 +1526,21 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1558,50 +1552,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E13" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H13" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I13" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J13" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K13" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L13" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M13" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N13" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O13" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1612,15 +1606,13 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1633,55 +1625,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C14" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D14" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E14" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F14" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H14" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I14" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J14" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K14" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L14" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M14" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N14" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O14" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1694,7 +1690,7 @@
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1713,57 +1709,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C15" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E15" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H15" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I15" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K15" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L15" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M15" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N15" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1776,76 +1772,78 @@
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D16" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E16" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F16" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I16" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J16" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L16" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M16" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N16" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,28 +1851,26 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1886,50 +1882,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C17" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D17" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E17" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F17" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H17" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I17" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K17" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L17" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M17" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O17" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,12 +1933,10 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1968,50 +1962,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C18" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D18" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E18" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F18" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H18" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I18" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J18" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K18" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L18" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M18" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N18" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2022,7 +2016,7 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2048,50 +2042,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C19" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D19" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F19" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H19" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I19" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J19" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K19" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L19" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N19" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2102,21 +2096,25 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2128,50 +2126,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C20" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D20" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F20" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H20" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I20" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J20" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M20" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N20" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2179,96 +2177,100 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C21" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D21" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E21" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H21" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I21" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J21" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K21" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L21" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M21" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N21" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2282,81 +2284,73 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C22" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E22" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H22" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I22" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J22" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K22" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L22" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N22" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O22" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2380,50 +2374,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D23" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E23" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H23" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I23" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J23" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K23" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L23" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N23" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2431,28 +2425,30 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2460,50 +2456,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D24" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E24" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F24" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H24" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I24" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J24" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K24" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L24" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N24" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O24" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2516,18 +2512,14 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2537,55 +2529,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C25" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D25" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E25" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H25" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I25" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J25" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K25" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M25" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O25" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2593,19 +2589,25 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2624,56 +2626,58 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D26" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F26" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H26" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I26" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J26" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N26" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O26" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
@@ -2682,18 +2686,14 @@
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2705,64 +2705,66 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D27" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E27" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H27" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I27" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J27" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N27" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O27" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q27" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
@@ -2770,13 +2772,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2784,89 +2788,81 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C28" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D28" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F28" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H28" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I28" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J28" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L28" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N28" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2879,59 +2875,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C29" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H29" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I29" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J29" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K29" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M29" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N29" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O29" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2944,14 +2936,18 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2961,55 +2957,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C30" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D30" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E30" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H30" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I30" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J30" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K30" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M30" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O30" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3020,20 +3020,18 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3052,50 +3050,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C31" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D31" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F31" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H31" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I31" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L31" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M31" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N31" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3106,80 +3104,80 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W31" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D32" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E32" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F32" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H32" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I32" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J32" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K32" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L32" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M32" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N32" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3190,25 +3188,21 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3220,50 +3214,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F33" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H33" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I33" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L33" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N33" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O33" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3274,15 +3268,13 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3295,68 +3287,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C34" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D34" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E34" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F34" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H34" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I34" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J34" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K34" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O34" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+        <v>86.3</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3368,88 +3370,80 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C35" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H35" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I35" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J35" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L35" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M35" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N35" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N35" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O35" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3461,55 +3455,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C36" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E36" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F36" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H36" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I36" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M36" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3520,19 +3518,21 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3543,57 +3543,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C37" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D37" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F37" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H37" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I37" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J37" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L37" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M37" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N37" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O37" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3604,20 +3604,16 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3636,50 +3632,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C38" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D38" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F38" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H38" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I38" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J38" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K38" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N38" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3690,16 +3686,20 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
@@ -3711,57 +3711,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C39" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D39" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E39" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F39" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H39" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I39" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J39" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K39" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N39" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3772,7 +3772,7 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
+      <c r="S39" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3797,57 +3797,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C40" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D40" t="n">
         <v>85.8</v>
       </c>
-      <c r="C40" t="n">
-        <v>89</v>
-      </c>
-      <c r="D40" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E40" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F40" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H40" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I40" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J40" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K40" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L40" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N40" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O40" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3855,23 +3855,21 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3883,72 +3881,74 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C41" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E41" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H41" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I41" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J41" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K41" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L41" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M41" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N41" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O41" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3965,66 +3965,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C42" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D42" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E42" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H42" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I42" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L42" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N42" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
@@ -4032,7 +4030,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4056,69 +4054,63 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C43" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D43" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E43" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H43" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I43" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J43" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K43" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L43" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M43" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N43" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O43" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>91.45</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4140,50 +4132,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C44" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D44" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E44" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H44" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I44" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K44" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L44" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N44" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O44" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4196,11 +4188,13 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4213,55 +4207,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C45" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D45" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E45" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H45" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I45" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J45" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K45" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L45" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N45" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4272,15 +4270,13 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4295,57 +4291,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C46" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E46" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H46" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I46" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J46" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K46" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L46" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N46" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O46" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4356,78 +4352,80 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C47" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D47" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E47" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F47" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H47" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I47" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L47" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M47" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4438,7 +4436,7 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
+      <c r="S47" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4468,50 +4466,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E48" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F48" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H48" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I48" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K48" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L48" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M48" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N48" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O48" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4522,25 +4520,19 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4552,50 +4544,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C49" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D49" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E49" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F49" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H49" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I49" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K49" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N49" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O49" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4606,13 +4598,15 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4630,50 +4624,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C50" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D50" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E50" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F50" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H50" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I50" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J50" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K50" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L50" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M50" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N50" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O50" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4681,18 +4675,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4705,55 +4699,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D51" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E51" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F51" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H51" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I51" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J51" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K51" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O51" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4761,18 +4759,18 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4785,59 +4783,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C52" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E52" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F52" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H52" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I52" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J52" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K52" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M52" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O52" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4848,18 +4842,20 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
+      <c r="S52" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4874,50 +4870,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C53" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D53" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E53" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F53" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H53" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I53" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J53" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K53" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L53" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M53" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N53" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4928,7 +4924,7 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="10" t="inlineStr">
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4940,11 +4936,13 @@
       </c>
       <c r="U53" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
@@ -4956,50 +4954,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C54" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D54" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E54" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F54" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H54" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I54" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J54" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K54" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M54" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N54" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O54" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5012,78 +5010,76 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C55" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D55" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E55" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H55" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I55" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J55" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K55" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L55" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M55" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N55" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O55" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5096,11 +5092,13 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5113,59 +5111,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C56" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D56" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E56" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F56" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H56" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I56" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J56" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K56" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M56" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N56" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O56" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5176,9 +5170,9 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
@@ -5186,8 +5180,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5202,74 +5198,74 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C57" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D57" t="n">
-        <v>101.21</v>
+        <v>100.97</v>
       </c>
       <c r="E57" t="n">
-        <v>105.83</v>
+        <v>102.43</v>
       </c>
       <c r="F57" t="n">
-        <v>4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0321</v>
       </c>
       <c r="H57" t="n">
-        <v>5.54</v>
+        <v>4.66</v>
       </c>
       <c r="I57" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J57" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K57" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L57" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M57" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N57" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O57" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5279,72 +5275,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>105.48</v>
+        <v>102.18</v>
       </c>
       <c r="C58" t="n">
-        <v>105.63</v>
+        <v>102.47</v>
       </c>
       <c r="D58" t="n">
-        <v>100.97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>102.43</v>
+        <v>101.91</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.4</v>
+        <v>-0.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0051</v>
       </c>
       <c r="H58" t="n">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="I58" t="n">
-        <v>95.67</v>
+        <v>96.31</v>
       </c>
       <c r="J58" t="n">
-        <v>101.22</v>
+        <v>97.34</v>
       </c>
       <c r="K58" t="n">
-        <v>103.06</v>
+        <v>100.1</v>
       </c>
       <c r="L58" t="n">
-        <v>104.91</v>
+        <v>102.86</v>
       </c>
       <c r="M58" t="n">
-        <v>108.6</v>
+        <v>104.76</v>
       </c>
       <c r="N58" t="n">
-        <v>112.3</v>
+        <v>106.65</v>
       </c>
       <c r="O58" t="n">
-        <v>112.29</v>
+        <v>110.29</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5370,50 +5368,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>102.18</v>
+        <v>101.06</v>
       </c>
       <c r="C59" t="n">
-        <v>102.47</v>
+        <v>103.48</v>
       </c>
       <c r="D59" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E59" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F59" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="H59" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I59" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="J59" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E59" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="F59" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="G59" s="5" t="n">
-        <v>-0.0051</v>
-      </c>
-      <c r="H59" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="I59" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="J59" t="n">
-        <v>97.34</v>
-      </c>
       <c r="K59" t="n">
-        <v>100.1</v>
+        <v>100.23</v>
       </c>
       <c r="L59" t="n">
-        <v>102.86</v>
+        <v>101.35</v>
       </c>
       <c r="M59" t="n">
-        <v>104.76</v>
+        <v>103.6</v>
       </c>
       <c r="N59" t="n">
-        <v>106.65</v>
+        <v>105.84</v>
       </c>
       <c r="O59" t="n">
-        <v>110.29</v>
+        <v>105.84</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5423,12 +5421,12 @@
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5447,70 +5445,74 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>101.06</v>
+        <v>101</v>
       </c>
       <c r="C60" t="n">
-        <v>103.48</v>
+        <v>101.08</v>
       </c>
       <c r="D60" t="n">
-        <v>99.19</v>
+        <v>94.22</v>
       </c>
       <c r="E60" t="n">
-        <v>100.3</v>
+        <v>95.78</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.61</v>
+        <v>-4.52</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0158</v>
+        <v>-0.0451</v>
       </c>
       <c r="H60" t="n">
-        <v>4.29</v>
+        <v>6.86</v>
       </c>
       <c r="I60" t="n">
-        <v>95.73</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>99.09999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="K60" t="n">
-        <v>100.23</v>
+        <v>98.16</v>
       </c>
       <c r="L60" t="n">
-        <v>101.35</v>
+        <v>100.82</v>
       </c>
       <c r="M60" t="n">
-        <v>103.6</v>
+        <v>102.45</v>
       </c>
       <c r="N60" t="n">
-        <v>105.84</v>
+        <v>104.07</v>
       </c>
       <c r="O60" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+        <v>107.77</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5531,76 +5533,70 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>101</v>
+        <v>95.39</v>
       </c>
       <c r="C61" t="n">
-        <v>101.08</v>
+        <v>97.42</v>
       </c>
       <c r="D61" t="n">
-        <v>94.22</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>95.78</v>
+        <v>94.59</v>
       </c>
       <c r="F61" t="n">
-        <v>-4.52</v>
+        <v>-1.19</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0124</v>
       </c>
       <c r="H61" t="n">
-        <v>6.86</v>
+        <v>5.02</v>
       </c>
       <c r="I61" t="n">
-        <v>94.90000000000001</v>
+        <v>87.36</v>
       </c>
       <c r="J61" t="n">
-        <v>95.48999999999999</v>
+        <v>87.98</v>
       </c>
       <c r="K61" t="n">
-        <v>98.16</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>100.82</v>
+        <v>96.72</v>
       </c>
       <c r="M61" t="n">
-        <v>102.45</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>104.07</v>
+        <v>101.7</v>
       </c>
       <c r="O61" t="n">
-        <v>107.77</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>107.94</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5626,50 +5622,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>95.39</v>
+        <v>92.72</v>
       </c>
       <c r="C62" t="n">
-        <v>97.42</v>
+        <v>92.79000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>92.40000000000001</v>
+        <v>92.63</v>
       </c>
       <c r="E62" t="n">
-        <v>94.59</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.19</v>
+        <v>-1.91</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0202</v>
       </c>
       <c r="H62" t="n">
-        <v>5.02</v>
+        <v>0.16</v>
       </c>
       <c r="I62" t="n">
-        <v>87.36</v>
+        <v>87.38</v>
       </c>
       <c r="J62" t="n">
-        <v>87.98</v>
+        <v>89.41</v>
       </c>
       <c r="K62" t="n">
-        <v>92.34999999999999</v>
+        <v>92.08</v>
       </c>
       <c r="L62" t="n">
-        <v>96.72</v>
+        <v>94.75</v>
       </c>
       <c r="M62" t="n">
-        <v>99.20999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N62" t="n">
-        <v>101.7</v>
+        <v>99.45</v>
       </c>
       <c r="O62" t="n">
-        <v>107.94</v>
+        <v>102.44</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5677,12 +5673,14 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5701,93 +5699,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>89.89</v>
-      </c>
-      <c r="C63" t="n">
-        <v>91.36</v>
-      </c>
-      <c r="D63" t="n">
-        <v>88.70999999999999</v>
-      </c>
-      <c r="E63" t="n">
-        <v>91.08</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-3.51</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0371</v>
-      </c>
-      <c r="H63" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="I63" t="n">
-        <v>87.38</v>
-      </c>
-      <c r="J63" t="n">
-        <v>89.41</v>
-      </c>
-      <c r="K63" t="n">
-        <v>92.08</v>
-      </c>
-      <c r="L63" t="n">
-        <v>94.75</v>
-      </c>
-      <c r="M63" t="n">
-        <v>97.09999999999999</v>
-      </c>
-      <c r="N63" t="n">
-        <v>99.45</v>
-      </c>
-      <c r="O63" t="n">
-        <v>102.44</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R63" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,69 +634,71 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70.5</v>
+        <v>70.43000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>71.15000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>69.31999999999999</v>
+        <v>69.22</v>
       </c>
       <c r="E2" t="n">
-        <v>70.75</v>
+        <v>69.5</v>
       </c>
       <c r="F2" t="n">
-        <v>1.52</v>
+        <v>-1.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.022</v>
+        <v>-0.0177</v>
       </c>
       <c r="H2" t="n">
-        <v>1.83</v>
+        <v>2.38</v>
       </c>
       <c r="I2" t="n">
-        <v>65.26000000000001</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="J2" t="n">
-        <v>65.44</v>
+        <v>69.18000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>67.58</v>
+        <v>69.83</v>
       </c>
       <c r="L2" t="n">
-        <v>69.72</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>70.88</v>
+        <v>71.67</v>
       </c>
       <c r="N2" t="n">
-        <v>72.04000000000001</v>
+        <v>72.84</v>
       </c>
       <c r="O2" t="n">
-        <v>75.16</v>
+        <v>72.98</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -711,72 +713,70 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>70.43000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="C3" t="n">
-        <v>71.59999999999999</v>
+        <v>70.19</v>
       </c>
       <c r="D3" t="n">
-        <v>69.22</v>
+        <v>67.92</v>
       </c>
       <c r="E3" t="n">
-        <v>69.5</v>
+        <v>68.58</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0132</v>
       </c>
       <c r="H3" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="I3" t="n">
-        <v>67.48999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="J3" t="n">
-        <v>69.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="K3" t="n">
-        <v>69.83</v>
+        <v>68.31</v>
       </c>
       <c r="L3" t="n">
-        <v>70.48999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="M3" t="n">
-        <v>71.67</v>
+        <v>70.69</v>
       </c>
       <c r="N3" t="n">
-        <v>72.84</v>
+        <v>71.42</v>
       </c>
       <c r="O3" t="n">
-        <v>72.98</v>
+        <v>73.98</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -797,57 +797,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>69.98</v>
+        <v>68.03</v>
       </c>
       <c r="C4" t="n">
-        <v>70.19</v>
+        <v>68.8</v>
       </c>
       <c r="D4" t="n">
-        <v>67.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>68.58</v>
+        <v>68.69</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.0016</v>
       </c>
       <c r="H4" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="I4" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>66.67</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>68.31</v>
+        <v>67.44</v>
       </c>
       <c r="L4" t="n">
-        <v>69.95</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>70.69</v>
+        <v>69.72</v>
       </c>
       <c r="N4" t="n">
-        <v>71.42</v>
+        <v>70.61</v>
       </c>
       <c r="O4" t="n">
-        <v>73.98</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -857,12 +857,12 @@
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -881,57 +881,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D5" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F5" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H5" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I5" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J5" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L5" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M5" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O5" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,14 +939,12 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -965,57 +963,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C6" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E6" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H6" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I6" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L6" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M6" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N6" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1026,78 +1024,80 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C7" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D7" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E7" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F7" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H7" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I7" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L7" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N7" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O7" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,7 +1108,7 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1120,13 +1120,11 @@
       </c>
       <c r="U7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1138,50 +1136,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C8" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D8" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E8" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H8" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I8" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J8" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M8" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1189,23 +1187,21 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1215,55 +1211,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C9" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D9" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E9" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I9" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K9" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L9" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N9" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O9" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1276,7 +1276,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1304,50 +1304,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C10" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D10" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E10" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I10" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J10" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L10" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M10" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N10" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O10" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,83 +1355,83 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
-      </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D11" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E11" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F11" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H11" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I11" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J11" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K11" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L11" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M11" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N11" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O11" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,25 +1442,21 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1472,50 +1468,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E12" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H12" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I12" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J12" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K12" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L12" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M12" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N12" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O12" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1526,15 +1522,13 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1547,55 +1541,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C13" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D13" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E13" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F13" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I13" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J13" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K13" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L13" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M13" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N13" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O13" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1608,7 +1606,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1627,57 +1625,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C14" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E14" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H14" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I14" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K14" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L14" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M14" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N14" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1690,76 +1688,78 @@
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D15" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E15" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F15" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I15" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L15" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M15" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N15" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1767,28 +1767,26 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1800,50 +1798,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C16" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D16" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E16" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F16" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H16" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I16" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K16" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L16" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M16" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O16" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1851,12 +1849,10 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1882,50 +1878,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C17" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D17" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E17" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F17" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H17" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I17" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J17" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K17" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L17" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M17" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N17" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1936,7 +1932,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1962,50 +1958,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C18" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D18" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E18" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F18" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H18" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I18" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J18" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K18" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L18" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N18" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2016,21 +2012,25 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2042,50 +2042,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C19" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D19" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F19" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H19" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I19" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J19" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M19" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N19" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2093,96 +2093,100 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C20" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D20" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E20" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H20" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I20" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J20" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K20" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L20" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M20" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N20" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2196,81 +2200,73 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C21" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E21" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H21" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I21" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J21" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K21" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L21" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O21" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2294,50 +2290,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E22" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H22" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I22" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J22" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K22" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L22" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N22" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2345,28 +2341,30 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2374,50 +2372,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C23" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D23" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E23" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F23" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H23" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I23" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J23" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K23" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L23" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N23" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O23" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2430,18 +2428,14 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2451,55 +2445,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C24" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D24" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E24" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H24" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I24" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J24" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K24" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M24" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O24" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2507,19 +2505,25 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2538,56 +2542,58 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D25" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F25" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H25" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I25" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J25" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N25" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O25" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
@@ -2596,18 +2602,14 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2619,64 +2621,66 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D26" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E26" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H26" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I26" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J26" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N26" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O26" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q26" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
@@ -2684,13 +2688,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2698,89 +2704,81 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W26" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C27" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D27" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F27" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H27" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I27" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J27" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L27" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N27" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2793,59 +2791,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C28" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D28" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H28" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I28" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J28" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K28" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M28" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N28" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O28" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2858,14 +2852,18 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2875,55 +2873,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C29" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D29" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E29" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H29" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I29" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J29" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K29" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M29" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O29" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2934,20 +2936,18 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2966,50 +2966,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C30" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D30" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F30" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H30" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I30" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L30" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M30" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N30" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O30" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3020,80 +3020,80 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
+      <c r="S30" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D31" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E31" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F31" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H31" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I31" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J31" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K31" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L31" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M31" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N31" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3104,25 +3104,21 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
@@ -3134,50 +3130,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F32" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H32" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I32" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L32" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N32" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O32" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3188,15 +3184,13 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3209,68 +3203,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C33" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D33" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E33" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F33" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H33" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I33" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J33" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K33" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N33" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O33" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+        <v>86.3</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3282,88 +3286,80 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C34" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H34" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I34" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J34" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L34" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M34" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N34" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N34" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O34" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3375,55 +3371,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C35" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E35" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F35" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H35" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I35" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K35" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M35" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3434,19 +3434,21 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3457,57 +3459,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C36" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D36" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F36" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H36" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I36" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L36" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M36" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N36" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O36" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3518,20 +3520,16 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3550,50 +3548,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C37" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D37" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F37" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H37" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I37" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J37" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K37" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N37" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3604,16 +3602,20 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3625,57 +3627,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C38" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D38" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E38" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F38" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H38" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I38" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J38" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K38" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N38" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3686,7 +3688,7 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3711,57 +3713,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C39" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D39" t="n">
         <v>85.8</v>
       </c>
-      <c r="C39" t="n">
-        <v>89</v>
-      </c>
-      <c r="D39" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E39" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F39" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H39" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I39" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J39" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K39" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L39" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N39" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O39" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3769,23 +3771,21 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
@@ -3797,72 +3797,74 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C40" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E40" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H40" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I40" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J40" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K40" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L40" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M40" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N40" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O40" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3879,66 +3881,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C41" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D41" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E41" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H41" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I41" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L41" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N41" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q41" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
@@ -3946,7 +3946,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
+      <c r="S41" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3970,69 +3970,63 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C42" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D42" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E42" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H42" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I42" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J42" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K42" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L42" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M42" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N42" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O42" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>91.45</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4054,50 +4048,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C43" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D43" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E43" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H43" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I43" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K43" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L43" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N43" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O43" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4110,11 +4104,13 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4127,55 +4123,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C44" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D44" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E44" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H44" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I44" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J44" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K44" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L44" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N44" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4186,15 +4186,13 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4209,57 +4207,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C45" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E45" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H45" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I45" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J45" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K45" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L45" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N45" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O45" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4270,78 +4268,80 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C46" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D46" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E46" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F46" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H46" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I46" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L46" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M46" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4352,7 +4352,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4382,50 +4382,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E47" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F47" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I47" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L47" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M47" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N47" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O47" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4436,25 +4436,19 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4466,50 +4460,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C48" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D48" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E48" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F48" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H48" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I48" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K48" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N48" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O48" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4520,13 +4514,15 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
+      <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4544,50 +4540,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C49" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D49" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E49" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F49" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H49" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I49" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J49" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K49" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L49" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M49" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N49" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O49" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4595,18 +4591,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4619,55 +4615,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D50" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E50" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F50" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H50" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I50" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J50" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K50" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O50" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4675,18 +4675,18 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4699,59 +4699,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C51" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E51" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F51" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H51" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I51" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J51" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K51" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M51" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O51" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4762,18 +4758,20 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
+      <c r="S51" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4788,50 +4786,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C52" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D52" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E52" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F52" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H52" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I52" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J52" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K52" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L52" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M52" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N52" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4842,7 +4840,7 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4854,11 +4852,13 @@
       </c>
       <c r="U52" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
@@ -4870,50 +4870,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C53" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D53" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E53" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F53" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H53" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I53" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J53" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K53" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M53" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N53" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O53" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4926,78 +4926,76 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C54" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D54" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E54" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H54" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I54" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J54" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K54" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L54" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M54" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N54" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O54" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5010,11 +5008,13 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5027,59 +5027,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C55" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D55" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E55" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F55" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H55" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I55" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J55" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K55" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M55" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N55" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O55" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5090,9 +5086,9 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
@@ -5100,8 +5096,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5116,74 +5114,74 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C56" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D56" t="n">
-        <v>101.21</v>
+        <v>100.97</v>
       </c>
       <c r="E56" t="n">
-        <v>105.83</v>
+        <v>102.43</v>
       </c>
       <c r="F56" t="n">
-        <v>4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0321</v>
       </c>
       <c r="H56" t="n">
-        <v>5.54</v>
+        <v>4.66</v>
       </c>
       <c r="I56" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J56" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K56" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L56" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M56" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N56" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O56" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5193,72 +5191,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>105.48</v>
+        <v>102.18</v>
       </c>
       <c r="C57" t="n">
-        <v>105.63</v>
+        <v>102.47</v>
       </c>
       <c r="D57" t="n">
-        <v>100.97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>102.43</v>
+        <v>101.91</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.4</v>
+        <v>-0.52</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0051</v>
       </c>
       <c r="H57" t="n">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="I57" t="n">
-        <v>95.67</v>
+        <v>96.31</v>
       </c>
       <c r="J57" t="n">
-        <v>101.22</v>
+        <v>97.34</v>
       </c>
       <c r="K57" t="n">
-        <v>103.06</v>
+        <v>100.1</v>
       </c>
       <c r="L57" t="n">
-        <v>104.91</v>
+        <v>102.86</v>
       </c>
       <c r="M57" t="n">
-        <v>108.6</v>
+        <v>104.76</v>
       </c>
       <c r="N57" t="n">
-        <v>112.3</v>
+        <v>106.65</v>
       </c>
       <c r="O57" t="n">
-        <v>112.29</v>
+        <v>110.29</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5284,50 +5284,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>102.18</v>
+        <v>101.06</v>
       </c>
       <c r="C58" t="n">
-        <v>102.47</v>
+        <v>103.48</v>
       </c>
       <c r="D58" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E58" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="H58" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I58" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="J58" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E58" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0051</v>
-      </c>
-      <c r="H58" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="I58" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="J58" t="n">
-        <v>97.34</v>
-      </c>
       <c r="K58" t="n">
-        <v>100.1</v>
+        <v>100.23</v>
       </c>
       <c r="L58" t="n">
-        <v>102.86</v>
+        <v>101.35</v>
       </c>
       <c r="M58" t="n">
-        <v>104.76</v>
+        <v>103.6</v>
       </c>
       <c r="N58" t="n">
-        <v>106.65</v>
+        <v>105.84</v>
       </c>
       <c r="O58" t="n">
-        <v>110.29</v>
+        <v>105.84</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5337,12 +5337,12 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5361,70 +5361,74 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>101.06</v>
+        <v>101</v>
       </c>
       <c r="C59" t="n">
-        <v>103.48</v>
+        <v>101.08</v>
       </c>
       <c r="D59" t="n">
-        <v>99.19</v>
+        <v>94.22</v>
       </c>
       <c r="E59" t="n">
-        <v>100.3</v>
+        <v>95.78</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.61</v>
+        <v>-4.52</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0158</v>
+        <v>-0.0451</v>
       </c>
       <c r="H59" t="n">
-        <v>4.29</v>
+        <v>6.86</v>
       </c>
       <c r="I59" t="n">
-        <v>95.73</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>99.09999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>100.23</v>
+        <v>98.16</v>
       </c>
       <c r="L59" t="n">
-        <v>101.35</v>
+        <v>100.82</v>
       </c>
       <c r="M59" t="n">
-        <v>103.6</v>
+        <v>102.45</v>
       </c>
       <c r="N59" t="n">
-        <v>105.84</v>
+        <v>104.07</v>
       </c>
       <c r="O59" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+        <v>107.77</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5445,76 +5449,70 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>101</v>
+        <v>95.39</v>
       </c>
       <c r="C60" t="n">
-        <v>101.08</v>
+        <v>97.42</v>
       </c>
       <c r="D60" t="n">
-        <v>94.22</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>95.78</v>
+        <v>94.59</v>
       </c>
       <c r="F60" t="n">
-        <v>-4.52</v>
+        <v>-1.19</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0124</v>
       </c>
       <c r="H60" t="n">
-        <v>6.86</v>
+        <v>5.02</v>
       </c>
       <c r="I60" t="n">
-        <v>94.90000000000001</v>
+        <v>87.36</v>
       </c>
       <c r="J60" t="n">
-        <v>95.48999999999999</v>
+        <v>87.98</v>
       </c>
       <c r="K60" t="n">
-        <v>98.16</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>100.82</v>
+        <v>96.72</v>
       </c>
       <c r="M60" t="n">
-        <v>102.45</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>104.07</v>
+        <v>101.7</v>
       </c>
       <c r="O60" t="n">
-        <v>107.77</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>107.94</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5540,63 +5538,67 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>95.39</v>
+        <v>89.89</v>
       </c>
       <c r="C61" t="n">
-        <v>97.42</v>
+        <v>93.06</v>
       </c>
       <c r="D61" t="n">
-        <v>92.40000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E61" t="n">
-        <v>94.59</v>
+        <v>92.16</v>
       </c>
       <c r="F61" t="n">
-        <v>-1.19</v>
+        <v>-2.43</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0257</v>
       </c>
       <c r="H61" t="n">
-        <v>5.02</v>
+        <v>4.35</v>
       </c>
       <c r="I61" t="n">
-        <v>87.36</v>
+        <v>87.38</v>
       </c>
       <c r="J61" t="n">
-        <v>87.98</v>
+        <v>89.41</v>
       </c>
       <c r="K61" t="n">
-        <v>92.34999999999999</v>
+        <v>92.08</v>
       </c>
       <c r="L61" t="n">
-        <v>96.72</v>
+        <v>94.75</v>
       </c>
       <c r="M61" t="n">
-        <v>99.20999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>101.7</v>
+        <v>99.45</v>
       </c>
       <c r="O61" t="n">
-        <v>107.94</v>
+        <v>102.44</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5622,50 +5624,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>92.72</v>
+        <v>94.75</v>
       </c>
       <c r="C62" t="n">
-        <v>92.79000000000001</v>
+        <v>94.75</v>
       </c>
       <c r="D62" t="n">
-        <v>92.63</v>
+        <v>94.27</v>
       </c>
       <c r="E62" t="n">
-        <v>92.68000000000001</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="F62" t="n">
-        <v>-1.91</v>
+        <v>2.41</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0202</v>
+        <v>0.0262</v>
       </c>
       <c r="H62" t="n">
-        <v>0.16</v>
+        <v>0.48</v>
       </c>
       <c r="I62" t="n">
-        <v>87.38</v>
+        <v>84.36</v>
       </c>
       <c r="J62" t="n">
-        <v>89.41</v>
+        <v>88.45</v>
       </c>
       <c r="K62" t="n">
-        <v>92.08</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="L62" t="n">
-        <v>94.75</v>
+        <v>91.52</v>
       </c>
       <c r="M62" t="n">
-        <v>97.09999999999999</v>
+        <v>94.34</v>
       </c>
       <c r="N62" t="n">
-        <v>99.45</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="O62" t="n">
-        <v>102.44</v>
+        <v>97.41</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5673,19 +5675,19 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
-      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
@@ -5697,11 +5699,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,64 +634,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>70.43000000000001</v>
+        <v>69.98</v>
       </c>
       <c r="C2" t="n">
-        <v>71.59999999999999</v>
+        <v>70.19</v>
       </c>
       <c r="D2" t="n">
-        <v>69.22</v>
+        <v>67.92</v>
       </c>
       <c r="E2" t="n">
-        <v>69.5</v>
+        <v>68.58</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.25</v>
+        <v>-0.92</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0177</v>
+        <v>-0.0132</v>
       </c>
       <c r="H2" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="I2" t="n">
-        <v>67.48999999999999</v>
+        <v>66.84</v>
       </c>
       <c r="J2" t="n">
-        <v>69.18000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="K2" t="n">
-        <v>69.83</v>
+        <v>68.31</v>
       </c>
       <c r="L2" t="n">
-        <v>70.48999999999999</v>
+        <v>69.95</v>
       </c>
       <c r="M2" t="n">
-        <v>71.67</v>
+        <v>70.69</v>
       </c>
       <c r="N2" t="n">
-        <v>72.84</v>
+        <v>71.42</v>
       </c>
       <c r="O2" t="n">
-        <v>72.98</v>
+        <v>73.98</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -713,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>69.98</v>
+        <v>68.03</v>
       </c>
       <c r="C3" t="n">
-        <v>70.19</v>
+        <v>68.8</v>
       </c>
       <c r="D3" t="n">
-        <v>67.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E3" t="n">
-        <v>68.58</v>
+        <v>68.69</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.0016</v>
       </c>
       <c r="H3" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="I3" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>66.67</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>68.31</v>
+        <v>67.44</v>
       </c>
       <c r="L3" t="n">
-        <v>69.95</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>70.69</v>
+        <v>69.72</v>
       </c>
       <c r="N3" t="n">
-        <v>71.42</v>
+        <v>70.61</v>
       </c>
       <c r="O3" t="n">
-        <v>73.98</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -773,12 +771,12 @@
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -797,57 +795,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C4" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D4" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E4" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F4" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H4" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I4" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J4" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L4" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M4" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O4" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -855,14 +853,12 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -881,57 +877,57 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C5" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D5" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E5" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H5" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I5" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K5" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L5" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M5" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N5" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -944,76 +940,78 @@
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C6" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D6" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E6" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F6" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H6" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I6" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L6" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N6" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O6" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1036,13 +1034,11 @@
       </c>
       <c r="U6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1054,50 +1050,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C7" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D7" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E7" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H7" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I7" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J7" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L7" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M7" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,24 +1101,22 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
@@ -1131,55 +1125,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C8" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D8" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E8" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I8" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J8" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K8" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L8" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N8" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O8" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1220,50 +1218,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C9" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D9" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E9" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I9" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J9" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L9" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M9" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N9" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O9" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,83 +1269,83 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
-      </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D10" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E10" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F10" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H10" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I10" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J10" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K10" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M10" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N10" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O10" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1365,18 +1363,14 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1388,50 +1382,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E11" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H11" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I11" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J11" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K11" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L11" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M11" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N11" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O11" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1444,13 +1438,11 @@
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1463,55 +1455,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C12" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D12" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E12" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F12" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I12" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J12" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K12" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L12" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M12" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N12" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O12" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1522,9 +1518,9 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1543,57 +1539,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C13" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D13" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E13" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H13" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I13" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K13" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L13" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M13" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N13" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1604,78 +1600,80 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C14" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D14" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E14" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F14" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I14" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K14" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L14" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M14" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N14" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1683,8 +1681,10 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
@@ -1693,18 +1693,14 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1716,50 +1712,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C15" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D15" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E15" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F15" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H15" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I15" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K15" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L15" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M15" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O15" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1767,10 +1763,8 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
@@ -1798,50 +1792,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C16" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D16" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E16" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F16" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H16" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I16" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J16" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K16" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L16" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M16" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N16" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1878,50 +1872,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C17" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D17" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F17" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H17" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I17" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J17" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K17" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L17" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N17" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1939,14 +1933,18 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1958,50 +1956,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C18" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D18" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E18" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F18" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H18" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I18" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J18" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M18" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N18" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2009,93 +2007,97 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
+      </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C19" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D19" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E19" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H19" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I19" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J19" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K19" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L19" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M19" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N19" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
@@ -2112,78 +2114,70 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C20" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E20" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H20" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I20" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J20" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K20" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L20" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O20" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
@@ -2210,50 +2204,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E21" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I21" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J21" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K21" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L21" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N21" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2261,28 +2255,30 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2290,50 +2286,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C22" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D22" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E22" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F22" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H22" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I22" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J22" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K22" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L22" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N22" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O22" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2344,20 +2340,16 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2367,55 +2359,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C23" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D23" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E23" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H23" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I23" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J23" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K23" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M23" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O23" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2423,19 +2419,25 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2454,76 +2456,74 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D24" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F24" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H24" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I24" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J24" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N24" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O24" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2535,64 +2535,66 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D25" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E25" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H25" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I25" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J25" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L25" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N25" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O25" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q25" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
@@ -2605,8 +2607,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2614,89 +2618,81 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C26" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D26" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F26" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H26" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I26" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J26" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L26" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N26" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2709,59 +2705,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C27" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D27" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H27" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I27" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J27" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K27" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M27" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N27" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O27" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2772,16 +2764,20 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2791,55 +2787,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C28" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D28" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E28" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H28" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I28" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J28" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K28" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M28" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O28" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2857,13 +2857,11 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2882,50 +2880,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C29" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D29" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F29" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H29" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I29" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L29" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M29" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N29" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O29" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2943,73 +2941,73 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D30" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E30" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F30" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H30" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I30" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J30" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K30" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L30" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M30" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N30" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3027,18 +3025,14 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
@@ -3050,50 +3044,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F31" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H31" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I31" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L31" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N31" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O31" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3106,13 +3100,11 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3125,68 +3117,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C32" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D32" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E32" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F32" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H32" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I32" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J32" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K32" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N32" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O32" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>86.3</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3198,88 +3200,80 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W32" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C33" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F33" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H33" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I33" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J33" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L33" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M33" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N33" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N33" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O33" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3291,55 +3285,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C34" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E34" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F34" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H34" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I34" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J34" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M34" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3357,12 +3355,14 @@
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3373,57 +3373,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C35" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D35" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F35" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H35" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I35" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J35" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L35" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M35" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N35" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O35" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3436,18 +3436,14 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3466,50 +3462,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C36" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D36" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F36" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H36" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I36" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J36" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K36" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N36" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3522,14 +3518,18 @@
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3541,57 +3541,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C37" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D37" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E37" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F37" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H37" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I37" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J37" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K37" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N37" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3627,57 +3627,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C38" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D38" t="n">
         <v>85.8</v>
       </c>
-      <c r="C38" t="n">
-        <v>89</v>
-      </c>
-      <c r="D38" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E38" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F38" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I38" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J38" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K38" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L38" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N38" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O38" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3685,24 +3685,22 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
+      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3713,63 +3711,65 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C39" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E39" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H39" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I39" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J39" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K39" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L39" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M39" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N39" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O39" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3795,66 +3795,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C40" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D40" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E40" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H40" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I40" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L40" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N40" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q40" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
@@ -3886,69 +3884,63 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C41" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D41" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E41" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H41" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I41" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J41" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K41" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L41" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M41" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N41" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O41" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>91.45</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3970,50 +3962,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C42" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D42" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H42" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I42" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K42" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L42" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N42" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O42" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4024,13 +4016,15 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4043,55 +4037,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C43" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D43" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E43" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H43" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I43" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J43" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K43" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L43" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N43" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4104,13 +4102,11 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4125,57 +4121,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C44" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E44" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H44" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I44" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J44" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K44" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L44" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N44" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O44" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4188,76 +4184,78 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C45" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D45" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E45" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F45" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H45" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I45" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L45" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M45" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O45" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4298,50 +4296,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E46" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F46" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H46" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I46" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K46" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L46" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M46" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N46" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O46" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4354,23 +4352,17 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
@@ -4382,50 +4374,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C47" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D47" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E47" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F47" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H47" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I47" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K47" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N47" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O47" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4441,8 +4433,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4460,50 +4454,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C48" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D48" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E48" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F48" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H48" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I48" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J48" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K48" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L48" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M48" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N48" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O48" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4511,18 +4505,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4535,55 +4529,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D49" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E49" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F49" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H49" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I49" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J49" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K49" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O49" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4591,18 +4589,18 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R49" s="6" t="n">
+        <v/>
       </c>
       <c r="S49" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4615,59 +4613,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C50" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E50" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F50" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H50" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I50" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J50" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K50" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M50" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O50" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4685,11 +4679,13 @@
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4704,50 +4700,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C51" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D51" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E51" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F51" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H51" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I51" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J51" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K51" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L51" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M51" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N51" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4770,11 +4766,13 @@
       </c>
       <c r="U51" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
@@ -4786,50 +4784,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C52" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D52" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E52" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F52" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H52" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I52" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J52" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K52" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M52" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N52" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O52" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4840,80 +4838,78 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C53" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D53" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E53" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H53" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I53" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J53" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K53" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L53" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M53" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N53" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O53" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4924,13 +4920,15 @@
       <c r="R53" s="6" t="n">
         <v/>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4943,59 +4941,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C54" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D54" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E54" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F54" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H54" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I54" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J54" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K54" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L54" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M54" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N54" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O54" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5008,7 +5002,7 @@
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
@@ -5016,8 +5010,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5032,75 +5028,75 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C55" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D55" t="n">
-        <v>101.21</v>
+        <v>100.97</v>
       </c>
       <c r="E55" t="n">
-        <v>105.83</v>
+        <v>102.43</v>
       </c>
       <c r="F55" t="n">
-        <v>4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0321</v>
       </c>
       <c r="H55" t="n">
-        <v>5.54</v>
+        <v>4.66</v>
       </c>
       <c r="I55" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J55" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K55" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L55" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M55" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N55" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O55" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
+      <c r="Q55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U55" s="8" t="inlineStr">
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5109,72 +5105,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>105.48</v>
+        <v>102.18</v>
       </c>
       <c r="C56" t="n">
-        <v>105.63</v>
+        <v>102.47</v>
       </c>
       <c r="D56" t="n">
-        <v>100.97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>102.43</v>
+        <v>101.91</v>
       </c>
       <c r="F56" t="n">
-        <v>-3.4</v>
+        <v>-0.52</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0051</v>
       </c>
       <c r="H56" t="n">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="I56" t="n">
-        <v>95.67</v>
+        <v>96.31</v>
       </c>
       <c r="J56" t="n">
-        <v>101.22</v>
+        <v>97.34</v>
       </c>
       <c r="K56" t="n">
-        <v>103.06</v>
+        <v>100.1</v>
       </c>
       <c r="L56" t="n">
-        <v>104.91</v>
+        <v>102.86</v>
       </c>
       <c r="M56" t="n">
-        <v>108.6</v>
+        <v>104.76</v>
       </c>
       <c r="N56" t="n">
-        <v>112.3</v>
+        <v>106.65</v>
       </c>
       <c r="O56" t="n">
-        <v>112.29</v>
+        <v>110.29</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5200,50 +5198,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>102.18</v>
+        <v>101.06</v>
       </c>
       <c r="C57" t="n">
-        <v>102.47</v>
+        <v>103.48</v>
       </c>
       <c r="D57" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E57" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F57" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I57" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="J57" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E57" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="F57" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="G57" s="5" t="n">
-        <v>-0.0051</v>
-      </c>
-      <c r="H57" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="I57" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="J57" t="n">
-        <v>97.34</v>
-      </c>
       <c r="K57" t="n">
-        <v>100.1</v>
+        <v>100.23</v>
       </c>
       <c r="L57" t="n">
-        <v>102.86</v>
+        <v>101.35</v>
       </c>
       <c r="M57" t="n">
-        <v>104.76</v>
+        <v>103.6</v>
       </c>
       <c r="N57" t="n">
-        <v>106.65</v>
+        <v>105.84</v>
       </c>
       <c r="O57" t="n">
-        <v>110.29</v>
+        <v>105.84</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5253,12 +5251,12 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5277,67 +5275,71 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>101.06</v>
+        <v>101</v>
       </c>
       <c r="C58" t="n">
-        <v>103.48</v>
+        <v>101.08</v>
       </c>
       <c r="D58" t="n">
-        <v>99.19</v>
+        <v>94.22</v>
       </c>
       <c r="E58" t="n">
-        <v>100.3</v>
+        <v>95.78</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.61</v>
+        <v>-4.52</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0158</v>
+        <v>-0.0451</v>
       </c>
       <c r="H58" t="n">
-        <v>4.29</v>
+        <v>6.86</v>
       </c>
       <c r="I58" t="n">
-        <v>95.73</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>99.09999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>100.23</v>
+        <v>98.16</v>
       </c>
       <c r="L58" t="n">
-        <v>101.35</v>
+        <v>100.82</v>
       </c>
       <c r="M58" t="n">
-        <v>103.6</v>
+        <v>102.45</v>
       </c>
       <c r="N58" t="n">
-        <v>105.84</v>
+        <v>104.07</v>
       </c>
       <c r="O58" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+        <v>107.77</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="7" t="inlineStr">
@@ -5361,76 +5363,70 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>101</v>
+        <v>95.39</v>
       </c>
       <c r="C59" t="n">
-        <v>101.08</v>
+        <v>97.42</v>
       </c>
       <c r="D59" t="n">
-        <v>94.22</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>95.78</v>
+        <v>94.59</v>
       </c>
       <c r="F59" t="n">
-        <v>-4.52</v>
+        <v>-1.19</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0124</v>
       </c>
       <c r="H59" t="n">
-        <v>6.86</v>
+        <v>5.02</v>
       </c>
       <c r="I59" t="n">
-        <v>94.90000000000001</v>
+        <v>87.36</v>
       </c>
       <c r="J59" t="n">
-        <v>95.48999999999999</v>
+        <v>87.98</v>
       </c>
       <c r="K59" t="n">
-        <v>98.16</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>100.82</v>
+        <v>96.72</v>
       </c>
       <c r="M59" t="n">
-        <v>102.45</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="N59" t="n">
-        <v>104.07</v>
+        <v>101.7</v>
       </c>
       <c r="O59" t="n">
-        <v>107.77</v>
-      </c>
-      <c r="P59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>107.94</v>
+      </c>
+      <c r="P59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5456,63 +5452,67 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>95.39</v>
+        <v>89.89</v>
       </c>
       <c r="C60" t="n">
-        <v>97.42</v>
+        <v>93.06</v>
       </c>
       <c r="D60" t="n">
-        <v>92.40000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E60" t="n">
-        <v>94.59</v>
+        <v>92.16</v>
       </c>
       <c r="F60" t="n">
-        <v>-1.19</v>
+        <v>-2.43</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0257</v>
       </c>
       <c r="H60" t="n">
-        <v>5.02</v>
+        <v>4.35</v>
       </c>
       <c r="I60" t="n">
-        <v>87.36</v>
+        <v>87.38</v>
       </c>
       <c r="J60" t="n">
-        <v>87.98</v>
+        <v>89.41</v>
       </c>
       <c r="K60" t="n">
-        <v>92.34999999999999</v>
+        <v>92.08</v>
       </c>
       <c r="L60" t="n">
-        <v>96.72</v>
+        <v>94.75</v>
       </c>
       <c r="M60" t="n">
-        <v>99.20999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>101.7</v>
+        <v>99.45</v>
       </c>
       <c r="O60" t="n">
-        <v>107.94</v>
+        <v>102.44</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5538,72 +5538,70 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>89.89</v>
+        <v>92.72</v>
       </c>
       <c r="C61" t="n">
-        <v>93.06</v>
+        <v>96.78</v>
       </c>
       <c r="D61" t="n">
-        <v>88.70999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="E61" t="n">
-        <v>92.16</v>
+        <v>94.61</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.43</v>
+        <v>2.45</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0266</v>
       </c>
       <c r="H61" t="n">
-        <v>4.35</v>
+        <v>5.55</v>
       </c>
       <c r="I61" t="n">
-        <v>87.38</v>
+        <v>84.36</v>
       </c>
       <c r="J61" t="n">
-        <v>89.41</v>
+        <v>88.45</v>
       </c>
       <c r="K61" t="n">
-        <v>92.08</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="L61" t="n">
-        <v>94.75</v>
+        <v>91.52</v>
       </c>
       <c r="M61" t="n">
-        <v>97.09999999999999</v>
+        <v>94.34</v>
       </c>
       <c r="N61" t="n">
-        <v>99.45</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="O61" t="n">
-        <v>102.44</v>
+        <v>97.41</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5615,16 +5613,12 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
@@ -5634,40 +5628,40 @@
         <v>94.75</v>
       </c>
       <c r="D62" t="n">
-        <v>94.27</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>94.56999999999999</v>
+        <v>92.41</v>
       </c>
       <c r="F62" t="n">
-        <v>2.41</v>
+        <v>-2.2</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0262</v>
+        <v>-0.0233</v>
       </c>
       <c r="H62" t="n">
-        <v>0.48</v>
+        <v>3.24</v>
       </c>
       <c r="I62" t="n">
-        <v>84.36</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="J62" t="n">
-        <v>88.45</v>
+        <v>89.36</v>
       </c>
       <c r="K62" t="n">
-        <v>89.98999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="L62" t="n">
-        <v>91.52</v>
+        <v>94.31</v>
       </c>
       <c r="M62" t="n">
-        <v>94.34</v>
+        <v>97.38</v>
       </c>
       <c r="N62" t="n">
-        <v>97.15000000000001</v>
+        <v>100.46</v>
       </c>
       <c r="O62" t="n">
-        <v>97.41</v>
+        <v>102.33</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5675,19 +5669,19 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
+      <c r="R62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
@@ -5699,7 +5693,93 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>93.58</v>
+      </c>
+      <c r="C63" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="D63" t="n">
+        <v>93.16</v>
+      </c>
+      <c r="E63" t="n">
+        <v>92.41</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="I63" t="n">
+        <v>88.27</v>
+      </c>
+      <c r="J63" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="K63" t="n">
+        <v>90.79000000000001</v>
+      </c>
+      <c r="L63" t="n">
+        <v>92.77</v>
+      </c>
+      <c r="M63" t="n">
+        <v>94.03</v>
+      </c>
+      <c r="N63" t="n">
+        <v>95.29000000000001</v>
+      </c>
+      <c r="O63" t="n">
+        <v>97.98999999999999</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>69.98</v>
+        <v>68.03</v>
       </c>
       <c r="C2" t="n">
-        <v>70.19</v>
+        <v>68.8</v>
       </c>
       <c r="D2" t="n">
-        <v>67.92</v>
+        <v>67.04000000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>68.58</v>
+        <v>68.69</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.92</v>
+        <v>0.11</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0132</v>
+        <v>0.0016</v>
       </c>
       <c r="H2" t="n">
-        <v>2.27</v>
+        <v>1.76</v>
       </c>
       <c r="I2" t="n">
-        <v>66.84</v>
+        <v>65.65000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>66.67</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>68.31</v>
+        <v>67.44</v>
       </c>
       <c r="L2" t="n">
-        <v>69.95</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>70.69</v>
+        <v>69.72</v>
       </c>
       <c r="N2" t="n">
-        <v>71.42</v>
+        <v>70.61</v>
       </c>
       <c r="O2" t="n">
-        <v>73.98</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -687,12 +687,12 @@
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -711,57 +711,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E3" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F3" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H3" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I3" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J3" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L3" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M3" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O3" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,14 +769,12 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -795,57 +793,57 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C4" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D4" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E4" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H4" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I4" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L4" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M4" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N4" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -858,76 +856,78 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C5" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D5" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E5" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F5" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H5" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I5" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L5" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N5" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -950,13 +950,11 @@
       </c>
       <c r="U5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -968,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C6" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D6" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E6" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F6" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H6" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I6" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J6" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L6" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M6" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O6" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,24 +1017,22 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
@@ -1045,55 +1041,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C7" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D7" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E7" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I7" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K7" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L7" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N7" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O7" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1134,50 +1134,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C8" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D8" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E8" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I8" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J8" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L8" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M8" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N8" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O8" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1185,83 +1185,83 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
-      </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D9" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E9" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F9" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H9" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I9" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J9" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K9" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M9" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N9" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O9" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1279,18 +1279,14 @@
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1302,50 +1298,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E10" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H10" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I10" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J10" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K10" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L10" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M10" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N10" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O10" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1358,13 +1354,11 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1377,55 +1371,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C11" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D11" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E11" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F11" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I11" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J11" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K11" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L11" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M11" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N11" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O11" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1436,9 +1434,9 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1457,57 +1455,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C12" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D12" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E12" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H12" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I12" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K12" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L12" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M12" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N12" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O12" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1518,78 +1516,80 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D13" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E13" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F13" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I13" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L13" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M13" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N13" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1597,8 +1597,10 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
@@ -1607,18 +1609,14 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1630,50 +1628,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C14" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D14" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E14" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F14" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H14" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I14" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K14" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L14" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M14" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O14" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1681,10 +1679,8 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R14" s="6" t="n">
+        <v/>
       </c>
       <c r="S14" s="10" t="inlineStr">
         <is>
@@ -1712,50 +1708,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C15" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D15" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E15" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F15" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H15" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I15" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J15" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K15" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L15" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M15" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N15" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1792,50 +1788,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C16" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D16" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F16" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H16" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I16" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J16" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K16" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L16" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N16" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,14 +1849,18 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1872,50 +1872,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C17" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D17" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E17" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F17" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H17" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I17" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J17" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M17" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N17" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1923,93 +1923,97 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
+      </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C18" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D18" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E18" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H18" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I18" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J18" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K18" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L18" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M18" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N18" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
@@ -2026,78 +2030,70 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C19" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E19" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H19" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I19" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J19" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K19" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L19" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O19" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S19" s="7" t="inlineStr">
@@ -2124,50 +2120,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D20" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E20" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I20" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J20" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K20" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L20" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N20" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2175,28 +2171,30 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2204,50 +2202,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D21" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E21" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F21" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H21" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I21" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J21" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K21" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L21" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N21" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O21" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2258,20 +2256,16 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2281,55 +2275,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C22" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D22" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E22" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H22" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I22" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J22" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K22" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M22" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O22" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2337,19 +2335,25 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2368,76 +2372,74 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D23" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E23" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F23" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H23" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I23" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J23" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N23" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O23" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2449,64 +2451,66 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D24" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E24" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H24" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I24" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J24" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N24" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O24" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q24" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
@@ -2519,8 +2523,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2528,89 +2534,81 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C25" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D25" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H25" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I25" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J25" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L25" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N25" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2623,59 +2621,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C26" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D26" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H26" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I26" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J26" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K26" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M26" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N26" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O26" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2686,16 +2680,20 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2705,55 +2703,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C27" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D27" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E27" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H27" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I27" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J27" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K27" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L27" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M27" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N27" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O27" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2771,13 +2773,11 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2796,50 +2796,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C28" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D28" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F28" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H28" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I28" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L28" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M28" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N28" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O28" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2857,73 +2857,73 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W28" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D29" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E29" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F29" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H29" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I29" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J29" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K29" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L29" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M29" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N29" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2941,18 +2941,14 @@
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
@@ -2964,50 +2960,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F30" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H30" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I30" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L30" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N30" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O30" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3020,13 +3016,11 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3039,68 +3033,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C31" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D31" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E31" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H31" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I31" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J31" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K31" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N31" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O31" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>86.3</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3112,88 +3116,80 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W31" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C32" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H32" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I32" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J32" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L32" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M32" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N32" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N32" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O32" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3205,55 +3201,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C33" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E33" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F33" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H33" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I33" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J33" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K33" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M33" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3271,12 +3271,14 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
@@ -3287,57 +3289,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C34" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D34" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F34" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H34" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I34" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J34" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L34" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M34" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N34" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O34" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3350,18 +3352,14 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3380,50 +3378,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C35" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D35" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F35" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H35" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I35" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J35" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K35" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N35" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3436,14 +3434,18 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3455,57 +3457,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C36" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D36" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F36" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H36" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I36" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J36" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K36" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L36" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N36" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3541,57 +3543,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C37" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D37" t="n">
         <v>85.8</v>
       </c>
-      <c r="C37" t="n">
-        <v>89</v>
-      </c>
-      <c r="D37" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E37" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F37" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H37" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I37" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J37" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K37" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L37" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N37" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O37" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3599,24 +3601,22 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
+      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
@@ -3627,63 +3627,65 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C38" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E38" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H38" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I38" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J38" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K38" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L38" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M38" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N38" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O38" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
@@ -3692,7 +3694,7 @@
       </c>
       <c r="S38" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3709,66 +3711,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C39" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D39" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E39" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H39" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I39" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L39" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N39" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q39" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
@@ -3800,69 +3800,63 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C40" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D40" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E40" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F40" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H40" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I40" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J40" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K40" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L40" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M40" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N40" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O40" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>91.45</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3884,50 +3878,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C41" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D41" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H41" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I41" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K41" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L41" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N41" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O41" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3938,13 +3932,15 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3957,55 +3953,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C42" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D42" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E42" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H42" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I42" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J42" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K42" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L42" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N42" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4018,13 +4018,11 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4039,57 +4037,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C43" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E43" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H43" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I43" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J43" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K43" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L43" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N43" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O43" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4102,76 +4100,78 @@
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C44" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D44" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E44" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F44" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H44" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I44" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L44" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M44" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O44" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4212,50 +4212,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E45" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F45" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H45" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I45" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K45" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L45" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M45" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N45" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O45" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4268,23 +4268,17 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
       </c>
       <c r="W45" s="9" t="inlineStr">
         <is>
@@ -4296,50 +4290,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C46" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D46" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E46" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F46" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H46" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I46" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K46" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N46" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O46" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4355,8 +4349,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4374,50 +4370,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C47" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D47" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E47" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F47" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H47" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I47" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J47" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K47" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L47" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M47" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N47" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O47" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4425,18 +4421,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4449,55 +4445,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C48" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D48" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E48" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F48" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H48" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I48" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J48" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K48" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M48" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O48" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4505,18 +4505,18 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R48" s="6" t="n">
+        <v/>
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4529,59 +4529,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C49" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E49" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F49" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H49" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I49" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J49" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K49" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M49" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O49" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4599,11 +4595,13 @@
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4618,50 +4616,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C50" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D50" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E50" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F50" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H50" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I50" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J50" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K50" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L50" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M50" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N50" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4684,11 +4682,13 @@
       </c>
       <c r="U50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
@@ -4700,50 +4700,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C51" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D51" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E51" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F51" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H51" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I51" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J51" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K51" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M51" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N51" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O51" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4754,80 +4754,78 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C52" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D52" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E52" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H52" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I52" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J52" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K52" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L52" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M52" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N52" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O52" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4838,13 +4836,15 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4857,59 +4857,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C53" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D53" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E53" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F53" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H53" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I53" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J53" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K53" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M53" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N53" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O53" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4922,7 +4918,7 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T53" s="8" t="inlineStr">
@@ -4930,8 +4926,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4946,75 +4944,75 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C54" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D54" t="n">
-        <v>101.21</v>
+        <v>100.97</v>
       </c>
       <c r="E54" t="n">
-        <v>105.83</v>
+        <v>102.43</v>
       </c>
       <c r="F54" t="n">
-        <v>4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0321</v>
       </c>
       <c r="H54" t="n">
-        <v>5.54</v>
+        <v>4.66</v>
       </c>
       <c r="I54" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J54" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K54" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L54" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M54" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N54" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O54" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U54" s="8" t="inlineStr">
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
@@ -5023,72 +5021,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>105.48</v>
+        <v>102.18</v>
       </c>
       <c r="C55" t="n">
-        <v>105.63</v>
+        <v>102.47</v>
       </c>
       <c r="D55" t="n">
-        <v>100.97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E55" t="n">
-        <v>102.43</v>
+        <v>101.91</v>
       </c>
       <c r="F55" t="n">
-        <v>-3.4</v>
+        <v>-0.52</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0051</v>
       </c>
       <c r="H55" t="n">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="I55" t="n">
-        <v>95.67</v>
+        <v>96.31</v>
       </c>
       <c r="J55" t="n">
-        <v>101.22</v>
+        <v>97.34</v>
       </c>
       <c r="K55" t="n">
-        <v>103.06</v>
+        <v>100.1</v>
       </c>
       <c r="L55" t="n">
-        <v>104.91</v>
+        <v>102.86</v>
       </c>
       <c r="M55" t="n">
-        <v>108.6</v>
+        <v>104.76</v>
       </c>
       <c r="N55" t="n">
-        <v>112.3</v>
+        <v>106.65</v>
       </c>
       <c r="O55" t="n">
-        <v>112.29</v>
+        <v>110.29</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5114,50 +5114,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>102.18</v>
+        <v>101.06</v>
       </c>
       <c r="C56" t="n">
-        <v>102.47</v>
+        <v>103.48</v>
       </c>
       <c r="D56" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E56" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F56" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I56" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="J56" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E56" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="F56" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="G56" s="5" t="n">
-        <v>-0.0051</v>
-      </c>
-      <c r="H56" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="I56" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="J56" t="n">
-        <v>97.34</v>
-      </c>
       <c r="K56" t="n">
-        <v>100.1</v>
+        <v>100.23</v>
       </c>
       <c r="L56" t="n">
-        <v>102.86</v>
+        <v>101.35</v>
       </c>
       <c r="M56" t="n">
-        <v>104.76</v>
+        <v>103.6</v>
       </c>
       <c r="N56" t="n">
-        <v>106.65</v>
+        <v>105.84</v>
       </c>
       <c r="O56" t="n">
-        <v>110.29</v>
+        <v>105.84</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5167,12 +5167,12 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5191,67 +5191,71 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>101.06</v>
+        <v>101</v>
       </c>
       <c r="C57" t="n">
-        <v>103.48</v>
+        <v>101.08</v>
       </c>
       <c r="D57" t="n">
-        <v>99.19</v>
+        <v>94.22</v>
       </c>
       <c r="E57" t="n">
-        <v>100.3</v>
+        <v>95.78</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.61</v>
+        <v>-4.52</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0158</v>
+        <v>-0.0451</v>
       </c>
       <c r="H57" t="n">
-        <v>4.29</v>
+        <v>6.86</v>
       </c>
       <c r="I57" t="n">
-        <v>95.73</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J57" t="n">
-        <v>99.09999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>100.23</v>
+        <v>98.16</v>
       </c>
       <c r="L57" t="n">
-        <v>101.35</v>
+        <v>100.82</v>
       </c>
       <c r="M57" t="n">
-        <v>103.6</v>
+        <v>102.45</v>
       </c>
       <c r="N57" t="n">
-        <v>105.84</v>
+        <v>104.07</v>
       </c>
       <c r="O57" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+        <v>107.77</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
@@ -5275,76 +5279,70 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>101</v>
+        <v>95.39</v>
       </c>
       <c r="C58" t="n">
-        <v>101.08</v>
+        <v>97.42</v>
       </c>
       <c r="D58" t="n">
-        <v>94.22</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>95.78</v>
+        <v>94.59</v>
       </c>
       <c r="F58" t="n">
-        <v>-4.52</v>
+        <v>-1.19</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0124</v>
       </c>
       <c r="H58" t="n">
-        <v>6.86</v>
+        <v>5.02</v>
       </c>
       <c r="I58" t="n">
-        <v>94.90000000000001</v>
+        <v>87.36</v>
       </c>
       <c r="J58" t="n">
-        <v>95.48999999999999</v>
+        <v>87.98</v>
       </c>
       <c r="K58" t="n">
-        <v>98.16</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>100.82</v>
+        <v>96.72</v>
       </c>
       <c r="M58" t="n">
-        <v>102.45</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>104.07</v>
+        <v>101.7</v>
       </c>
       <c r="O58" t="n">
-        <v>107.77</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>107.94</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5370,63 +5368,67 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>95.39</v>
+        <v>89.89</v>
       </c>
       <c r="C59" t="n">
-        <v>97.42</v>
+        <v>93.06</v>
       </c>
       <c r="D59" t="n">
-        <v>92.40000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E59" t="n">
-        <v>94.59</v>
+        <v>92.16</v>
       </c>
       <c r="F59" t="n">
-        <v>-1.19</v>
+        <v>-2.43</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0257</v>
       </c>
       <c r="H59" t="n">
-        <v>5.02</v>
+        <v>4.35</v>
       </c>
       <c r="I59" t="n">
-        <v>87.36</v>
+        <v>87.38</v>
       </c>
       <c r="J59" t="n">
-        <v>87.98</v>
+        <v>89.41</v>
       </c>
       <c r="K59" t="n">
-        <v>92.34999999999999</v>
+        <v>92.08</v>
       </c>
       <c r="L59" t="n">
-        <v>96.72</v>
+        <v>94.75</v>
       </c>
       <c r="M59" t="n">
-        <v>99.20999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N59" t="n">
-        <v>101.7</v>
+        <v>99.45</v>
       </c>
       <c r="O59" t="n">
-        <v>107.94</v>
+        <v>102.44</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5452,72 +5454,70 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>89.89</v>
+        <v>92.72</v>
       </c>
       <c r="C60" t="n">
-        <v>93.06</v>
+        <v>96.78</v>
       </c>
       <c r="D60" t="n">
-        <v>88.70999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="E60" t="n">
-        <v>92.16</v>
+        <v>94.61</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.43</v>
+        <v>2.45</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0266</v>
       </c>
       <c r="H60" t="n">
-        <v>4.35</v>
+        <v>5.55</v>
       </c>
       <c r="I60" t="n">
-        <v>87.38</v>
+        <v>84.36</v>
       </c>
       <c r="J60" t="n">
-        <v>89.41</v>
+        <v>88.45</v>
       </c>
       <c r="K60" t="n">
-        <v>92.08</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>94.75</v>
+        <v>91.52</v>
       </c>
       <c r="M60" t="n">
-        <v>97.09999999999999</v>
+        <v>94.34</v>
       </c>
       <c r="N60" t="n">
-        <v>99.45</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>102.44</v>
+        <v>97.41</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
@@ -5529,59 +5529,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>92.72</v>
+        <v>94.75</v>
       </c>
       <c r="C61" t="n">
-        <v>96.78</v>
+        <v>94.75</v>
       </c>
       <c r="D61" t="n">
-        <v>91.23</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="E61" t="n">
-        <v>94.61</v>
+        <v>92.41</v>
       </c>
       <c r="F61" t="n">
-        <v>2.45</v>
+        <v>-2.2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0266</v>
+        <v>-0.0233</v>
       </c>
       <c r="H61" t="n">
-        <v>5.55</v>
+        <v>3.24</v>
       </c>
       <c r="I61" t="n">
-        <v>84.36</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="J61" t="n">
-        <v>88.45</v>
+        <v>89.36</v>
       </c>
       <c r="K61" t="n">
-        <v>89.98999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="L61" t="n">
-        <v>91.52</v>
+        <v>94.31</v>
       </c>
       <c r="M61" t="n">
-        <v>94.34</v>
+        <v>97.38</v>
       </c>
       <c r="N61" t="n">
-        <v>97.15000000000001</v>
+        <v>100.46</v>
       </c>
       <c r="O61" t="n">
-        <v>97.41</v>
+        <v>102.33</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5589,19 +5585,19 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5613,55 +5609,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>94.75</v>
+        <v>93.53</v>
       </c>
       <c r="C62" t="n">
-        <v>94.75</v>
+        <v>93.77</v>
       </c>
       <c r="D62" t="n">
-        <v>91.51000000000001</v>
+        <v>93.39</v>
       </c>
       <c r="E62" t="n">
-        <v>92.41</v>
+        <v>93.39</v>
       </c>
       <c r="F62" t="n">
-        <v>-2.2</v>
+        <v>0.98</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0233</v>
+        <v>0.0106</v>
       </c>
       <c r="H62" t="n">
-        <v>3.24</v>
+        <v>0.38</v>
       </c>
       <c r="I62" t="n">
-        <v>85.68000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="J62" t="n">
-        <v>89.36</v>
+        <v>88.81</v>
       </c>
       <c r="K62" t="n">
-        <v>91.84</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>94.31</v>
+        <v>92.77</v>
       </c>
       <c r="M62" t="n">
-        <v>97.38</v>
+        <v>94.03</v>
       </c>
       <c r="N62" t="n">
-        <v>100.46</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="O62" t="n">
-        <v>102.33</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5669,14 +5669,12 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5694,88 +5692,6 @@
         </is>
       </c>
       <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>93.58</v>
-      </c>
-      <c r="C63" t="n">
-        <v>93.8</v>
-      </c>
-      <c r="D63" t="n">
-        <v>93.16</v>
-      </c>
-      <c r="E63" t="n">
-        <v>92.41</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="I63" t="n">
-        <v>88.27</v>
-      </c>
-      <c r="J63" t="n">
-        <v>88.81</v>
-      </c>
-      <c r="K63" t="n">
-        <v>90.79000000000001</v>
-      </c>
-      <c r="L63" t="n">
-        <v>92.77</v>
-      </c>
-      <c r="M63" t="n">
-        <v>94.03</v>
-      </c>
-      <c r="N63" t="n">
-        <v>95.29000000000001</v>
-      </c>
-      <c r="O63" t="n">
-        <v>97.98999999999999</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.03</v>
+        <v>68.68000000000001</v>
       </c>
       <c r="C2" t="n">
-        <v>68.8</v>
+        <v>69.20999999999999</v>
       </c>
       <c r="D2" t="n">
-        <v>67.04000000000001</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E2" t="n">
-        <v>68.69</v>
+        <v>68.55</v>
       </c>
       <c r="F2" t="n">
-        <v>0.11</v>
+        <v>-0.14</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0016</v>
+        <v>-0.002</v>
       </c>
       <c r="H2" t="n">
-        <v>1.76</v>
+        <v>1.39</v>
       </c>
       <c r="I2" t="n">
-        <v>65.65000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="J2" t="n">
-        <v>66.06999999999999</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>67.44</v>
+        <v>67.81</v>
       </c>
       <c r="L2" t="n">
-        <v>68.81999999999999</v>
+        <v>68.31</v>
       </c>
       <c r="M2" t="n">
-        <v>69.72</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>70.61</v>
+        <v>70.84</v>
       </c>
       <c r="O2" t="n">
-        <v>72.45999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,14 +685,12 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -711,57 +709,57 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C3" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D3" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E3" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H3" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I3" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L3" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M3" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N3" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,78 +770,80 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C4" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D4" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E4" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F4" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H4" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I4" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L4" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M4" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N4" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O4" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -854,7 +854,7 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
+      <c r="S4" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -866,13 +866,11 @@
       </c>
       <c r="U4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -884,50 +882,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C5" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D5" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E5" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F5" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H5" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I5" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J5" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M5" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O5" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,23 +933,21 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -961,55 +957,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C6" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D6" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E6" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H6" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I6" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K6" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L6" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N6" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O6" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1022,7 +1022,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
+      <c r="S6" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1050,50 +1050,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C7" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D7" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E7" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I7" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J7" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L7" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M7" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N7" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O7" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1101,83 +1101,83 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
-      </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C8" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D8" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E8" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F8" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H8" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I8" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J8" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K8" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M8" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N8" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O8" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,25 +1188,21 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
@@ -1218,50 +1214,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E9" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H9" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I9" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J9" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K9" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L9" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M9" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N9" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O9" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1272,15 +1268,13 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1293,55 +1287,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C10" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D10" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E10" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F10" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I10" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J10" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K10" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L10" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M10" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N10" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O10" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,7 +1352,7 @@
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1373,57 +1371,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C11" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E11" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H11" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I11" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K11" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L11" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M11" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N11" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1436,76 +1434,78 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C12" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D12" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E12" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F12" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I12" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J12" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L12" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M12" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N12" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1513,28 +1513,26 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1546,50 +1544,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C13" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D13" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E13" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F13" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H13" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I13" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K13" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L13" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M13" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O13" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1597,12 +1595,10 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1628,50 +1624,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C14" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D14" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E14" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F14" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H14" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I14" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J14" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K14" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L14" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M14" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N14" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1682,7 +1678,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="10" t="inlineStr">
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1708,50 +1704,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C15" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D15" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F15" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H15" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I15" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J15" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K15" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L15" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N15" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1762,21 +1758,25 @@
       <c r="R15" s="6" t="n">
         <v/>
       </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1788,50 +1788,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C16" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D16" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E16" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F16" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H16" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I16" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J16" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M16" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N16" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1839,96 +1839,100 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C17" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D17" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E17" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H17" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I17" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J17" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K17" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L17" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M17" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N17" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1942,81 +1946,73 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C18" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E18" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H18" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I18" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J18" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K18" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L18" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O18" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2040,50 +2036,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D19" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E19" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I19" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J19" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K19" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L19" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M19" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N19" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2091,28 +2087,30 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2120,50 +2118,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D20" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E20" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F20" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H20" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I20" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J20" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K20" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L20" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N20" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O20" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2176,18 +2174,14 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2197,55 +2191,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C21" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D21" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E21" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H21" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I21" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J21" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K21" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M21" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N21" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O21" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2253,19 +2251,25 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2284,56 +2288,58 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D22" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F22" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H22" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I22" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J22" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N22" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O22" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
@@ -2342,18 +2348,14 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2365,64 +2367,66 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D23" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E23" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H23" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I23" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J23" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N23" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O23" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q23" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
@@ -2430,13 +2434,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2444,89 +2450,81 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C24" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D24" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H24" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I24" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J24" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L24" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N24" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2539,59 +2537,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C25" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D25" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H25" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I25" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J25" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K25" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M25" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N25" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O25" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2604,14 +2598,18 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2621,55 +2619,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C26" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D26" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E26" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H26" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I26" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J26" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K26" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M26" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N26" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O26" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2680,20 +2682,18 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2712,50 +2712,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C27" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D27" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F27" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H27" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I27" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L27" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M27" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N27" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O27" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2766,80 +2766,80 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W27" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D28" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E28" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F28" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H28" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I28" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J28" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K28" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L28" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M28" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N28" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2850,25 +2850,21 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
+      <c r="S28" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2880,50 +2876,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F29" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H29" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I29" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L29" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N29" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O29" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2934,15 +2930,13 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2955,68 +2949,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C30" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D30" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E30" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F30" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H30" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I30" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J30" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K30" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N30" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O30" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+        <v>86.3</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3028,88 +3032,80 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C31" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H31" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I31" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J31" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L31" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M31" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N31" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N31" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O31" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3121,55 +3117,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C32" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E32" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F32" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H32" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I32" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J32" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M32" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3180,19 +3180,21 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
+      <c r="S32" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
@@ -3203,57 +3205,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C33" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D33" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F33" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H33" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I33" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J33" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L33" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M33" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N33" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O33" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3264,20 +3266,16 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3296,50 +3294,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C34" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D34" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F34" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H34" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I34" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J34" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K34" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N34" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3350,16 +3348,20 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3371,57 +3373,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C35" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D35" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F35" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H35" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I35" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J35" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K35" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L35" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N35" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3432,7 +3434,7 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3457,57 +3459,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C36" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D36" t="n">
         <v>85.8</v>
       </c>
-      <c r="C36" t="n">
-        <v>89</v>
-      </c>
-      <c r="D36" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E36" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F36" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H36" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I36" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J36" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K36" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L36" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N36" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O36" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3515,23 +3517,21 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3543,72 +3543,74 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C37" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E37" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H37" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I37" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J37" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K37" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L37" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M37" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N37" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O37" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3625,66 +3627,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C38" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D38" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E38" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H38" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I38" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L38" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N38" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q38" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
@@ -3692,7 +3692,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3716,69 +3716,63 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C39" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D39" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E39" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F39" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H39" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I39" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J39" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K39" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L39" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M39" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N39" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O39" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>91.45</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3800,50 +3794,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C40" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D40" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H40" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I40" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K40" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L40" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N40" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O40" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3856,11 +3850,13 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3873,55 +3869,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C41" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D41" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E41" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H41" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I41" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J41" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K41" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L41" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N41" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3932,15 +3932,13 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3955,57 +3953,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C42" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E42" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H42" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I42" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J42" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K42" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L42" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N42" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O42" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4016,78 +4014,80 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W42" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C43" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D43" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E43" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F43" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H43" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I43" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L43" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M43" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O43" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4098,7 +4098,7 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
+      <c r="S43" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4128,50 +4128,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D44" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E44" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F44" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I44" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K44" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L44" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M44" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N44" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O44" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4182,25 +4182,19 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
       </c>
       <c r="W44" s="9" t="inlineStr">
         <is>
@@ -4212,50 +4206,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C45" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D45" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E45" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F45" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H45" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I45" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K45" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N45" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O45" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4266,13 +4260,15 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
+      <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4290,50 +4286,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C46" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D46" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E46" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F46" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H46" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I46" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J46" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K46" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L46" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M46" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N46" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O46" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4341,18 +4337,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4365,55 +4361,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C47" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D47" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E47" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F47" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H47" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I47" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J47" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K47" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O47" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4421,18 +4421,18 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4445,59 +4445,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C48" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E48" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F48" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H48" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I48" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K48" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M48" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N48" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O48" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4508,18 +4504,20 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4534,50 +4532,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C49" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D49" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E49" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F49" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H49" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I49" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J49" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K49" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L49" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M49" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N49" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O49" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4588,7 +4586,7 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4600,11 +4598,13 @@
       </c>
       <c r="U49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
@@ -4616,50 +4616,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C50" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D50" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E50" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F50" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H50" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I50" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J50" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K50" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M50" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N50" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O50" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4672,78 +4672,76 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C51" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D51" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E51" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H51" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I51" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J51" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K51" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L51" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M51" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N51" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O51" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4756,11 +4754,13 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4773,59 +4773,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C52" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D52" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E52" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F52" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H52" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I52" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J52" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K52" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M52" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N52" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O52" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4836,9 +4832,9 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T52" s="8" t="inlineStr">
@@ -4846,8 +4842,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
@@ -4862,74 +4860,74 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C53" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D53" t="n">
-        <v>101.21</v>
+        <v>100.97</v>
       </c>
       <c r="E53" t="n">
-        <v>105.83</v>
+        <v>102.43</v>
       </c>
       <c r="F53" t="n">
-        <v>4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0321</v>
       </c>
       <c r="H53" t="n">
-        <v>5.54</v>
+        <v>4.66</v>
       </c>
       <c r="I53" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J53" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K53" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L53" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M53" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N53" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O53" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4939,72 +4937,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>105.48</v>
+        <v>102.18</v>
       </c>
       <c r="C54" t="n">
-        <v>105.63</v>
+        <v>102.47</v>
       </c>
       <c r="D54" t="n">
-        <v>100.97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E54" t="n">
-        <v>102.43</v>
+        <v>101.91</v>
       </c>
       <c r="F54" t="n">
-        <v>-3.4</v>
+        <v>-0.52</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0051</v>
       </c>
       <c r="H54" t="n">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="I54" t="n">
-        <v>95.67</v>
+        <v>96.31</v>
       </c>
       <c r="J54" t="n">
-        <v>101.22</v>
+        <v>97.34</v>
       </c>
       <c r="K54" t="n">
-        <v>103.06</v>
+        <v>100.1</v>
       </c>
       <c r="L54" t="n">
-        <v>104.91</v>
+        <v>102.86</v>
       </c>
       <c r="M54" t="n">
-        <v>108.6</v>
+        <v>104.76</v>
       </c>
       <c r="N54" t="n">
-        <v>112.3</v>
+        <v>106.65</v>
       </c>
       <c r="O54" t="n">
-        <v>112.29</v>
+        <v>110.29</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5030,50 +5030,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>102.18</v>
+        <v>101.06</v>
       </c>
       <c r="C55" t="n">
-        <v>102.47</v>
+        <v>103.48</v>
       </c>
       <c r="D55" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E55" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F55" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="H55" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I55" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="J55" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E55" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="F55" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="G55" s="5" t="n">
-        <v>-0.0051</v>
-      </c>
-      <c r="H55" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="I55" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="J55" t="n">
-        <v>97.34</v>
-      </c>
       <c r="K55" t="n">
-        <v>100.1</v>
+        <v>100.23</v>
       </c>
       <c r="L55" t="n">
-        <v>102.86</v>
+        <v>101.35</v>
       </c>
       <c r="M55" t="n">
-        <v>104.76</v>
+        <v>103.6</v>
       </c>
       <c r="N55" t="n">
-        <v>106.65</v>
+        <v>105.84</v>
       </c>
       <c r="O55" t="n">
-        <v>110.29</v>
+        <v>105.84</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5107,70 +5107,74 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>101.06</v>
+        <v>101</v>
       </c>
       <c r="C56" t="n">
-        <v>103.48</v>
+        <v>101.08</v>
       </c>
       <c r="D56" t="n">
-        <v>99.19</v>
+        <v>94.22</v>
       </c>
       <c r="E56" t="n">
-        <v>100.3</v>
+        <v>95.78</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.61</v>
+        <v>-4.52</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0158</v>
+        <v>-0.0451</v>
       </c>
       <c r="H56" t="n">
-        <v>4.29</v>
+        <v>6.86</v>
       </c>
       <c r="I56" t="n">
-        <v>95.73</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J56" t="n">
-        <v>99.09999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="K56" t="n">
-        <v>100.23</v>
+        <v>98.16</v>
       </c>
       <c r="L56" t="n">
-        <v>101.35</v>
+        <v>100.82</v>
       </c>
       <c r="M56" t="n">
-        <v>103.6</v>
+        <v>102.45</v>
       </c>
       <c r="N56" t="n">
-        <v>105.84</v>
+        <v>104.07</v>
       </c>
       <c r="O56" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+        <v>107.77</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5191,76 +5195,70 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>101</v>
+        <v>95.39</v>
       </c>
       <c r="C57" t="n">
-        <v>101.08</v>
+        <v>97.42</v>
       </c>
       <c r="D57" t="n">
-        <v>94.22</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E57" t="n">
-        <v>95.78</v>
+        <v>94.59</v>
       </c>
       <c r="F57" t="n">
-        <v>-4.52</v>
+        <v>-1.19</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0124</v>
       </c>
       <c r="H57" t="n">
-        <v>6.86</v>
+        <v>5.02</v>
       </c>
       <c r="I57" t="n">
-        <v>94.90000000000001</v>
+        <v>87.36</v>
       </c>
       <c r="J57" t="n">
-        <v>95.48999999999999</v>
+        <v>87.98</v>
       </c>
       <c r="K57" t="n">
-        <v>98.16</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>100.82</v>
+        <v>96.72</v>
       </c>
       <c r="M57" t="n">
-        <v>102.45</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>104.07</v>
+        <v>101.7</v>
       </c>
       <c r="O57" t="n">
-        <v>107.77</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>107.94</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5286,63 +5284,67 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>95.39</v>
+        <v>89.89</v>
       </c>
       <c r="C58" t="n">
-        <v>97.42</v>
+        <v>93.06</v>
       </c>
       <c r="D58" t="n">
-        <v>92.40000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>94.59</v>
+        <v>92.16</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.19</v>
+        <v>-2.43</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0257</v>
       </c>
       <c r="H58" t="n">
-        <v>5.02</v>
+        <v>4.35</v>
       </c>
       <c r="I58" t="n">
-        <v>87.36</v>
+        <v>87.38</v>
       </c>
       <c r="J58" t="n">
-        <v>87.98</v>
+        <v>89.41</v>
       </c>
       <c r="K58" t="n">
-        <v>92.34999999999999</v>
+        <v>92.08</v>
       </c>
       <c r="L58" t="n">
-        <v>96.72</v>
+        <v>94.75</v>
       </c>
       <c r="M58" t="n">
-        <v>99.20999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N58" t="n">
-        <v>101.7</v>
+        <v>99.45</v>
       </c>
       <c r="O58" t="n">
-        <v>107.94</v>
+        <v>102.44</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5368,72 +5370,70 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>89.89</v>
+        <v>92.72</v>
       </c>
       <c r="C59" t="n">
-        <v>93.06</v>
+        <v>96.78</v>
       </c>
       <c r="D59" t="n">
-        <v>88.70999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="E59" t="n">
-        <v>92.16</v>
+        <v>94.61</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.43</v>
+        <v>2.45</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0266</v>
       </c>
       <c r="H59" t="n">
-        <v>4.35</v>
+        <v>5.55</v>
       </c>
       <c r="I59" t="n">
-        <v>87.38</v>
+        <v>84.36</v>
       </c>
       <c r="J59" t="n">
-        <v>89.41</v>
+        <v>88.45</v>
       </c>
       <c r="K59" t="n">
-        <v>92.08</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>94.75</v>
+        <v>91.52</v>
       </c>
       <c r="M59" t="n">
-        <v>97.09999999999999</v>
+        <v>94.34</v>
       </c>
       <c r="N59" t="n">
-        <v>99.45</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>102.44</v>
+        <v>97.41</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5445,59 +5445,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>92.72</v>
+        <v>94.75</v>
       </c>
       <c r="C60" t="n">
-        <v>96.78</v>
+        <v>94.75</v>
       </c>
       <c r="D60" t="n">
-        <v>91.23</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="E60" t="n">
-        <v>94.61</v>
+        <v>92.41</v>
       </c>
       <c r="F60" t="n">
-        <v>2.45</v>
+        <v>-2.2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0266</v>
+        <v>-0.0233</v>
       </c>
       <c r="H60" t="n">
-        <v>5.55</v>
+        <v>3.24</v>
       </c>
       <c r="I60" t="n">
-        <v>84.36</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="J60" t="n">
-        <v>88.45</v>
+        <v>89.36</v>
       </c>
       <c r="K60" t="n">
-        <v>89.98999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="L60" t="n">
-        <v>91.52</v>
+        <v>94.31</v>
       </c>
       <c r="M60" t="n">
-        <v>94.34</v>
+        <v>97.38</v>
       </c>
       <c r="N60" t="n">
-        <v>97.15000000000001</v>
+        <v>100.46</v>
       </c>
       <c r="O60" t="n">
-        <v>97.41</v>
+        <v>102.33</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5505,18 +5501,18 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5529,55 +5525,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>94.75</v>
+        <v>93.58</v>
       </c>
       <c r="C61" t="n">
-        <v>94.75</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D61" t="n">
-        <v>91.51000000000001</v>
+        <v>91.25</v>
       </c>
       <c r="E61" t="n">
-        <v>92.41</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F61" t="n">
-        <v>-2.2</v>
+        <v>0.19</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0233</v>
+        <v>0.0021</v>
       </c>
       <c r="H61" t="n">
-        <v>3.24</v>
+        <v>5.29</v>
       </c>
       <c r="I61" t="n">
-        <v>85.68000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="J61" t="n">
-        <v>89.36</v>
+        <v>88.81</v>
       </c>
       <c r="K61" t="n">
-        <v>91.84</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>94.31</v>
+        <v>92.77</v>
       </c>
       <c r="M61" t="n">
-        <v>97.38</v>
+        <v>94.03</v>
       </c>
       <c r="N61" t="n">
-        <v>100.46</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="O61" t="n">
-        <v>102.33</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5585,21 +5585,23 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5611,57 +5613,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>93.53</v>
+        <v>89</v>
       </c>
       <c r="C62" t="n">
-        <v>93.77</v>
+        <v>89.06999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>93.39</v>
+        <v>88.58</v>
       </c>
       <c r="E62" t="n">
-        <v>93.39</v>
+        <v>88.66</v>
       </c>
       <c r="F62" t="n">
-        <v>0.98</v>
+        <v>-3.94</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0106</v>
+        <v>-0.0425</v>
       </c>
       <c r="H62" t="n">
-        <v>0.38</v>
+        <v>0.49</v>
       </c>
       <c r="I62" t="n">
-        <v>88.27</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>88.81</v>
+        <v>86.66</v>
       </c>
       <c r="K62" t="n">
-        <v>90.79000000000001</v>
+        <v>89.95</v>
       </c>
       <c r="L62" t="n">
-        <v>92.77</v>
+        <v>93.25</v>
       </c>
       <c r="M62" t="n">
-        <v>94.03</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="N62" t="n">
-        <v>95.29000000000001</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="O62" t="n">
-        <v>97.98999999999999</v>
+        <v>101.83</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5669,12 +5671,14 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5693,7 +5697,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.68000000000001</v>
+        <v>68.58</v>
       </c>
       <c r="C2" t="n">
-        <v>69.20999999999999</v>
+        <v>72.51000000000001</v>
       </c>
       <c r="D2" t="n">
-        <v>67.81999999999999</v>
+        <v>68.58</v>
       </c>
       <c r="E2" t="n">
-        <v>68.55</v>
+        <v>70.44</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.14</v>
+        <v>1.89</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.002</v>
+        <v>0.0276</v>
       </c>
       <c r="H2" t="n">
-        <v>1.39</v>
+        <v>3.93</v>
       </c>
       <c r="I2" t="n">
-        <v>65.28</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>67.31999999999999</v>
+        <v>67.18000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>67.81</v>
+        <v>67.86</v>
       </c>
       <c r="L2" t="n">
-        <v>68.31</v>
+        <v>68.53</v>
       </c>
       <c r="M2" t="n">
-        <v>69.56999999999999</v>
+        <v>69.25</v>
       </c>
       <c r="N2" t="n">
-        <v>70.84</v>
+        <v>69.95999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>70.56</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,76 +690,78 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C3" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D3" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E3" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F3" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H3" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I3" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L3" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N3" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -782,13 +784,11 @@
       </c>
       <c r="U3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -800,50 +800,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C4" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D4" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E4" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H4" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I4" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J4" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L4" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M4" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,24 +851,22 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
@@ -877,55 +875,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C5" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D5" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E5" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I5" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K5" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L5" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N5" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O5" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -966,50 +968,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C6" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D6" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E6" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I6" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J6" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L6" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M6" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N6" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O6" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1017,83 +1019,83 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
-      </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C7" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D7" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E7" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F7" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H7" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I7" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J7" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K7" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M7" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N7" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O7" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,18 +1113,14 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1134,50 +1132,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E8" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H8" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I8" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J8" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K8" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L8" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M8" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N8" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O8" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1190,13 +1188,11 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1209,55 +1205,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C9" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D9" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E9" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F9" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I9" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J9" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K9" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L9" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M9" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N9" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O9" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1268,9 +1268,9 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1289,57 +1289,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C10" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E10" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H10" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I10" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K10" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L10" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M10" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N10" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O10" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1350,78 +1350,80 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D11" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E11" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F11" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H11" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I11" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L11" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M11" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N11" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1429,8 +1431,10 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
@@ -1439,18 +1443,14 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1462,50 +1462,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C12" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D12" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E12" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F12" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H12" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I12" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J12" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K12" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L12" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M12" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N12" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O12" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1513,10 +1513,8 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R12" s="6" t="n">
+        <v/>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
@@ -1544,50 +1542,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C13" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D13" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E13" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F13" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H13" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I13" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J13" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K13" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L13" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M13" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N13" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1624,50 +1622,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C14" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D14" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F14" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H14" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I14" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J14" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K14" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L14" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N14" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1685,14 +1683,18 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1704,50 +1706,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C15" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D15" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F15" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H15" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I15" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J15" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M15" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N15" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1755,93 +1757,97 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
+      </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C16" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D16" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E16" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H16" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I16" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J16" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K16" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L16" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M16" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N16" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
@@ -1858,78 +1864,70 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C17" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E17" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F17" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H17" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I17" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J17" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K17" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L17" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O17" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
@@ -1956,50 +1954,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E18" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H18" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I18" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J18" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K18" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L18" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N18" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2007,28 +2005,30 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2036,50 +2036,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D19" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E19" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F19" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H19" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I19" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J19" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K19" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L19" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N19" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O19" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2090,20 +2090,16 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2113,55 +2109,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C20" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D20" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E20" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H20" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I20" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J20" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K20" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M20" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O20" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2169,19 +2169,25 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2200,76 +2206,74 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D21" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F21" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H21" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I21" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J21" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N21" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O21" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2281,64 +2285,66 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D22" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E22" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H22" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I22" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J22" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N22" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O22" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q22" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
@@ -2351,8 +2357,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2360,89 +2368,81 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C23" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D23" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H23" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I23" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J23" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L23" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N23" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O23" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2455,59 +2455,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C24" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D24" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H24" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I24" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J24" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K24" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M24" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N24" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O24" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2518,16 +2514,20 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2537,55 +2537,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C25" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D25" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E25" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H25" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I25" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J25" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K25" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M25" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N25" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O25" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2603,13 +2607,11 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2628,50 +2630,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C26" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D26" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F26" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H26" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I26" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L26" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M26" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N26" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2689,73 +2691,73 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D27" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E27" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F27" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H27" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I27" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J27" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K27" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L27" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M27" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N27" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2773,18 +2775,14 @@
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2796,50 +2794,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E28" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F28" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H28" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I28" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L28" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N28" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O28" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2852,13 +2850,11 @@
       </c>
       <c r="S28" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2871,68 +2867,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C29" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D29" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E29" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F29" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H29" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I29" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J29" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K29" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O29" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>86.3</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2944,88 +2950,80 @@
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W29" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C30" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H30" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I30" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J30" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L30" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M30" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N30" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N30" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O30" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
@@ -3037,55 +3035,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C31" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D31" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E31" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F31" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H31" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I31" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K31" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M31" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3103,12 +3105,14 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
@@ -3119,57 +3123,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C32" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D32" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F32" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H32" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I32" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J32" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L32" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M32" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N32" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O32" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3182,18 +3186,14 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3212,50 +3212,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C33" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D33" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F33" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H33" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I33" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J33" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K33" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N33" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O33" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3268,14 +3268,18 @@
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3287,57 +3291,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C34" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D34" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F34" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H34" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I34" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J34" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K34" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L34" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N34" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3373,57 +3377,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C35" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D35" t="n">
         <v>85.8</v>
       </c>
-      <c r="C35" t="n">
-        <v>89</v>
-      </c>
-      <c r="D35" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E35" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F35" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I35" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J35" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K35" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L35" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N35" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O35" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3431,24 +3435,22 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3459,63 +3461,65 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C36" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E36" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H36" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I36" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J36" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K36" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L36" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M36" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N36" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O36" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
@@ -3524,7 +3528,7 @@
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3541,66 +3545,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C37" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D37" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E37" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H37" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I37" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L37" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N37" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
@@ -3632,69 +3634,63 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C38" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D38" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E38" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F38" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H38" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I38" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J38" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K38" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L38" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M38" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N38" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O38" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>91.45</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3716,50 +3712,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C39" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D39" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H39" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I39" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J39" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K39" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L39" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N39" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O39" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3770,13 +3766,15 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3789,55 +3787,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C40" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D40" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E40" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H40" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I40" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J40" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K40" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L40" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N40" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3850,13 +3852,11 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3871,57 +3871,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C41" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E41" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H41" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I41" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J41" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K41" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L41" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N41" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O41" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3934,76 +3934,78 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W41" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W41" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C42" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D42" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E42" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F42" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H42" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I42" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L42" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M42" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O42" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4044,50 +4046,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C43" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D43" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E43" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F43" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I43" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L43" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M43" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N43" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O43" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4100,23 +4102,17 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V43" s="8" t="n">
+        <v/>
       </c>
       <c r="W43" s="9" t="inlineStr">
         <is>
@@ -4128,50 +4124,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C44" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D44" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E44" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F44" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H44" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I44" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J44" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K44" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N44" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O44" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4187,8 +4183,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4206,50 +4204,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C45" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D45" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E45" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F45" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H45" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I45" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J45" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K45" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L45" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M45" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N45" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O45" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4257,18 +4255,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4281,55 +4279,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C46" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D46" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E46" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F46" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H46" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I46" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J46" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K46" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M46" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O46" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4337,18 +4339,18 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4361,59 +4363,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C47" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E47" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F47" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H47" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I47" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J47" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K47" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L47" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M47" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O47" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4431,11 +4429,13 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4450,50 +4450,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C48" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D48" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E48" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F48" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H48" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I48" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J48" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K48" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L48" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M48" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N48" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O48" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4516,11 +4516,13 @@
       </c>
       <c r="U48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4532,50 +4534,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C49" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D49" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E49" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F49" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H49" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I49" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J49" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K49" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M49" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N49" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O49" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4586,80 +4588,78 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C50" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D50" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E50" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H50" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I50" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J50" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K50" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L50" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M50" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N50" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O50" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4670,13 +4670,15 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4689,59 +4691,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C51" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D51" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E51" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F51" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H51" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I51" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J51" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K51" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L51" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M51" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N51" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O51" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4754,7 +4752,7 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T51" s="8" t="inlineStr">
@@ -4762,8 +4760,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4778,75 +4778,75 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C52" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D52" t="n">
-        <v>101.21</v>
+        <v>100.97</v>
       </c>
       <c r="E52" t="n">
-        <v>105.83</v>
+        <v>102.43</v>
       </c>
       <c r="F52" t="n">
-        <v>4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0321</v>
       </c>
       <c r="H52" t="n">
-        <v>5.54</v>
+        <v>4.66</v>
       </c>
       <c r="I52" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J52" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K52" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L52" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M52" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N52" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O52" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U52" s="8" t="inlineStr">
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
@@ -4855,72 +4855,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>105.48</v>
+        <v>102.18</v>
       </c>
       <c r="C53" t="n">
-        <v>105.63</v>
+        <v>102.47</v>
       </c>
       <c r="D53" t="n">
-        <v>100.97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E53" t="n">
-        <v>102.43</v>
+        <v>101.91</v>
       </c>
       <c r="F53" t="n">
-        <v>-3.4</v>
+        <v>-0.52</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0051</v>
       </c>
       <c r="H53" t="n">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="I53" t="n">
-        <v>95.67</v>
+        <v>96.31</v>
       </c>
       <c r="J53" t="n">
-        <v>101.22</v>
+        <v>97.34</v>
       </c>
       <c r="K53" t="n">
-        <v>103.06</v>
+        <v>100.1</v>
       </c>
       <c r="L53" t="n">
-        <v>104.91</v>
+        <v>102.86</v>
       </c>
       <c r="M53" t="n">
-        <v>108.6</v>
+        <v>104.76</v>
       </c>
       <c r="N53" t="n">
-        <v>112.3</v>
+        <v>106.65</v>
       </c>
       <c r="O53" t="n">
-        <v>112.29</v>
+        <v>110.29</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4946,50 +4948,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>102.18</v>
+        <v>101.06</v>
       </c>
       <c r="C54" t="n">
-        <v>102.47</v>
+        <v>103.48</v>
       </c>
       <c r="D54" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E54" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F54" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G54" s="5" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I54" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="J54" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E54" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="F54" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="G54" s="5" t="n">
-        <v>-0.0051</v>
-      </c>
-      <c r="H54" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="I54" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="J54" t="n">
-        <v>97.34</v>
-      </c>
       <c r="K54" t="n">
-        <v>100.1</v>
+        <v>100.23</v>
       </c>
       <c r="L54" t="n">
-        <v>102.86</v>
+        <v>101.35</v>
       </c>
       <c r="M54" t="n">
-        <v>104.76</v>
+        <v>103.6</v>
       </c>
       <c r="N54" t="n">
-        <v>106.65</v>
+        <v>105.84</v>
       </c>
       <c r="O54" t="n">
-        <v>110.29</v>
+        <v>105.84</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -4999,12 +5001,12 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5023,67 +5025,71 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>101.06</v>
+        <v>101</v>
       </c>
       <c r="C55" t="n">
-        <v>103.48</v>
+        <v>101.08</v>
       </c>
       <c r="D55" t="n">
-        <v>99.19</v>
+        <v>94.22</v>
       </c>
       <c r="E55" t="n">
-        <v>100.3</v>
+        <v>95.78</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.61</v>
+        <v>-4.52</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0158</v>
+        <v>-0.0451</v>
       </c>
       <c r="H55" t="n">
-        <v>4.29</v>
+        <v>6.86</v>
       </c>
       <c r="I55" t="n">
-        <v>95.73</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J55" t="n">
-        <v>99.09999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>100.23</v>
+        <v>98.16</v>
       </c>
       <c r="L55" t="n">
-        <v>101.35</v>
+        <v>100.82</v>
       </c>
       <c r="M55" t="n">
-        <v>103.6</v>
+        <v>102.45</v>
       </c>
       <c r="N55" t="n">
-        <v>105.84</v>
+        <v>104.07</v>
       </c>
       <c r="O55" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+        <v>107.77</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
@@ -5107,76 +5113,70 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>101</v>
+        <v>95.39</v>
       </c>
       <c r="C56" t="n">
-        <v>101.08</v>
+        <v>97.42</v>
       </c>
       <c r="D56" t="n">
-        <v>94.22</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E56" t="n">
-        <v>95.78</v>
+        <v>94.59</v>
       </c>
       <c r="F56" t="n">
-        <v>-4.52</v>
+        <v>-1.19</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0124</v>
       </c>
       <c r="H56" t="n">
-        <v>6.86</v>
+        <v>5.02</v>
       </c>
       <c r="I56" t="n">
-        <v>94.90000000000001</v>
+        <v>87.36</v>
       </c>
       <c r="J56" t="n">
-        <v>95.48999999999999</v>
+        <v>87.98</v>
       </c>
       <c r="K56" t="n">
-        <v>98.16</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>100.82</v>
+        <v>96.72</v>
       </c>
       <c r="M56" t="n">
-        <v>102.45</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>104.07</v>
+        <v>101.7</v>
       </c>
       <c r="O56" t="n">
-        <v>107.77</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>107.94</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5202,63 +5202,67 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>95.39</v>
+        <v>89.89</v>
       </c>
       <c r="C57" t="n">
-        <v>97.42</v>
+        <v>93.06</v>
       </c>
       <c r="D57" t="n">
-        <v>92.40000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E57" t="n">
-        <v>94.59</v>
+        <v>92.16</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.19</v>
+        <v>-2.43</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0257</v>
       </c>
       <c r="H57" t="n">
-        <v>5.02</v>
+        <v>4.35</v>
       </c>
       <c r="I57" t="n">
-        <v>87.36</v>
+        <v>87.38</v>
       </c>
       <c r="J57" t="n">
-        <v>87.98</v>
+        <v>89.41</v>
       </c>
       <c r="K57" t="n">
-        <v>92.34999999999999</v>
+        <v>92.08</v>
       </c>
       <c r="L57" t="n">
-        <v>96.72</v>
+        <v>94.75</v>
       </c>
       <c r="M57" t="n">
-        <v>99.20999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N57" t="n">
-        <v>101.7</v>
+        <v>99.45</v>
       </c>
       <c r="O57" t="n">
-        <v>107.94</v>
+        <v>102.44</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5284,72 +5288,70 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>89.89</v>
+        <v>92.72</v>
       </c>
       <c r="C58" t="n">
-        <v>93.06</v>
+        <v>96.78</v>
       </c>
       <c r="D58" t="n">
-        <v>88.70999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="E58" t="n">
-        <v>92.16</v>
+        <v>94.61</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.43</v>
+        <v>2.45</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0266</v>
       </c>
       <c r="H58" t="n">
-        <v>4.35</v>
+        <v>5.55</v>
       </c>
       <c r="I58" t="n">
-        <v>87.38</v>
+        <v>84.36</v>
       </c>
       <c r="J58" t="n">
-        <v>89.41</v>
+        <v>88.45</v>
       </c>
       <c r="K58" t="n">
-        <v>92.08</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="L58" t="n">
-        <v>94.75</v>
+        <v>91.52</v>
       </c>
       <c r="M58" t="n">
-        <v>97.09999999999999</v>
+        <v>94.34</v>
       </c>
       <c r="N58" t="n">
-        <v>99.45</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="O58" t="n">
-        <v>102.44</v>
+        <v>97.41</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5361,59 +5363,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>92.72</v>
+        <v>94.75</v>
       </c>
       <c r="C59" t="n">
-        <v>96.78</v>
+        <v>94.75</v>
       </c>
       <c r="D59" t="n">
-        <v>91.23</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="E59" t="n">
-        <v>94.61</v>
+        <v>92.41</v>
       </c>
       <c r="F59" t="n">
-        <v>2.45</v>
+        <v>-2.2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0266</v>
+        <v>-0.0233</v>
       </c>
       <c r="H59" t="n">
-        <v>5.55</v>
+        <v>3.24</v>
       </c>
       <c r="I59" t="n">
-        <v>84.36</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="J59" t="n">
-        <v>88.45</v>
+        <v>89.36</v>
       </c>
       <c r="K59" t="n">
-        <v>89.98999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="L59" t="n">
-        <v>91.52</v>
+        <v>94.31</v>
       </c>
       <c r="M59" t="n">
-        <v>94.34</v>
+        <v>97.38</v>
       </c>
       <c r="N59" t="n">
-        <v>97.15000000000001</v>
+        <v>100.46</v>
       </c>
       <c r="O59" t="n">
-        <v>97.41</v>
+        <v>102.33</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5421,19 +5419,19 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+      <c r="R59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5445,55 +5443,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>94.75</v>
+        <v>93.58</v>
       </c>
       <c r="C60" t="n">
-        <v>94.75</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D60" t="n">
-        <v>91.51000000000001</v>
+        <v>91.25</v>
       </c>
       <c r="E60" t="n">
-        <v>92.41</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F60" t="n">
-        <v>-2.2</v>
+        <v>0.19</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0233</v>
+        <v>0.0021</v>
       </c>
       <c r="H60" t="n">
-        <v>3.24</v>
+        <v>5.29</v>
       </c>
       <c r="I60" t="n">
-        <v>85.68000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="J60" t="n">
-        <v>89.36</v>
+        <v>88.81</v>
       </c>
       <c r="K60" t="n">
-        <v>91.84</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="L60" t="n">
-        <v>94.31</v>
+        <v>92.77</v>
       </c>
       <c r="M60" t="n">
-        <v>97.38</v>
+        <v>94.03</v>
       </c>
       <c r="N60" t="n">
-        <v>100.46</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="O60" t="n">
-        <v>102.33</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5501,21 +5503,23 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5527,57 +5531,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>93.58</v>
+        <v>93.53</v>
       </c>
       <c r="C61" t="n">
-        <v>96.54000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>91.25</v>
+        <v>88.78</v>
       </c>
       <c r="E61" t="n">
-        <v>92.59999999999999</v>
+        <v>89.38</v>
       </c>
       <c r="F61" t="n">
-        <v>0.19</v>
+        <v>-3.22</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0348</v>
       </c>
       <c r="H61" t="n">
-        <v>5.29</v>
+        <v>5.96</v>
       </c>
       <c r="I61" t="n">
-        <v>88.27</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>88.81</v>
+        <v>86.66</v>
       </c>
       <c r="K61" t="n">
-        <v>90.79000000000001</v>
+        <v>89.95</v>
       </c>
       <c r="L61" t="n">
-        <v>92.77</v>
+        <v>93.25</v>
       </c>
       <c r="M61" t="n">
-        <v>94.03</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="N61" t="n">
-        <v>95.29000000000001</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="O61" t="n">
-        <v>97.98999999999999</v>
+        <v>101.83</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5585,23 +5589,21 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5613,57 +5615,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>89</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>89.06999999999999</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>88.58</v>
+        <v>90.23999999999999</v>
       </c>
       <c r="E62" t="n">
-        <v>88.66</v>
+        <v>90.28</v>
       </c>
       <c r="F62" t="n">
-        <v>-3.94</v>
+        <v>0.9</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0425</v>
+        <v>0.0101</v>
       </c>
       <c r="H62" t="n">
-        <v>0.49</v>
+        <v>0.27</v>
       </c>
       <c r="I62" t="n">
-        <v>85.95999999999999</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="J62" t="n">
-        <v>86.66</v>
+        <v>82.23</v>
       </c>
       <c r="K62" t="n">
-        <v>89.95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>93.25</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="M62" t="n">
-        <v>95.23999999999999</v>
+        <v>92.36</v>
       </c>
       <c r="N62" t="n">
-        <v>97.23999999999999</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="O62" t="n">
-        <v>101.83</v>
+        <v>100.7</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5671,14 +5673,12 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5697,7 +5697,7 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5626,25 +5626,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>90.40000000000001</v>
+        <v>89</v>
       </c>
       <c r="C62" t="n">
-        <v>90.51000000000001</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="D62" t="n">
-        <v>90.23999999999999</v>
+        <v>88.58</v>
       </c>
       <c r="E62" t="n">
-        <v>90.28</v>
+        <v>90.42</v>
       </c>
       <c r="F62" t="n">
-        <v>0.9</v>
+        <v>1.04</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0101</v>
+        <v>0.0116</v>
       </c>
       <c r="H62" t="n">
-        <v>0.27</v>
+        <v>3.38</v>
       </c>
       <c r="I62" t="n">
         <v>82.81999999999999</v>
@@ -5697,9 +5697,91 @@
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="C63" t="n">
+        <v>93.51000000000001</v>
+      </c>
+      <c r="D63" t="n">
+        <v>93.08</v>
+      </c>
+      <c r="E63" t="n">
+        <v>93.15000000000001</v>
+      </c>
+      <c r="F63" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0302</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I63" t="n">
+        <v>85.2</v>
+      </c>
+      <c r="J63" t="n">
+        <v>87.11</v>
+      </c>
+      <c r="K63" t="n">
+        <v>88.73</v>
+      </c>
+      <c r="L63" t="n">
+        <v>90.34</v>
+      </c>
+      <c r="M63" t="n">
+        <v>92.11</v>
+      </c>
+      <c r="N63" t="n">
+        <v>93.87</v>
+      </c>
+      <c r="O63" t="n">
+        <v>95.34</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68.58</v>
+        <v>72.38</v>
       </c>
       <c r="C2" t="n">
-        <v>72.51000000000001</v>
+        <v>76.08</v>
       </c>
       <c r="D2" t="n">
-        <v>68.58</v>
+        <v>71.75</v>
       </c>
       <c r="E2" t="n">
-        <v>70.44</v>
+        <v>73.52</v>
       </c>
       <c r="F2" t="n">
-        <v>1.89</v>
+        <v>3.08</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0276</v>
+        <v>0.0437</v>
       </c>
       <c r="H2" t="n">
-        <v>3.93</v>
+        <v>4.33</v>
       </c>
       <c r="I2" t="n">
-        <v>66.43000000000001</v>
+        <v>64.65000000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>67.18000000000001</v>
+        <v>66.45999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>67.86</v>
+        <v>68.48</v>
       </c>
       <c r="L2" t="n">
-        <v>68.53</v>
+        <v>70.48999999999999</v>
       </c>
       <c r="M2" t="n">
-        <v>69.25</v>
+        <v>72.41</v>
       </c>
       <c r="N2" t="n">
-        <v>69.95999999999999</v>
+        <v>74.31999999999999</v>
       </c>
       <c r="O2" t="n">
-        <v>70.59999999999999</v>
+        <v>76.44</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,13 +700,11 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -718,50 +716,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C3" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D3" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E3" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F3" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H3" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I3" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J3" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L3" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M3" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N3" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,24 +767,22 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
@@ -795,55 +791,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C4" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D4" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E4" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H4" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I4" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K4" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L4" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M4" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N4" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O4" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -884,50 +884,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C5" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D5" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E5" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I5" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J5" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L5" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M5" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N5" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O5" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -935,83 +935,83 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
-      </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C6" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D6" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E6" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F6" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H6" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I6" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J6" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K6" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L6" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M6" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N6" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O6" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1029,18 +1029,14 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1052,50 +1048,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C7" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E7" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H7" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I7" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J7" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K7" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L7" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M7" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N7" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O7" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,13 +1104,11 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1127,55 +1121,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C8" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D8" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E8" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F8" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I8" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J8" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K8" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L8" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M8" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N8" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O8" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1186,9 +1184,9 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1207,57 +1205,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C9" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D9" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E9" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H9" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I9" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J9" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K9" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L9" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M9" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N9" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O9" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1268,78 +1266,80 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C10" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D10" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E10" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F10" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H10" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I10" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J10" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K10" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L10" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M10" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N10" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O10" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1347,8 +1347,10 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
@@ -1357,18 +1359,14 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1380,50 +1378,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C11" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D11" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E11" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F11" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H11" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I11" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K11" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L11" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M11" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N11" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O11" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1431,10 +1429,8 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
@@ -1462,50 +1458,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C12" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D12" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E12" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F12" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H12" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I12" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J12" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K12" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L12" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M12" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N12" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1542,50 +1538,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C13" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D13" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F13" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H13" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I13" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J13" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K13" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L13" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N13" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1603,14 +1599,18 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1622,50 +1622,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C14" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D14" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F14" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H14" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I14" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J14" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M14" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N14" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O14" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1673,93 +1673,97 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
+      </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C15" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D15" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E15" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F15" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H15" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I15" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J15" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K15" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L15" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M15" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N15" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
@@ -1776,78 +1780,70 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C16" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E16" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F16" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H16" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I16" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J16" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K16" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L16" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O16" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S16" s="10" t="inlineStr">
@@ -1874,50 +1870,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E17" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I17" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J17" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K17" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L17" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N17" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1925,28 +1921,30 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1954,50 +1952,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D18" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E18" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F18" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H18" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I18" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J18" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K18" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L18" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N18" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O18" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2008,20 +2006,16 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2031,55 +2025,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C19" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D19" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E19" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H19" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I19" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J19" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K19" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M19" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N19" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O19" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2087,19 +2085,25 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2118,76 +2122,74 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D20" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F20" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H20" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I20" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J20" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N20" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O20" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2199,64 +2201,66 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D21" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E21" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H21" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I21" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J21" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N21" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O21" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q21" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
@@ -2269,8 +2273,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2278,89 +2284,81 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C22" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D22" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H22" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I22" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J22" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L22" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N22" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2373,59 +2371,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C23" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D23" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H23" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I23" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J23" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K23" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M23" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N23" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O23" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2436,16 +2430,20 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2455,55 +2453,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C24" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D24" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E24" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H24" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I24" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J24" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K24" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M24" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N24" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O24" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2521,13 +2523,11 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2546,50 +2546,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C25" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D25" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F25" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H25" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I25" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J25" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L25" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M25" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N25" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O25" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2607,73 +2607,73 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D26" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E26" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F26" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H26" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I26" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J26" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K26" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L26" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M26" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N26" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2691,18 +2691,14 @@
       </c>
       <c r="T26" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2714,50 +2710,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E27" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F27" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H27" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I27" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J27" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L27" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N27" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O27" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2770,13 +2766,11 @@
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2789,68 +2783,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C28" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D28" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E28" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F28" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H28" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I28" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J28" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K28" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L28" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O28" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+        <v>86.3</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2862,88 +2866,80 @@
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W28" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C29" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H29" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I29" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J29" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K29" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L29" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M29" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N29" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N29" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O29" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
       <c r="U29" s="8" t="n">
         <v/>
       </c>
@@ -2955,55 +2951,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C30" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D30" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E30" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F30" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H30" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I30" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J30" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L30" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M30" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3021,12 +3021,14 @@
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3037,57 +3039,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C31" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D31" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F31" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H31" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I31" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J31" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K31" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L31" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M31" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N31" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O31" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3100,18 +3102,14 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3130,50 +3128,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C32" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D32" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F32" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H32" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I32" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J32" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K32" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N32" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O32" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3186,14 +3184,18 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3205,57 +3207,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C33" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D33" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F33" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H33" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I33" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J33" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K33" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L33" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N33" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3291,57 +3293,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C34" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D34" t="n">
         <v>85.8</v>
       </c>
-      <c r="C34" t="n">
-        <v>89</v>
-      </c>
-      <c r="D34" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E34" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F34" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H34" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I34" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J34" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K34" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L34" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M34" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N34" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O34" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3349,24 +3351,22 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3377,63 +3377,65 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C35" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E35" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H35" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I35" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J35" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K35" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L35" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M35" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N35" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O35" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
@@ -3442,7 +3444,7 @@
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3459,66 +3461,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C36" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D36" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E36" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H36" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I36" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J36" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L36" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M36" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N36" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
@@ -3550,69 +3550,63 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C37" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D37" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E37" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F37" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H37" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I37" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J37" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K37" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L37" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M37" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N37" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O37" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>91.45</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3634,50 +3628,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C38" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D38" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H38" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I38" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K38" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L38" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N38" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O38" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3688,13 +3682,15 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3707,55 +3703,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C39" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D39" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E39" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H39" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I39" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J39" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K39" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L39" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N39" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3768,13 +3768,11 @@
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3789,57 +3787,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C40" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D40" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E40" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H40" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I40" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J40" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K40" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L40" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N40" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O40" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3852,76 +3850,78 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W40" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C41" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D41" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E41" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F41" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H41" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I41" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L41" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M41" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O41" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3962,50 +3962,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C42" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E42" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F42" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I42" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L42" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M42" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N42" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O42" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4018,23 +4018,17 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V42" s="8" t="n">
+        <v/>
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
@@ -4046,50 +4040,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C43" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D43" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E43" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F43" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H43" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I43" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J43" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K43" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N43" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O43" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4105,8 +4099,10 @@
           <t>↑C</t>
         </is>
       </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4124,50 +4120,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C44" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D44" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E44" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F44" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H44" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I44" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J44" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K44" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L44" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M44" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N44" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O44" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4175,18 +4171,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4199,55 +4195,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C45" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D45" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E45" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F45" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H45" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I45" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J45" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K45" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L45" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M45" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O45" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4255,18 +4255,18 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4279,59 +4279,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C46" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E46" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F46" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H46" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I46" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K46" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M46" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O46" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4349,11 +4345,13 @@
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4368,50 +4366,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C47" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D47" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E47" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F47" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H47" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I47" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J47" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K47" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L47" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M47" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N47" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O47" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4434,11 +4432,13 @@
       </c>
       <c r="U47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4450,50 +4450,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C48" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D48" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E48" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F48" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H48" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I48" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J48" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K48" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L48" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M48" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N48" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O48" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4504,80 +4504,78 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C49" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D49" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E49" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H49" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I49" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J49" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K49" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L49" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M49" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N49" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O49" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4588,13 +4586,15 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4607,59 +4607,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C50" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D50" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E50" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F50" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H50" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I50" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J50" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K50" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M50" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N50" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O50" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4672,7 +4668,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T50" s="8" t="inlineStr">
@@ -4680,8 +4676,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4696,75 +4694,75 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C51" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D51" t="n">
-        <v>101.21</v>
+        <v>100.97</v>
       </c>
       <c r="E51" t="n">
-        <v>105.83</v>
+        <v>102.43</v>
       </c>
       <c r="F51" t="n">
-        <v>4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0321</v>
       </c>
       <c r="H51" t="n">
-        <v>5.54</v>
+        <v>4.66</v>
       </c>
       <c r="I51" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J51" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K51" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L51" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M51" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N51" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O51" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
+      <c r="Q51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U51" s="8" t="inlineStr">
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
@@ -4773,72 +4771,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>105.48</v>
+        <v>102.18</v>
       </c>
       <c r="C52" t="n">
-        <v>105.63</v>
+        <v>102.47</v>
       </c>
       <c r="D52" t="n">
-        <v>100.97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>102.43</v>
+        <v>101.91</v>
       </c>
       <c r="F52" t="n">
-        <v>-3.4</v>
+        <v>-0.52</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0051</v>
       </c>
       <c r="H52" t="n">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="I52" t="n">
-        <v>95.67</v>
+        <v>96.31</v>
       </c>
       <c r="J52" t="n">
-        <v>101.22</v>
+        <v>97.34</v>
       </c>
       <c r="K52" t="n">
-        <v>103.06</v>
+        <v>100.1</v>
       </c>
       <c r="L52" t="n">
-        <v>104.91</v>
+        <v>102.86</v>
       </c>
       <c r="M52" t="n">
-        <v>108.6</v>
+        <v>104.76</v>
       </c>
       <c r="N52" t="n">
-        <v>112.3</v>
+        <v>106.65</v>
       </c>
       <c r="O52" t="n">
-        <v>112.29</v>
+        <v>110.29</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4864,50 +4864,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>102.18</v>
+        <v>101.06</v>
       </c>
       <c r="C53" t="n">
-        <v>102.47</v>
+        <v>103.48</v>
       </c>
       <c r="D53" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E53" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F53" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="H53" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I53" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="J53" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E53" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="F53" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="G53" s="5" t="n">
-        <v>-0.0051</v>
-      </c>
-      <c r="H53" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="I53" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="J53" t="n">
-        <v>97.34</v>
-      </c>
       <c r="K53" t="n">
-        <v>100.1</v>
+        <v>100.23</v>
       </c>
       <c r="L53" t="n">
-        <v>102.86</v>
+        <v>101.35</v>
       </c>
       <c r="M53" t="n">
-        <v>104.76</v>
+        <v>103.6</v>
       </c>
       <c r="N53" t="n">
-        <v>106.65</v>
+        <v>105.84</v>
       </c>
       <c r="O53" t="n">
-        <v>110.29</v>
+        <v>105.84</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4917,12 +4917,12 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4941,67 +4941,71 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>101.06</v>
+        <v>101</v>
       </c>
       <c r="C54" t="n">
-        <v>103.48</v>
+        <v>101.08</v>
       </c>
       <c r="D54" t="n">
-        <v>99.19</v>
+        <v>94.22</v>
       </c>
       <c r="E54" t="n">
-        <v>100.3</v>
+        <v>95.78</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.61</v>
+        <v>-4.52</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0158</v>
+        <v>-0.0451</v>
       </c>
       <c r="H54" t="n">
-        <v>4.29</v>
+        <v>6.86</v>
       </c>
       <c r="I54" t="n">
-        <v>95.73</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J54" t="n">
-        <v>99.09999999999999</v>
+        <v>95.48999999999999</v>
       </c>
       <c r="K54" t="n">
-        <v>100.23</v>
+        <v>98.16</v>
       </c>
       <c r="L54" t="n">
-        <v>101.35</v>
+        <v>100.82</v>
       </c>
       <c r="M54" t="n">
-        <v>103.6</v>
+        <v>102.45</v>
       </c>
       <c r="N54" t="n">
-        <v>105.84</v>
+        <v>104.07</v>
       </c>
       <c r="O54" t="n">
-        <v>105.84</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+        <v>107.77</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="10" t="inlineStr">
@@ -5025,76 +5029,70 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>101</v>
+        <v>95.39</v>
       </c>
       <c r="C55" t="n">
-        <v>101.08</v>
+        <v>97.42</v>
       </c>
       <c r="D55" t="n">
-        <v>94.22</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="E55" t="n">
-        <v>95.78</v>
+        <v>94.59</v>
       </c>
       <c r="F55" t="n">
-        <v>-4.52</v>
+        <v>-1.19</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0451</v>
+        <v>-0.0124</v>
       </c>
       <c r="H55" t="n">
-        <v>6.86</v>
+        <v>5.02</v>
       </c>
       <c r="I55" t="n">
-        <v>94.90000000000001</v>
+        <v>87.36</v>
       </c>
       <c r="J55" t="n">
-        <v>95.48999999999999</v>
+        <v>87.98</v>
       </c>
       <c r="K55" t="n">
-        <v>98.16</v>
+        <v>92.34999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>100.82</v>
+        <v>96.72</v>
       </c>
       <c r="M55" t="n">
-        <v>102.45</v>
+        <v>99.20999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>104.07</v>
+        <v>101.7</v>
       </c>
       <c r="O55" t="n">
-        <v>107.77</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>107.94</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5120,63 +5118,67 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>95.39</v>
+        <v>89.89</v>
       </c>
       <c r="C56" t="n">
-        <v>97.42</v>
+        <v>93.06</v>
       </c>
       <c r="D56" t="n">
-        <v>92.40000000000001</v>
+        <v>88.70999999999999</v>
       </c>
       <c r="E56" t="n">
-        <v>94.59</v>
+        <v>92.16</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.19</v>
+        <v>-2.43</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0124</v>
+        <v>-0.0257</v>
       </c>
       <c r="H56" t="n">
-        <v>5.02</v>
+        <v>4.35</v>
       </c>
       <c r="I56" t="n">
-        <v>87.36</v>
+        <v>87.38</v>
       </c>
       <c r="J56" t="n">
-        <v>87.98</v>
+        <v>89.41</v>
       </c>
       <c r="K56" t="n">
-        <v>92.34999999999999</v>
+        <v>92.08</v>
       </c>
       <c r="L56" t="n">
-        <v>96.72</v>
+        <v>94.75</v>
       </c>
       <c r="M56" t="n">
-        <v>99.20999999999999</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="N56" t="n">
-        <v>101.7</v>
+        <v>99.45</v>
       </c>
       <c r="O56" t="n">
-        <v>107.94</v>
+        <v>102.44</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T56" s="8" t="n">
@@ -5202,72 +5204,70 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>89.89</v>
+        <v>92.72</v>
       </c>
       <c r="C57" t="n">
-        <v>93.06</v>
+        <v>96.78</v>
       </c>
       <c r="D57" t="n">
-        <v>88.70999999999999</v>
+        <v>91.23</v>
       </c>
       <c r="E57" t="n">
-        <v>92.16</v>
+        <v>94.61</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.43</v>
+        <v>2.45</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0257</v>
+        <v>0.0266</v>
       </c>
       <c r="H57" t="n">
-        <v>4.35</v>
+        <v>5.55</v>
       </c>
       <c r="I57" t="n">
-        <v>87.38</v>
+        <v>84.36</v>
       </c>
       <c r="J57" t="n">
-        <v>89.41</v>
+        <v>88.45</v>
       </c>
       <c r="K57" t="n">
-        <v>92.08</v>
+        <v>89.98999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>94.75</v>
+        <v>91.52</v>
       </c>
       <c r="M57" t="n">
-        <v>97.09999999999999</v>
+        <v>94.34</v>
       </c>
       <c r="N57" t="n">
-        <v>99.45</v>
+        <v>97.15000000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>102.44</v>
+        <v>97.41</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5279,59 +5279,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>92.72</v>
+        <v>94.75</v>
       </c>
       <c r="C58" t="n">
-        <v>96.78</v>
+        <v>94.75</v>
       </c>
       <c r="D58" t="n">
-        <v>91.23</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>94.61</v>
+        <v>92.41</v>
       </c>
       <c r="F58" t="n">
-        <v>2.45</v>
+        <v>-2.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0266</v>
+        <v>-0.0233</v>
       </c>
       <c r="H58" t="n">
-        <v>5.55</v>
+        <v>3.24</v>
       </c>
       <c r="I58" t="n">
-        <v>84.36</v>
+        <v>85.68000000000001</v>
       </c>
       <c r="J58" t="n">
-        <v>88.45</v>
+        <v>89.36</v>
       </c>
       <c r="K58" t="n">
-        <v>89.98999999999999</v>
+        <v>91.84</v>
       </c>
       <c r="L58" t="n">
-        <v>91.52</v>
+        <v>94.31</v>
       </c>
       <c r="M58" t="n">
-        <v>94.34</v>
+        <v>97.38</v>
       </c>
       <c r="N58" t="n">
-        <v>97.15000000000001</v>
+        <v>100.46</v>
       </c>
       <c r="O58" t="n">
-        <v>97.41</v>
+        <v>102.33</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5339,19 +5335,19 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
@@ -5363,55 +5359,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>94.75</v>
+        <v>93.58</v>
       </c>
       <c r="C59" t="n">
-        <v>94.75</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="D59" t="n">
-        <v>91.51000000000001</v>
+        <v>91.25</v>
       </c>
       <c r="E59" t="n">
-        <v>92.41</v>
+        <v>92.59999999999999</v>
       </c>
       <c r="F59" t="n">
-        <v>-2.2</v>
+        <v>0.19</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0233</v>
+        <v>0.0021</v>
       </c>
       <c r="H59" t="n">
-        <v>3.24</v>
+        <v>5.29</v>
       </c>
       <c r="I59" t="n">
-        <v>85.68000000000001</v>
+        <v>88.27</v>
       </c>
       <c r="J59" t="n">
-        <v>89.36</v>
+        <v>88.81</v>
       </c>
       <c r="K59" t="n">
-        <v>91.84</v>
+        <v>90.79000000000001</v>
       </c>
       <c r="L59" t="n">
-        <v>94.31</v>
+        <v>92.77</v>
       </c>
       <c r="M59" t="n">
-        <v>97.38</v>
+        <v>94.03</v>
       </c>
       <c r="N59" t="n">
-        <v>100.46</v>
+        <v>95.29000000000001</v>
       </c>
       <c r="O59" t="n">
-        <v>102.33</v>
+        <v>97.98999999999999</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5419,21 +5419,23 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5445,57 +5447,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>93.58</v>
+        <v>93.53</v>
       </c>
       <c r="C60" t="n">
-        <v>96.54000000000001</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="D60" t="n">
-        <v>91.25</v>
+        <v>88.78</v>
       </c>
       <c r="E60" t="n">
-        <v>92.59999999999999</v>
+        <v>89.38</v>
       </c>
       <c r="F60" t="n">
-        <v>0.19</v>
+        <v>-3.22</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0021</v>
+        <v>-0.0348</v>
       </c>
       <c r="H60" t="n">
-        <v>5.29</v>
+        <v>5.96</v>
       </c>
       <c r="I60" t="n">
-        <v>88.27</v>
+        <v>85.95999999999999</v>
       </c>
       <c r="J60" t="n">
-        <v>88.81</v>
+        <v>86.66</v>
       </c>
       <c r="K60" t="n">
-        <v>90.79000000000001</v>
+        <v>89.95</v>
       </c>
       <c r="L60" t="n">
-        <v>92.77</v>
+        <v>93.25</v>
       </c>
       <c r="M60" t="n">
-        <v>94.03</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="N60" t="n">
-        <v>95.29000000000001</v>
+        <v>97.23999999999999</v>
       </c>
       <c r="O60" t="n">
-        <v>97.98999999999999</v>
+        <v>101.83</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5503,23 +5505,21 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S60" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5531,57 +5531,57 @@
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>93.53</v>
+        <v>89</v>
       </c>
       <c r="C61" t="n">
-        <v>94.73999999999999</v>
+        <v>91.95999999999999</v>
       </c>
       <c r="D61" t="n">
-        <v>88.78</v>
+        <v>88.58</v>
       </c>
       <c r="E61" t="n">
-        <v>89.38</v>
+        <v>90.42</v>
       </c>
       <c r="F61" t="n">
-        <v>-3.22</v>
+        <v>1.04</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0348</v>
+        <v>0.0116</v>
       </c>
       <c r="H61" t="n">
-        <v>5.96</v>
+        <v>3.38</v>
       </c>
       <c r="I61" t="n">
-        <v>85.95999999999999</v>
+        <v>82.81999999999999</v>
       </c>
       <c r="J61" t="n">
-        <v>86.66</v>
+        <v>82.23</v>
       </c>
       <c r="K61" t="n">
-        <v>89.95</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="L61" t="n">
-        <v>93.25</v>
+        <v>90.56999999999999</v>
       </c>
       <c r="M61" t="n">
-        <v>95.23999999999999</v>
+        <v>92.36</v>
       </c>
       <c r="N61" t="n">
-        <v>97.23999999999999</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="O61" t="n">
-        <v>101.83</v>
+        <v>100.7</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5589,14 +5589,12 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5615,57 +5613,57 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>89</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="C62" t="n">
-        <v>91.95999999999999</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="D62" t="n">
-        <v>88.58</v>
+        <v>88.79000000000001</v>
       </c>
       <c r="E62" t="n">
-        <v>90.42</v>
+        <v>92.87</v>
       </c>
       <c r="F62" t="n">
-        <v>1.04</v>
+        <v>2.45</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0271</v>
       </c>
       <c r="H62" t="n">
-        <v>3.38</v>
+        <v>4.89</v>
       </c>
       <c r="I62" t="n">
-        <v>82.81999999999999</v>
+        <v>85.2</v>
       </c>
       <c r="J62" t="n">
-        <v>82.23</v>
+        <v>87.11</v>
       </c>
       <c r="K62" t="n">
-        <v>86.40000000000001</v>
+        <v>88.73</v>
       </c>
       <c r="L62" t="n">
-        <v>90.56999999999999</v>
+        <v>90.34</v>
       </c>
       <c r="M62" t="n">
-        <v>92.36</v>
+        <v>92.11</v>
       </c>
       <c r="N62" t="n">
-        <v>94.15000000000001</v>
+        <v>93.87</v>
       </c>
       <c r="O62" t="n">
-        <v>100.7</v>
+        <v>95.34</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5676,13 +5674,15 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5695,16 +5695,12 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="n">
@@ -5714,65 +5710,65 @@
         <v>93.51000000000001</v>
       </c>
       <c r="D63" t="n">
-        <v>93.08</v>
+        <v>88.06</v>
       </c>
       <c r="E63" t="n">
-        <v>93.15000000000001</v>
+        <v>91.11</v>
       </c>
       <c r="F63" t="n">
-        <v>2.73</v>
+        <v>-1.76</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0302</v>
+        <v>-0.019</v>
       </c>
       <c r="H63" t="n">
-        <v>0.43</v>
+        <v>5.45</v>
       </c>
       <c r="I63" t="n">
-        <v>85.2</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="J63" t="n">
-        <v>87.11</v>
+        <v>88.8</v>
       </c>
       <c r="K63" t="n">
-        <v>88.73</v>
+        <v>90.43000000000001</v>
       </c>
       <c r="L63" t="n">
-        <v>90.34</v>
+        <v>92.05</v>
       </c>
       <c r="M63" t="n">
-        <v>92.11</v>
+        <v>95.31999999999999</v>
       </c>
       <c r="N63" t="n">
-        <v>93.87</v>
+        <v>98.58</v>
       </c>
       <c r="O63" t="n">
-        <v>95.34</v>
+        <v>98.56999999999999</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
       </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
+      <c r="Q63" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U63" s="8" t="inlineStr">
+      <c r="R63" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
       <c r="V63" s="8" t="n">
         <v/>
       </c>
@@ -5781,7 +5777,93 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr"/>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>91.77</v>
+      </c>
+      <c r="C64" t="n">
+        <v>91.88</v>
+      </c>
+      <c r="D64" t="n">
+        <v>91.41</v>
+      </c>
+      <c r="E64" t="n">
+        <v>91.11</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="I64" t="n">
+        <v>82.61</v>
+      </c>
+      <c r="J64" t="n">
+        <v>85.81999999999999</v>
+      </c>
+      <c r="K64" t="n">
+        <v>88.38</v>
+      </c>
+      <c r="L64" t="n">
+        <v>90.95</v>
+      </c>
+      <c r="M64" t="n">
+        <v>93.84</v>
+      </c>
+      <c r="N64" t="n">
+        <v>96.72</v>
+      </c>
+      <c r="O64" t="n">
+        <v>98.95999999999999</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/CL_daily.xlsx
+++ b/three_gate/analysis/CL_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>72.38</v>
+        <v>74.95</v>
       </c>
       <c r="C2" t="n">
-        <v>76.08</v>
+        <v>75.13</v>
       </c>
       <c r="D2" t="n">
-        <v>71.75</v>
+        <v>71.42</v>
       </c>
       <c r="E2" t="n">
-        <v>73.52</v>
+        <v>72.08</v>
       </c>
       <c r="F2" t="n">
-        <v>3.08</v>
+        <v>-1.44</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0437</v>
+        <v>-0.0196</v>
       </c>
       <c r="H2" t="n">
-        <v>4.33</v>
+        <v>3.71</v>
       </c>
       <c r="I2" t="n">
-        <v>64.65000000000001</v>
+        <v>67.42</v>
       </c>
       <c r="J2" t="n">
-        <v>66.45999999999999</v>
+        <v>68.98999999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>68.48</v>
+        <v>71.34999999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>70.48999999999999</v>
+        <v>73.72</v>
       </c>
       <c r="M2" t="n">
-        <v>72.41</v>
+        <v>75.68000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>74.31999999999999</v>
+        <v>77.65000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>76.44</v>
+        <v>80.41</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,23 +685,21 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -711,55 +709,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>74.95</v>
+        <v>71.86</v>
       </c>
       <c r="C3" t="n">
-        <v>75.13</v>
+        <v>73.16</v>
       </c>
       <c r="D3" t="n">
-        <v>71.42</v>
+        <v>70.77</v>
       </c>
       <c r="E3" t="n">
-        <v>72.08</v>
+        <v>71.41</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.44</v>
+        <v>-0.67</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0196</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="H3" t="n">
-        <v>3.71</v>
+        <v>2.39</v>
       </c>
       <c r="I3" t="n">
-        <v>67.42</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>68.98999999999999</v>
+        <v>67.77</v>
       </c>
       <c r="K3" t="n">
-        <v>71.34999999999999</v>
+        <v>70.23</v>
       </c>
       <c r="L3" t="n">
-        <v>73.72</v>
+        <v>72.68000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>75.68000000000001</v>
+        <v>73.94</v>
       </c>
       <c r="N3" t="n">
-        <v>77.65000000000001</v>
+        <v>75.19</v>
       </c>
       <c r="O3" t="n">
-        <v>80.41</v>
+        <v>78.84</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,7 +774,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -800,50 +802,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>71.86</v>
+        <v>73.69</v>
       </c>
       <c r="C4" t="n">
-        <v>73.16</v>
+        <v>78.58</v>
       </c>
       <c r="D4" t="n">
-        <v>70.77</v>
+        <v>72.61</v>
       </c>
       <c r="E4" t="n">
-        <v>71.41</v>
+        <v>78.14</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.67</v>
+        <v>6.73</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.009299999999999999</v>
+        <v>0.09420000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>2.39</v>
+        <v>5.97</v>
       </c>
       <c r="I4" t="n">
-        <v>67.70999999999999</v>
+        <v>68.38</v>
       </c>
       <c r="J4" t="n">
-        <v>67.77</v>
+        <v>68.73999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>70.23</v>
+        <v>70.22</v>
       </c>
       <c r="L4" t="n">
-        <v>72.68000000000001</v>
+        <v>71.69</v>
       </c>
       <c r="M4" t="n">
-        <v>73.94</v>
+        <v>72.61</v>
       </c>
       <c r="N4" t="n">
-        <v>75.19</v>
+        <v>73.52</v>
       </c>
       <c r="O4" t="n">
-        <v>78.84</v>
+        <v>75.55</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,83 +853,83 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73.69</v>
+        <v>78.04000000000001</v>
       </c>
       <c r="C5" t="n">
-        <v>78.58</v>
+        <v>81.27</v>
       </c>
       <c r="D5" t="n">
-        <v>72.61</v>
+        <v>77.84</v>
       </c>
       <c r="E5" t="n">
-        <v>78.14</v>
+        <v>79.34</v>
       </c>
       <c r="F5" t="n">
-        <v>6.73</v>
+        <v>1.2</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.09420000000000001</v>
+        <v>0.0154</v>
       </c>
       <c r="H5" t="n">
-        <v>5.97</v>
+        <v>3.43</v>
       </c>
       <c r="I5" t="n">
-        <v>68.38</v>
+        <v>66.64</v>
       </c>
       <c r="J5" t="n">
-        <v>68.73999999999999</v>
+        <v>73.44</v>
       </c>
       <c r="K5" t="n">
-        <v>70.22</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>71.69</v>
+        <v>76.87</v>
       </c>
       <c r="M5" t="n">
-        <v>72.61</v>
+        <v>81.12</v>
       </c>
       <c r="N5" t="n">
-        <v>73.52</v>
+        <v>85.38</v>
       </c>
       <c r="O5" t="n">
-        <v>75.55</v>
+        <v>84.55</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,25 +940,21 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -968,50 +966,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>78.04000000000001</v>
+        <v>79.73999999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>81.27</v>
+        <v>80.93000000000001</v>
       </c>
       <c r="D6" t="n">
-        <v>77.84</v>
+        <v>78.19</v>
       </c>
       <c r="E6" t="n">
-        <v>79.34</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2</v>
+        <v>0.26</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0154</v>
+        <v>0.0033</v>
       </c>
       <c r="H6" t="n">
-        <v>3.43</v>
+        <v>2.74</v>
       </c>
       <c r="I6" t="n">
-        <v>66.64</v>
+        <v>74.41</v>
       </c>
       <c r="J6" t="n">
-        <v>73.44</v>
+        <v>75.8</v>
       </c>
       <c r="K6" t="n">
-        <v>75.15000000000001</v>
+        <v>77.62</v>
       </c>
       <c r="L6" t="n">
-        <v>76.87</v>
+        <v>79.45</v>
       </c>
       <c r="M6" t="n">
-        <v>81.12</v>
+        <v>81.05</v>
       </c>
       <c r="N6" t="n">
-        <v>85.38</v>
+        <v>82.66</v>
       </c>
       <c r="O6" t="n">
-        <v>84.55</v>
+        <v>84.7</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1022,15 +1020,13 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1043,55 +1039,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>79.73999999999999</v>
+        <v>80</v>
       </c>
       <c r="C7" t="n">
-        <v>80.93000000000001</v>
+        <v>80.87</v>
       </c>
       <c r="D7" t="n">
-        <v>78.19</v>
+        <v>78.58</v>
       </c>
       <c r="E7" t="n">
-        <v>79.59999999999999</v>
+        <v>78.95</v>
       </c>
       <c r="F7" t="n">
-        <v>0.26</v>
+        <v>-0.65</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0033</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>2.74</v>
+        <v>2.29</v>
       </c>
       <c r="I7" t="n">
-        <v>74.41</v>
+        <v>75.45</v>
       </c>
       <c r="J7" t="n">
-        <v>75.8</v>
+        <v>76.88</v>
       </c>
       <c r="K7" t="n">
-        <v>77.62</v>
+        <v>78.23</v>
       </c>
       <c r="L7" t="n">
-        <v>79.45</v>
+        <v>79.58</v>
       </c>
       <c r="M7" t="n">
-        <v>81.05</v>
+        <v>80.97</v>
       </c>
       <c r="N7" t="n">
-        <v>82.66</v>
+        <v>82.36</v>
       </c>
       <c r="O7" t="n">
-        <v>84.7</v>
+        <v>83.67</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="S7" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1123,57 +1123,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>80</v>
+        <v>79.56999999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>80.87</v>
+        <v>82.76000000000001</v>
       </c>
       <c r="D8" t="n">
-        <v>78.58</v>
+        <v>78.61</v>
       </c>
       <c r="E8" t="n">
-        <v>78.95</v>
+        <v>82.48999999999999</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.65</v>
+        <v>3.54</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0.0448</v>
       </c>
       <c r="H8" t="n">
-        <v>2.29</v>
+        <v>4.15</v>
       </c>
       <c r="I8" t="n">
-        <v>75.45</v>
+        <v>76.29000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>76.88</v>
+        <v>76.27</v>
       </c>
       <c r="K8" t="n">
-        <v>78.23</v>
+        <v>77.8</v>
       </c>
       <c r="L8" t="n">
-        <v>79.58</v>
+        <v>79.34</v>
       </c>
       <c r="M8" t="n">
-        <v>80.97</v>
+        <v>80.09</v>
       </c>
       <c r="N8" t="n">
-        <v>82.36</v>
+        <v>80.84999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>83.67</v>
+        <v>83.16</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1186,76 +1186,78 @@
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>79.56999999999999</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="C9" t="n">
-        <v>82.76000000000001</v>
+        <v>85.39</v>
       </c>
       <c r="D9" t="n">
-        <v>78.61</v>
+        <v>80.27</v>
       </c>
       <c r="E9" t="n">
-        <v>82.48999999999999</v>
+        <v>83.23</v>
       </c>
       <c r="F9" t="n">
-        <v>3.54</v>
+        <v>0.74</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0448</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H9" t="n">
-        <v>4.15</v>
+        <v>5.12</v>
       </c>
       <c r="I9" t="n">
-        <v>76.29000000000001</v>
+        <v>74.45999999999999</v>
       </c>
       <c r="J9" t="n">
-        <v>76.27</v>
+        <v>79.23999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>77.8</v>
+        <v>80.41</v>
       </c>
       <c r="L9" t="n">
-        <v>79.34</v>
+        <v>81.59</v>
       </c>
       <c r="M9" t="n">
-        <v>80.09</v>
+        <v>84.56</v>
       </c>
       <c r="N9" t="n">
-        <v>80.84999999999999</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>83.16</v>
+        <v>86.91</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1263,28 +1265,26 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
@@ -1296,50 +1296,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>83.76000000000001</v>
+        <v>83.48</v>
       </c>
       <c r="C10" t="n">
-        <v>85.39</v>
+        <v>85.8</v>
       </c>
       <c r="D10" t="n">
-        <v>80.27</v>
+        <v>82.25</v>
       </c>
       <c r="E10" t="n">
-        <v>83.23</v>
+        <v>84.91</v>
       </c>
       <c r="F10" t="n">
-        <v>0.74</v>
+        <v>1.68</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.008999999999999999</v>
+        <v>0.0202</v>
       </c>
       <c r="H10" t="n">
-        <v>5.12</v>
+        <v>3.55</v>
       </c>
       <c r="I10" t="n">
-        <v>74.45999999999999</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>79.23999999999999</v>
+        <v>78.31</v>
       </c>
       <c r="K10" t="n">
-        <v>80.41</v>
+        <v>80.67</v>
       </c>
       <c r="L10" t="n">
-        <v>81.59</v>
+        <v>83.03</v>
       </c>
       <c r="M10" t="n">
-        <v>84.56</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="N10" t="n">
-        <v>87.54000000000001</v>
+        <v>88.55</v>
       </c>
       <c r="O10" t="n">
-        <v>86.91</v>
+        <v>90.51000000000001</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1347,12 +1347,10 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1378,50 +1376,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>83.48</v>
+        <v>84.69</v>
       </c>
       <c r="C11" t="n">
-        <v>85.8</v>
+        <v>88.61</v>
       </c>
       <c r="D11" t="n">
-        <v>82.25</v>
+        <v>84.44</v>
       </c>
       <c r="E11" t="n">
-        <v>84.91</v>
+        <v>86.83</v>
       </c>
       <c r="F11" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0202</v>
+        <v>0.0226</v>
       </c>
       <c r="H11" t="n">
-        <v>3.55</v>
+        <v>4.17</v>
       </c>
       <c r="I11" t="n">
-        <v>75.15000000000001</v>
+        <v>78.7</v>
       </c>
       <c r="J11" t="n">
-        <v>78.31</v>
+        <v>81.8</v>
       </c>
       <c r="K11" t="n">
-        <v>80.67</v>
+        <v>83.14</v>
       </c>
       <c r="L11" t="n">
-        <v>83.03</v>
+        <v>84.47</v>
       </c>
       <c r="M11" t="n">
-        <v>85.79000000000001</v>
+        <v>86.69</v>
       </c>
       <c r="N11" t="n">
-        <v>88.55</v>
+        <v>88.90000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>90.51000000000001</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1432,7 +1430,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1458,50 +1456,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>84.69</v>
+        <v>87.72</v>
       </c>
       <c r="C12" t="n">
-        <v>88.61</v>
+        <v>93.5</v>
       </c>
       <c r="D12" t="n">
-        <v>84.44</v>
+        <v>87.31999999999999</v>
       </c>
       <c r="E12" t="n">
-        <v>86.83</v>
+        <v>92.19</v>
       </c>
       <c r="F12" t="n">
-        <v>1.92</v>
+        <v>5.36</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0226</v>
+        <v>0.0617</v>
       </c>
       <c r="H12" t="n">
-        <v>4.17</v>
+        <v>6.18</v>
       </c>
       <c r="I12" t="n">
-        <v>78.7</v>
+        <v>80.27</v>
       </c>
       <c r="J12" t="n">
-        <v>81.8</v>
+        <v>82.81</v>
       </c>
       <c r="K12" t="n">
-        <v>83.14</v>
+        <v>84.75</v>
       </c>
       <c r="L12" t="n">
-        <v>84.47</v>
+        <v>86.68000000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>86.69</v>
+        <v>88.92</v>
       </c>
       <c r="N12" t="n">
-        <v>88.90000000000001</v>
+        <v>91.15000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>89.34999999999999</v>
+        <v>92.78</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1512,21 +1510,25 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1538,50 +1540,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>87.72</v>
+        <v>92.55</v>
       </c>
       <c r="C13" t="n">
-        <v>93.5</v>
+        <v>92.83</v>
       </c>
       <c r="D13" t="n">
-        <v>87.31999999999999</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>92.19</v>
+        <v>89.31</v>
       </c>
       <c r="F13" t="n">
-        <v>5.36</v>
+        <v>-2.88</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0617</v>
+        <v>-0.0312</v>
       </c>
       <c r="H13" t="n">
-        <v>6.18</v>
+        <v>5.15</v>
       </c>
       <c r="I13" t="n">
-        <v>80.27</v>
+        <v>81.14</v>
       </c>
       <c r="J13" t="n">
-        <v>82.81</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>84.75</v>
+        <v>89.09999999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>86.68000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="M13" t="n">
-        <v>88.92</v>
+        <v>95.28</v>
       </c>
       <c r="N13" t="n">
-        <v>91.15000000000001</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="O13" t="n">
-        <v>92.78</v>
+        <v>99.68000000000001</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1589,96 +1591,100 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>92.55</v>
+        <v>86.12</v>
       </c>
       <c r="C14" t="n">
-        <v>92.83</v>
+        <v>86.2</v>
       </c>
       <c r="D14" t="n">
-        <v>87.68000000000001</v>
+        <v>81.63</v>
       </c>
       <c r="E14" t="n">
-        <v>89.31</v>
+        <v>82.61</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.88</v>
+        <v>-6.7</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.075</v>
       </c>
       <c r="H14" t="n">
-        <v>5.15</v>
+        <v>4.57</v>
       </c>
       <c r="I14" t="n">
-        <v>81.14</v>
+        <v>82.53</v>
       </c>
       <c r="J14" t="n">
-        <v>86.90000000000001</v>
+        <v>83.69</v>
       </c>
       <c r="K14" t="n">
-        <v>89.09999999999999</v>
+        <v>86.73</v>
       </c>
       <c r="L14" t="n">
-        <v>91.3</v>
+        <v>89.78</v>
       </c>
       <c r="M14" t="n">
-        <v>95.28</v>
+        <v>91.88</v>
       </c>
       <c r="N14" t="n">
-        <v>99.26000000000001</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>99.68000000000001</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+        <v>97.98</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1692,81 +1698,73 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W14" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>86.12</v>
+        <v>82</v>
       </c>
       <c r="C15" t="n">
-        <v>86.2</v>
+        <v>82.43000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>81.63</v>
+        <v>77.78</v>
       </c>
       <c r="E15" t="n">
-        <v>82.61</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-6.7</v>
+        <v>-3.35</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.075</v>
+        <v>-0.0406</v>
       </c>
       <c r="H15" t="n">
-        <v>4.57</v>
+        <v>4.65</v>
       </c>
       <c r="I15" t="n">
-        <v>82.53</v>
+        <v>77.06</v>
       </c>
       <c r="J15" t="n">
-        <v>83.69</v>
+        <v>77.39</v>
       </c>
       <c r="K15" t="n">
-        <v>86.73</v>
+        <v>80.33</v>
       </c>
       <c r="L15" t="n">
-        <v>89.78</v>
+        <v>83.26000000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>91.88</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>93.98999999999999</v>
+        <v>86.53</v>
       </c>
       <c r="O15" t="n">
-        <v>97.98</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>90.77</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1790,50 +1788,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>82</v>
+        <v>80.04000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>82.43000000000001</v>
+        <v>85.56999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>77.78</v>
+        <v>79.92</v>
       </c>
       <c r="E16" t="n">
-        <v>79.26000000000001</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>-3.35</v>
+        <v>5.2</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0406</v>
+        <v>0.06560000000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>4.65</v>
+        <v>5.65</v>
       </c>
       <c r="I16" t="n">
-        <v>77.06</v>
+        <v>73.13</v>
       </c>
       <c r="J16" t="n">
-        <v>77.39</v>
+        <v>74.19</v>
       </c>
       <c r="K16" t="n">
-        <v>80.33</v>
+        <v>76.94</v>
       </c>
       <c r="L16" t="n">
-        <v>83.26000000000001</v>
+        <v>79.68000000000001</v>
       </c>
       <c r="M16" t="n">
-        <v>84.90000000000001</v>
+        <v>81.59</v>
       </c>
       <c r="N16" t="n">
-        <v>86.53</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>90.77</v>
+        <v>87.08</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1841,28 +1839,30 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr"/>
@@ -1870,50 +1870,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>80.04000000000001</v>
+        <v>84.65000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>85.56999999999999</v>
+        <v>85.94</v>
       </c>
       <c r="D17" t="n">
-        <v>79.92</v>
+        <v>82.97</v>
       </c>
       <c r="E17" t="n">
-        <v>84.45999999999999</v>
+        <v>83.59</v>
       </c>
       <c r="F17" t="n">
-        <v>5.2</v>
+        <v>-0.87</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.06560000000000001</v>
+        <v>-0.0103</v>
       </c>
       <c r="H17" t="n">
-        <v>5.65</v>
+        <v>2.97</v>
       </c>
       <c r="I17" t="n">
-        <v>73.13</v>
+        <v>74.27</v>
       </c>
       <c r="J17" t="n">
-        <v>74.19</v>
+        <v>79.67</v>
       </c>
       <c r="K17" t="n">
-        <v>76.94</v>
+        <v>81.63</v>
       </c>
       <c r="L17" t="n">
-        <v>79.68000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>81.59</v>
+        <v>87.28</v>
       </c>
       <c r="N17" t="n">
-        <v>83.48999999999999</v>
+        <v>90.97</v>
       </c>
       <c r="O17" t="n">
-        <v>87.08</v>
+        <v>91.22</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1926,18 +1926,14 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1947,55 +1943,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>84.65000000000001</v>
+        <v>83.92</v>
       </c>
       <c r="C18" t="n">
-        <v>85.94</v>
+        <v>86.87</v>
       </c>
       <c r="D18" t="n">
-        <v>82.97</v>
+        <v>81.06</v>
       </c>
       <c r="E18" t="n">
-        <v>83.59</v>
+        <v>84.67</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.87</v>
+        <v>1.08</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0129</v>
       </c>
       <c r="H18" t="n">
-        <v>2.97</v>
+        <v>5.81</v>
       </c>
       <c r="I18" t="n">
-        <v>74.27</v>
+        <v>80</v>
       </c>
       <c r="J18" t="n">
-        <v>79.67</v>
+        <v>80.19</v>
       </c>
       <c r="K18" t="n">
-        <v>81.63</v>
+        <v>82.09999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>83.59999999999999</v>
+        <v>84.02</v>
       </c>
       <c r="M18" t="n">
-        <v>87.28</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>90.97</v>
+        <v>86.13</v>
       </c>
       <c r="O18" t="n">
-        <v>91.22</v>
+        <v>88.91</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2003,19 +2003,25 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2034,56 +2040,58 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>83.92</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>86.87</v>
+        <v>81.3</v>
       </c>
       <c r="D19" t="n">
-        <v>81.06</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="E19" t="n">
-        <v>84.67</v>
+        <v>80.34</v>
       </c>
       <c r="F19" t="n">
-        <v>1.08</v>
+        <v>-4.33</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0511</v>
       </c>
       <c r="H19" t="n">
-        <v>5.81</v>
+        <v>2.87</v>
       </c>
       <c r="I19" t="n">
-        <v>80</v>
+        <v>75.25</v>
       </c>
       <c r="J19" t="n">
-        <v>80.19</v>
+        <v>79.20999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>82.09999999999999</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>84.02</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>85.06999999999999</v>
+        <v>87.58</v>
       </c>
       <c r="N19" t="n">
-        <v>86.13</v>
+        <v>90.83</v>
       </c>
       <c r="O19" t="n">
-        <v>88.91</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
@@ -2092,18 +2100,14 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2115,64 +2119,66 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" t="n">
         <v>80.09999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>81.3</v>
+        <v>82.33</v>
       </c>
       <c r="D20" t="n">
-        <v>78.43000000000001</v>
+        <v>75.11</v>
       </c>
       <c r="E20" t="n">
-        <v>80.34</v>
+        <v>75.77</v>
       </c>
       <c r="F20" t="n">
-        <v>-4.33</v>
+        <v>-4.57</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0511</v>
+        <v>-0.0569</v>
       </c>
       <c r="H20" t="n">
-        <v>2.87</v>
+        <v>7.22</v>
       </c>
       <c r="I20" t="n">
-        <v>75.25</v>
+        <v>75.56</v>
       </c>
       <c r="J20" t="n">
-        <v>79.20999999999999</v>
+        <v>77.70999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>81.76000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>84.31999999999999</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>87.58</v>
+        <v>81.77</v>
       </c>
       <c r="N20" t="n">
-        <v>90.83</v>
+        <v>83.45</v>
       </c>
       <c r="O20" t="n">
-        <v>92.68000000000001</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
+        <v>84.17</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q20" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
@@ -2180,13 +2186,15 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2194,89 +2202,81 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80.09999999999999</v>
+        <v>75.17</v>
       </c>
       <c r="C21" t="n">
-        <v>82.33</v>
+        <v>76.7</v>
       </c>
       <c r="D21" t="n">
-        <v>75.11</v>
+        <v>74.23999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>75.77</v>
+        <v>75.22</v>
       </c>
       <c r="F21" t="n">
-        <v>-4.57</v>
+        <v>-0.55</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0569</v>
+        <v>-0.0073</v>
       </c>
       <c r="H21" t="n">
-        <v>7.22</v>
+        <v>2.46</v>
       </c>
       <c r="I21" t="n">
-        <v>75.56</v>
+        <v>67.89</v>
       </c>
       <c r="J21" t="n">
-        <v>77.70999999999999</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>78.90000000000001</v>
+        <v>72.16</v>
       </c>
       <c r="L21" t="n">
-        <v>80.09999999999999</v>
+        <v>77.23999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>81.77</v>
+        <v>79.38</v>
       </c>
       <c r="N21" t="n">
-        <v>83.45</v>
+        <v>81.51000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>84.17</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>89.55</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2289,59 +2289,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>75.17</v>
+        <v>75.14</v>
       </c>
       <c r="C22" t="n">
-        <v>76.7</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>74.23999999999999</v>
+        <v>74.56999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>75.22</v>
+        <v>77.29000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.55</v>
+        <v>2.07</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0073</v>
+        <v>0.0275</v>
       </c>
       <c r="H22" t="n">
-        <v>2.46</v>
+        <v>3.94</v>
       </c>
       <c r="I22" t="n">
-        <v>67.89</v>
+        <v>71.78</v>
       </c>
       <c r="J22" t="n">
-        <v>67.06999999999999</v>
+        <v>72.64</v>
       </c>
       <c r="K22" t="n">
-        <v>72.16</v>
+        <v>73.98999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>77.23999999999999</v>
+        <v>75.34</v>
       </c>
       <c r="M22" t="n">
-        <v>79.38</v>
+        <v>76.45</v>
       </c>
       <c r="N22" t="n">
-        <v>81.51000000000001</v>
+        <v>77.56</v>
       </c>
       <c r="O22" t="n">
-        <v>89.55</v>
+        <v>79.16</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2354,14 +2350,18 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2371,55 +2371,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>75.14</v>
+        <v>78.17</v>
       </c>
       <c r="C23" t="n">
-        <v>78.51000000000001</v>
+        <v>78.77</v>
       </c>
       <c r="D23" t="n">
-        <v>74.56999999999999</v>
+        <v>76.53</v>
       </c>
       <c r="E23" t="n">
-        <v>77.29000000000001</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>2.07</v>
+        <v>0.89</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0275</v>
+        <v>0.0115</v>
       </c>
       <c r="H23" t="n">
-        <v>3.94</v>
+        <v>2.24</v>
       </c>
       <c r="I23" t="n">
-        <v>71.78</v>
+        <v>70.63</v>
       </c>
       <c r="J23" t="n">
-        <v>72.64</v>
+        <v>73.72</v>
       </c>
       <c r="K23" t="n">
-        <v>73.98999999999999</v>
+        <v>75.31999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>75.34</v>
+        <v>76.92</v>
       </c>
       <c r="M23" t="n">
-        <v>76.45</v>
+        <v>79.26000000000001</v>
       </c>
       <c r="N23" t="n">
-        <v>77.56</v>
+        <v>81.61</v>
       </c>
       <c r="O23" t="n">
-        <v>79.16</v>
+        <v>82.45</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2430,20 +2434,18 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2462,50 +2464,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>78.17</v>
+        <v>78.42</v>
       </c>
       <c r="C24" t="n">
-        <v>78.77</v>
+        <v>82.38</v>
       </c>
       <c r="D24" t="n">
-        <v>76.53</v>
+        <v>77.79000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>78.18000000000001</v>
+        <v>82.13</v>
       </c>
       <c r="F24" t="n">
-        <v>0.89</v>
+        <v>3.95</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0115</v>
+        <v>0.0505</v>
       </c>
       <c r="H24" t="n">
-        <v>2.24</v>
+        <v>4.59</v>
       </c>
       <c r="I24" t="n">
-        <v>70.63</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>73.72</v>
+        <v>76.20999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>75.31999999999999</v>
+        <v>77.06</v>
       </c>
       <c r="L24" t="n">
-        <v>76.92</v>
+        <v>77.91</v>
       </c>
       <c r="M24" t="n">
-        <v>79.26000000000001</v>
+        <v>79.3</v>
       </c>
       <c r="N24" t="n">
-        <v>81.61</v>
+        <v>80.68000000000001</v>
       </c>
       <c r="O24" t="n">
-        <v>82.45</v>
+        <v>81.01000000000001</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2516,80 +2518,80 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>78.42</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>82.38</v>
+        <v>84.61</v>
       </c>
       <c r="D25" t="n">
-        <v>77.79000000000001</v>
+        <v>81.27</v>
       </c>
       <c r="E25" t="n">
-        <v>82.13</v>
+        <v>83.2</v>
       </c>
       <c r="F25" t="n">
-        <v>3.95</v>
+        <v>1.07</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0505</v>
+        <v>0.013</v>
       </c>
       <c r="H25" t="n">
-        <v>4.59</v>
+        <v>3.34</v>
       </c>
       <c r="I25" t="n">
-        <v>74.29000000000001</v>
+        <v>73.2</v>
       </c>
       <c r="J25" t="n">
-        <v>76.20999999999999</v>
+        <v>78.56</v>
       </c>
       <c r="K25" t="n">
-        <v>77.06</v>
+        <v>79.83</v>
       </c>
       <c r="L25" t="n">
-        <v>77.91</v>
+        <v>81.11</v>
       </c>
       <c r="M25" t="n">
-        <v>79.3</v>
+        <v>84.42</v>
       </c>
       <c r="N25" t="n">
-        <v>80.68000000000001</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>81.01000000000001</v>
+        <v>86.97</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2600,25 +2602,21 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2630,50 +2628,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>82.34999999999999</v>
+        <v>83.48999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>84.61</v>
+        <v>84.34999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>81.27</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="E26" t="n">
-        <v>83.2</v>
+        <v>83.27</v>
       </c>
       <c r="F26" t="n">
-        <v>1.07</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.013</v>
+        <v>0.0008</v>
       </c>
       <c r="H26" t="n">
-        <v>3.34</v>
+        <v>1.95</v>
       </c>
       <c r="I26" t="n">
-        <v>73.2</v>
+        <v>77.93000000000001</v>
       </c>
       <c r="J26" t="n">
-        <v>78.56</v>
+        <v>79.98999999999999</v>
       </c>
       <c r="K26" t="n">
-        <v>79.83</v>
+        <v>81.53</v>
       </c>
       <c r="L26" t="n">
-        <v>81.11</v>
+        <v>83.06999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>84.42</v>
+        <v>84.87</v>
       </c>
       <c r="N26" t="n">
-        <v>87.73999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="O26" t="n">
-        <v>86.97</v>
+        <v>87.95</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2684,15 +2682,13 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2705,68 +2701,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>83.48999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="C27" t="n">
-        <v>84.34999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="D27" t="n">
-        <v>82.40000000000001</v>
+        <v>80.09</v>
       </c>
       <c r="E27" t="n">
-        <v>83.27</v>
+        <v>81.25</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07000000000000001</v>
+        <v>-2.02</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0008</v>
+        <v>-0.0243</v>
       </c>
       <c r="H27" t="n">
-        <v>1.95</v>
+        <v>3.21</v>
       </c>
       <c r="I27" t="n">
-        <v>77.93000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="J27" t="n">
-        <v>79.98999999999999</v>
+        <v>81.27</v>
       </c>
       <c r="K27" t="n">
-        <v>81.53</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="L27" t="n">
-        <v>83.06999999999999</v>
+        <v>83.31999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>84.87</v>
+        <v>84.23999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>86.67</v>
+        <v>85.17</v>
       </c>
       <c r="O27" t="n">
-        <v>87.95</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+        <v>86.3</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2778,88 +2784,80 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W27" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>82.7</v>
+        <v>81.27</v>
       </c>
       <c r="C28" t="n">
-        <v>83.3</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>80.09</v>
+        <v>80.70999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>81.25</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.02</v>
+        <v>1.15</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0243</v>
+        <v>0.0142</v>
       </c>
       <c r="H28" t="n">
-        <v>3.21</v>
+        <v>2.28</v>
       </c>
       <c r="I28" t="n">
-        <v>80.45</v>
+        <v>76.88</v>
       </c>
       <c r="J28" t="n">
-        <v>81.27</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K28" t="n">
-        <v>82.29000000000001</v>
+        <v>79.64</v>
       </c>
       <c r="L28" t="n">
-        <v>83.31999999999999</v>
+        <v>81.47</v>
       </c>
       <c r="M28" t="n">
+        <v>82.86</v>
+      </c>
+      <c r="N28" t="n">
         <v>84.23999999999999</v>
       </c>
-      <c r="N28" t="n">
-        <v>85.17</v>
-      </c>
       <c r="O28" t="n">
-        <v>86.3</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
+        <v>86.51000000000001</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
       <c r="U28" s="8" t="n">
         <v/>
       </c>
@@ -2871,55 +2869,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>81.27</v>
+        <v>82.53</v>
       </c>
       <c r="C29" t="n">
-        <v>82.98999999999999</v>
+        <v>85.04000000000001</v>
       </c>
       <c r="D29" t="n">
-        <v>80.70999999999999</v>
+        <v>81.5</v>
       </c>
       <c r="E29" t="n">
-        <v>82.40000000000001</v>
+        <v>84.5</v>
       </c>
       <c r="F29" t="n">
-        <v>1.15</v>
+        <v>2.1</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0142</v>
+        <v>0.0255</v>
       </c>
       <c r="H29" t="n">
-        <v>2.28</v>
+        <v>3.54</v>
       </c>
       <c r="I29" t="n">
-        <v>76.88</v>
+        <v>78.43000000000001</v>
       </c>
       <c r="J29" t="n">
-        <v>77.81999999999999</v>
+        <v>80.40000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>79.64</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>81.47</v>
+        <v>82.12</v>
       </c>
       <c r="M29" t="n">
-        <v>82.86</v>
+        <v>83.54000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>84.23999999999999</v>
+        <v>84.95999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>86.51000000000001</v>
+        <v>85.27</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2930,19 +2932,21 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
@@ -2953,57 +2957,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>82.53</v>
+        <v>84.98</v>
       </c>
       <c r="C30" t="n">
-        <v>85.04000000000001</v>
+        <v>85.94</v>
       </c>
       <c r="D30" t="n">
-        <v>81.5</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>84.5</v>
+        <v>84.94</v>
       </c>
       <c r="F30" t="n">
-        <v>2.1</v>
+        <v>0.44</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0255</v>
+        <v>0.0052</v>
       </c>
       <c r="H30" t="n">
-        <v>3.54</v>
+        <v>1.37</v>
       </c>
       <c r="I30" t="n">
-        <v>78.43000000000001</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="J30" t="n">
-        <v>80.40000000000001</v>
+        <v>81.56999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>81.26000000000001</v>
+        <v>82.73</v>
       </c>
       <c r="L30" t="n">
-        <v>82.12</v>
+        <v>83.89</v>
       </c>
       <c r="M30" t="n">
-        <v>83.54000000000001</v>
+        <v>86.27</v>
       </c>
       <c r="N30" t="n">
-        <v>84.95999999999999</v>
+        <v>88.66</v>
       </c>
       <c r="O30" t="n">
-        <v>85.27</v>
+        <v>88.58</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3014,20 +3018,16 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3046,50 +3046,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>84.98</v>
+        <v>85.42</v>
       </c>
       <c r="C31" t="n">
-        <v>85.94</v>
+        <v>87.19</v>
       </c>
       <c r="D31" t="n">
-        <v>84.56999999999999</v>
+        <v>84.31999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>84.94</v>
+        <v>85.83</v>
       </c>
       <c r="F31" t="n">
-        <v>0.44</v>
+        <v>0.89</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0052</v>
+        <v>0.0105</v>
       </c>
       <c r="H31" t="n">
-        <v>1.37</v>
+        <v>2.87</v>
       </c>
       <c r="I31" t="n">
-        <v>77.95999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="J31" t="n">
-        <v>81.56999999999999</v>
+        <v>83.41</v>
       </c>
       <c r="K31" t="n">
-        <v>82.73</v>
+        <v>84.26000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>83.89</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>86.27</v>
+        <v>85.63</v>
       </c>
       <c r="N31" t="n">
-        <v>88.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="O31" t="n">
-        <v>88.58</v>
+        <v>87.31</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3100,16 +3100,20 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3121,57 +3125,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>85.42</v>
+        <v>85.8</v>
       </c>
       <c r="C32" t="n">
-        <v>87.19</v>
+        <v>89</v>
       </c>
       <c r="D32" t="n">
-        <v>84.31999999999999</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>85.83</v>
+        <v>87.83</v>
       </c>
       <c r="F32" t="n">
-        <v>0.89</v>
+        <v>2</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0233</v>
       </c>
       <c r="H32" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="I32" t="n">
-        <v>83.2</v>
+        <v>81.45</v>
       </c>
       <c r="J32" t="n">
-        <v>83.41</v>
+        <v>83</v>
       </c>
       <c r="K32" t="n">
-        <v>84.26000000000001</v>
+        <v>84.40000000000001</v>
       </c>
       <c r="L32" t="n">
-        <v>85.09999999999999</v>
+        <v>85.79000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>85.63</v>
+        <v>87.27</v>
       </c>
       <c r="N32" t="n">
-        <v>86.15000000000001</v>
+        <v>88.73999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>87.31</v>
+        <v>90.06</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3182,7 +3186,7 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3207,57 +3211,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="n">
+        <v>86.27</v>
+      </c>
+      <c r="C33" t="n">
+        <v>87.51000000000001</v>
+      </c>
+      <c r="D33" t="n">
         <v>85.8</v>
       </c>
-      <c r="C33" t="n">
-        <v>89</v>
-      </c>
-      <c r="D33" t="n">
-        <v>85.59999999999999</v>
-      </c>
       <c r="E33" t="n">
-        <v>87.83</v>
+        <v>87.06</v>
       </c>
       <c r="F33" t="n">
-        <v>2</v>
+        <v>-0.77</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0233</v>
+        <v>-0.008800000000000001</v>
       </c>
       <c r="H33" t="n">
-        <v>3.4</v>
+        <v>1.71</v>
       </c>
       <c r="I33" t="n">
-        <v>81.45</v>
+        <v>82.2</v>
       </c>
       <c r="J33" t="n">
-        <v>83</v>
+        <v>84.7</v>
       </c>
       <c r="K33" t="n">
-        <v>84.40000000000001</v>
+        <v>86.13</v>
       </c>
       <c r="L33" t="n">
-        <v>85.79000000000001</v>
+        <v>87.56999999999999</v>
       </c>
       <c r="M33" t="n">
-        <v>87.27</v>
+        <v>89.53</v>
       </c>
       <c r="N33" t="n">
-        <v>88.73999999999999</v>
+        <v>91.5</v>
       </c>
       <c r="O33" t="n">
-        <v>90.06</v>
+        <v>92.40000000000001</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3265,23 +3269,21 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3293,72 +3295,74 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>86.27</v>
+        <v>86.5</v>
       </c>
       <c r="C34" t="n">
-        <v>87.51000000000001</v>
+        <v>86.56999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>85.8</v>
+        <v>84.36</v>
       </c>
       <c r="E34" t="n">
-        <v>87.06</v>
+        <v>85.01000000000001</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.77</v>
+        <v>-2.05</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.008800000000000001</v>
+        <v>-0.0235</v>
       </c>
       <c r="H34" t="n">
-        <v>1.71</v>
+        <v>2.21</v>
       </c>
       <c r="I34" t="n">
-        <v>82.2</v>
+        <v>84.09</v>
       </c>
       <c r="J34" t="n">
-        <v>84.7</v>
+        <v>85.55</v>
       </c>
       <c r="K34" t="n">
-        <v>86.13</v>
+        <v>86.2</v>
       </c>
       <c r="L34" t="n">
-        <v>87.56999999999999</v>
+        <v>86.86</v>
       </c>
       <c r="M34" t="n">
-        <v>89.53</v>
+        <v>87.91</v>
       </c>
       <c r="N34" t="n">
-        <v>91.5</v>
+        <v>88.97</v>
       </c>
       <c r="O34" t="n">
-        <v>92.40000000000001</v>
+        <v>89.22</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3375,66 +3379,64 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>86.5</v>
+        <v>85.03</v>
       </c>
       <c r="C35" t="n">
-        <v>86.56999999999999</v>
+        <v>85.84</v>
       </c>
       <c r="D35" t="n">
-        <v>84.36</v>
+        <v>80.23</v>
       </c>
       <c r="E35" t="n">
-        <v>85.01000000000001</v>
+        <v>82.36</v>
       </c>
       <c r="F35" t="n">
-        <v>-2.05</v>
+        <v>-2.65</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0235</v>
+        <v>-0.0312</v>
       </c>
       <c r="H35" t="n">
-        <v>2.21</v>
+        <v>5.61</v>
       </c>
       <c r="I35" t="n">
-        <v>84.09</v>
+        <v>82.15000000000001</v>
       </c>
       <c r="J35" t="n">
-        <v>85.55</v>
+        <v>82.56999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>86.2</v>
+        <v>83.91</v>
       </c>
       <c r="L35" t="n">
-        <v>86.86</v>
+        <v>85.23999999999999</v>
       </c>
       <c r="M35" t="n">
-        <v>87.91</v>
+        <v>86.12</v>
       </c>
       <c r="N35" t="n">
-        <v>88.97</v>
+        <v>86.98999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>89.22</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
+        <v>88.78</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
@@ -3442,7 +3444,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3466,69 +3468,63 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>85.03</v>
+        <v>81.11</v>
       </c>
       <c r="C36" t="n">
-        <v>85.84</v>
+        <v>83.31</v>
       </c>
       <c r="D36" t="n">
-        <v>80.23</v>
+        <v>79.62</v>
       </c>
       <c r="E36" t="n">
-        <v>82.36</v>
+        <v>82.23</v>
       </c>
       <c r="F36" t="n">
-        <v>-2.65</v>
+        <v>-0.13</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0312</v>
+        <v>-0.0016</v>
       </c>
       <c r="H36" t="n">
-        <v>5.61</v>
+        <v>3.69</v>
       </c>
       <c r="I36" t="n">
-        <v>82.15000000000001</v>
+        <v>74.62</v>
       </c>
       <c r="J36" t="n">
-        <v>82.56999999999999</v>
+        <v>76.41</v>
       </c>
       <c r="K36" t="n">
-        <v>83.91</v>
+        <v>79.56</v>
       </c>
       <c r="L36" t="n">
-        <v>85.23999999999999</v>
+        <v>82.7</v>
       </c>
       <c r="M36" t="n">
-        <v>86.12</v>
+        <v>85.16</v>
       </c>
       <c r="N36" t="n">
-        <v>86.98999999999999</v>
+        <v>87.63</v>
       </c>
       <c r="O36" t="n">
-        <v>88.78</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>91.45</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3550,50 +3546,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>81.11</v>
+        <v>82</v>
       </c>
       <c r="C37" t="n">
-        <v>83.31</v>
+        <v>84.27</v>
       </c>
       <c r="D37" t="n">
-        <v>79.62</v>
+        <v>80.65000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>82.23</v>
+        <v>83.53</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.13</v>
+        <v>1.3</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0158</v>
       </c>
       <c r="H37" t="n">
-        <v>3.69</v>
+        <v>3.62</v>
       </c>
       <c r="I37" t="n">
-        <v>74.62</v>
+        <v>75.93000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>76.41</v>
+        <v>78.92</v>
       </c>
       <c r="K37" t="n">
-        <v>79.56</v>
+        <v>80.39</v>
       </c>
       <c r="L37" t="n">
-        <v>82.7</v>
+        <v>81.84999999999999</v>
       </c>
       <c r="M37" t="n">
-        <v>85.16</v>
+        <v>84.08</v>
       </c>
       <c r="N37" t="n">
-        <v>87.63</v>
+        <v>86.3</v>
       </c>
       <c r="O37" t="n">
-        <v>91.45</v>
+        <v>87</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3606,11 +3602,13 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3623,55 +3621,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>82</v>
+        <v>83.67</v>
       </c>
       <c r="C38" t="n">
-        <v>84.27</v>
+        <v>83.78</v>
       </c>
       <c r="D38" t="n">
-        <v>80.65000000000001</v>
+        <v>82.25</v>
       </c>
       <c r="E38" t="n">
-        <v>83.53</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="F38" t="n">
-        <v>1.3</v>
+        <v>-0.13</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0158</v>
+        <v>-0.0016</v>
       </c>
       <c r="H38" t="n">
-        <v>3.62</v>
+        <v>1.53</v>
       </c>
       <c r="I38" t="n">
-        <v>75.93000000000001</v>
+        <v>77.03</v>
       </c>
       <c r="J38" t="n">
-        <v>78.92</v>
+        <v>80.45</v>
       </c>
       <c r="K38" t="n">
-        <v>80.39</v>
+        <v>81.72</v>
       </c>
       <c r="L38" t="n">
-        <v>81.84999999999999</v>
+        <v>82.98999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>84.08</v>
+        <v>85.34</v>
       </c>
       <c r="N38" t="n">
-        <v>86.3</v>
+        <v>87.68000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>87</v>
+        <v>87.89</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3682,15 +3684,13 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3705,57 +3705,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>83.67</v>
+        <v>84.69</v>
       </c>
       <c r="C39" t="n">
-        <v>83.78</v>
+        <v>86.79000000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>82.25</v>
+        <v>84.11</v>
       </c>
       <c r="E39" t="n">
-        <v>83.40000000000001</v>
+        <v>85.76000000000001</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.13</v>
+        <v>2.36</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0016</v>
+        <v>0.0283</v>
       </c>
       <c r="H39" t="n">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="I39" t="n">
-        <v>77.03</v>
+        <v>80.72</v>
       </c>
       <c r="J39" t="n">
-        <v>80.45</v>
+        <v>82.06</v>
       </c>
       <c r="K39" t="n">
-        <v>81.72</v>
+        <v>82.64</v>
       </c>
       <c r="L39" t="n">
-        <v>82.98999999999999</v>
+        <v>83.20999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>85.34</v>
+        <v>84.17</v>
       </c>
       <c r="N39" t="n">
-        <v>87.68000000000001</v>
+        <v>85.12</v>
       </c>
       <c r="O39" t="n">
-        <v>87.89</v>
+        <v>85.31</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3766,78 +3766,80 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W39" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W39" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>84.69</v>
+        <v>86.31</v>
       </c>
       <c r="C40" t="n">
-        <v>86.79000000000001</v>
+        <v>90.97</v>
       </c>
       <c r="D40" t="n">
-        <v>84.11</v>
+        <v>86.13</v>
       </c>
       <c r="E40" t="n">
-        <v>85.76000000000001</v>
+        <v>90.22</v>
       </c>
       <c r="F40" t="n">
-        <v>2.36</v>
+        <v>4.46</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0283</v>
+        <v>0.052</v>
       </c>
       <c r="H40" t="n">
-        <v>2.68</v>
+        <v>4.84</v>
       </c>
       <c r="I40" t="n">
-        <v>80.72</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="J40" t="n">
-        <v>82.06</v>
+        <v>83.23999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>82.64</v>
+        <v>84.42</v>
       </c>
       <c r="L40" t="n">
-        <v>83.20999999999999</v>
+        <v>85.61</v>
       </c>
       <c r="M40" t="n">
-        <v>84.17</v>
+        <v>87.09999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>85.12</v>
+        <v>88.59999999999999</v>
       </c>
       <c r="O40" t="n">
-        <v>85.31</v>
+        <v>89.47</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3848,7 +3850,7 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="7" t="inlineStr">
+      <c r="S40" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3878,50 +3880,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>86.31</v>
+        <v>90.65000000000001</v>
       </c>
       <c r="C41" t="n">
-        <v>90.97</v>
+        <v>92.29000000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>86.13</v>
+        <v>88.97</v>
       </c>
       <c r="E41" t="n">
-        <v>90.22</v>
+        <v>91.01000000000001</v>
       </c>
       <c r="F41" t="n">
-        <v>4.46</v>
+        <v>0.79</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.052</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="H41" t="n">
-        <v>4.84</v>
+        <v>3.32</v>
       </c>
       <c r="I41" t="n">
-        <v>81.43000000000001</v>
+        <v>81.29000000000001</v>
       </c>
       <c r="J41" t="n">
-        <v>83.23999999999999</v>
+        <v>86.20999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>84.42</v>
+        <v>87.8</v>
       </c>
       <c r="L41" t="n">
-        <v>85.61</v>
+        <v>89.39</v>
       </c>
       <c r="M41" t="n">
-        <v>87.09999999999999</v>
+        <v>92.64</v>
       </c>
       <c r="N41" t="n">
-        <v>88.59999999999999</v>
+        <v>95.90000000000001</v>
       </c>
       <c r="O41" t="n">
-        <v>89.47</v>
+        <v>95.81</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3932,25 +3934,19 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V41" s="8" t="n">
+        <v/>
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
@@ -3962,50 +3958,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>90.65000000000001</v>
+        <v>90.7</v>
       </c>
       <c r="C42" t="n">
-        <v>92.29000000000001</v>
+        <v>93.14</v>
       </c>
       <c r="D42" t="n">
-        <v>88.97</v>
+        <v>89.56999999999999</v>
       </c>
       <c r="E42" t="n">
-        <v>91.01000000000001</v>
+        <v>91.3</v>
       </c>
       <c r="F42" t="n">
-        <v>0.79</v>
+        <v>0.29</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0032</v>
       </c>
       <c r="H42" t="n">
-        <v>3.32</v>
+        <v>3.57</v>
       </c>
       <c r="I42" t="n">
-        <v>81.29000000000001</v>
+        <v>85.65000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>86.20999999999999</v>
+        <v>87.88</v>
       </c>
       <c r="K42" t="n">
-        <v>87.8</v>
+        <v>89.34999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>89.39</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>92.64</v>
+        <v>92.67</v>
       </c>
       <c r="N42" t="n">
-        <v>95.90000000000001</v>
+        <v>94.52</v>
       </c>
       <c r="O42" t="n">
-        <v>95.81</v>
+        <v>95.61</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4016,13 +4012,15 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
+      <c r="S42" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4040,50 +4038,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>90.7</v>
+        <v>91.67</v>
       </c>
       <c r="C43" t="n">
-        <v>93.14</v>
+        <v>92.17</v>
       </c>
       <c r="D43" t="n">
-        <v>89.56999999999999</v>
+        <v>88.72</v>
       </c>
       <c r="E43" t="n">
-        <v>91.3</v>
+        <v>91.48</v>
       </c>
       <c r="F43" t="n">
-        <v>0.29</v>
+        <v>0.18</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0032</v>
+        <v>0.002</v>
       </c>
       <c r="H43" t="n">
-        <v>3.57</v>
+        <v>3.45</v>
       </c>
       <c r="I43" t="n">
-        <v>85.65000000000001</v>
+        <v>86</v>
       </c>
       <c r="J43" t="n">
-        <v>87.88</v>
+        <v>87.7</v>
       </c>
       <c r="K43" t="n">
-        <v>89.34999999999999</v>
+        <v>89.52</v>
       </c>
       <c r="L43" t="n">
-        <v>90.81999999999999</v>
+        <v>91.33</v>
       </c>
       <c r="M43" t="n">
-        <v>92.67</v>
+        <v>93.09</v>
       </c>
       <c r="N43" t="n">
-        <v>94.52</v>
+        <v>94.84</v>
       </c>
       <c r="O43" t="n">
-        <v>95.61</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4091,18 +4089,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4115,55 +4113,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>91.67</v>
+        <v>92.26000000000001</v>
       </c>
       <c r="C44" t="n">
-        <v>92.17</v>
+        <v>94.73</v>
       </c>
       <c r="D44" t="n">
-        <v>88.72</v>
+        <v>90.87</v>
       </c>
       <c r="E44" t="n">
-        <v>91.48</v>
+        <v>93.03</v>
       </c>
       <c r="F44" t="n">
-        <v>0.18</v>
+        <v>1.55</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.002</v>
+        <v>0.0169</v>
       </c>
       <c r="H44" t="n">
-        <v>3.45</v>
+        <v>3.86</v>
       </c>
       <c r="I44" t="n">
-        <v>86</v>
+        <v>85.27</v>
       </c>
       <c r="J44" t="n">
-        <v>87.7</v>
+        <v>88.55</v>
       </c>
       <c r="K44" t="n">
-        <v>89.52</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="L44" t="n">
-        <v>91.33</v>
+        <v>90.95999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>93.09</v>
+        <v>93.20999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>94.84</v>
+        <v>95.45</v>
       </c>
       <c r="O44" t="n">
-        <v>96.70999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4171,18 +4173,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4195,59 +4197,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>92.26000000000001</v>
+        <v>94.31</v>
       </c>
       <c r="C45" t="n">
-        <v>94.73</v>
+        <v>96.93000000000001</v>
       </c>
       <c r="D45" t="n">
-        <v>90.87</v>
+        <v>93.76000000000001</v>
       </c>
       <c r="E45" t="n">
-        <v>93.03</v>
+        <v>96.05</v>
       </c>
       <c r="F45" t="n">
-        <v>1.55</v>
+        <v>3.02</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0325</v>
       </c>
       <c r="H45" t="n">
-        <v>3.86</v>
+        <v>3.17</v>
       </c>
       <c r="I45" t="n">
-        <v>85.27</v>
+        <v>87.01000000000001</v>
       </c>
       <c r="J45" t="n">
-        <v>88.55</v>
+        <v>89.28</v>
       </c>
       <c r="K45" t="n">
-        <v>89.76000000000001</v>
+        <v>91.09999999999999</v>
       </c>
       <c r="L45" t="n">
-        <v>90.95999999999999</v>
+        <v>92.92</v>
       </c>
       <c r="M45" t="n">
-        <v>93.20999999999999</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>95.45</v>
+        <v>97</v>
       </c>
       <c r="O45" t="n">
-        <v>95.62</v>
+        <v>98.59</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4258,18 +4256,20 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T45" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4284,50 +4284,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>94.31</v>
+        <v>96.88</v>
       </c>
       <c r="C46" t="n">
-        <v>96.93000000000001</v>
+        <v>104.04</v>
       </c>
       <c r="D46" t="n">
-        <v>93.76000000000001</v>
+        <v>95.37</v>
       </c>
       <c r="E46" t="n">
-        <v>96.05</v>
+        <v>102.48</v>
       </c>
       <c r="F46" t="n">
-        <v>3.02</v>
+        <v>6.43</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0325</v>
+        <v>0.0669</v>
       </c>
       <c r="H46" t="n">
-        <v>3.17</v>
+        <v>8.67</v>
       </c>
       <c r="I46" t="n">
-        <v>87.01000000000001</v>
+        <v>90.59</v>
       </c>
       <c r="J46" t="n">
-        <v>89.28</v>
+        <v>93.23</v>
       </c>
       <c r="K46" t="n">
-        <v>91.09999999999999</v>
+        <v>94.47</v>
       </c>
       <c r="L46" t="n">
-        <v>92.92</v>
+        <v>95.7</v>
       </c>
       <c r="M46" t="n">
-        <v>94.95999999999999</v>
+        <v>97.64</v>
       </c>
       <c r="N46" t="n">
-        <v>97</v>
+        <v>99.56999999999999</v>
       </c>
       <c r="O46" t="n">
-        <v>98.59</v>
+        <v>100.1</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4338,7 +4338,7 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -4350,11 +4350,13 @@
       </c>
       <c r="U46" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
@@ -4366,50 +4368,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>96.88</v>
+        <v>104.32</v>
       </c>
       <c r="C47" t="n">
-        <v>104.04</v>
+        <v>104.46</v>
       </c>
       <c r="D47" t="n">
-        <v>95.37</v>
+        <v>98.48</v>
       </c>
       <c r="E47" t="n">
-        <v>102.48</v>
+        <v>100.05</v>
       </c>
       <c r="F47" t="n">
-        <v>6.43</v>
+        <v>-2.43</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0669</v>
+        <v>-0.0237</v>
       </c>
       <c r="H47" t="n">
-        <v>8.67</v>
+        <v>5.98</v>
       </c>
       <c r="I47" t="n">
-        <v>90.59</v>
+        <v>86.7</v>
       </c>
       <c r="J47" t="n">
-        <v>93.23</v>
+        <v>95.2</v>
       </c>
       <c r="K47" t="n">
-        <v>94.47</v>
+        <v>98.15000000000001</v>
       </c>
       <c r="L47" t="n">
-        <v>95.7</v>
+        <v>101.09</v>
       </c>
       <c r="M47" t="n">
-        <v>97.64</v>
+        <v>106.82</v>
       </c>
       <c r="N47" t="n">
-        <v>99.56999999999999</v>
+        <v>112.54</v>
       </c>
       <c r="O47" t="n">
-        <v>100.1</v>
+        <v>112.71</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4422,78 +4424,76 @@
       </c>
       <c r="S47" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>104.32</v>
+        <v>102.25</v>
       </c>
       <c r="C48" t="n">
-        <v>104.46</v>
+        <v>104.95</v>
       </c>
       <c r="D48" t="n">
-        <v>98.48</v>
+        <v>100.53</v>
       </c>
       <c r="E48" t="n">
-        <v>100.05</v>
+        <v>101.39</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.43</v>
+        <v>1.34</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0237</v>
+        <v>0.0134</v>
       </c>
       <c r="H48" t="n">
-        <v>5.98</v>
+        <v>4.42</v>
       </c>
       <c r="I48" t="n">
-        <v>86.7</v>
+        <v>92.5</v>
       </c>
       <c r="J48" t="n">
-        <v>95.2</v>
+        <v>93.36</v>
       </c>
       <c r="K48" t="n">
-        <v>98.15000000000001</v>
+        <v>97.06</v>
       </c>
       <c r="L48" t="n">
-        <v>101.09</v>
+        <v>100.76</v>
       </c>
       <c r="M48" t="n">
-        <v>106.82</v>
+        <v>103.04</v>
       </c>
       <c r="N48" t="n">
-        <v>112.54</v>
+        <v>105.32</v>
       </c>
       <c r="O48" t="n">
-        <v>112.71</v>
+        <v>110.44</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4506,11 +4506,13 @@
       </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4523,59 +4525,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>102.25</v>
+        <v>102.01</v>
       </c>
       <c r="C49" t="n">
-        <v>104.95</v>
+        <v>106.75</v>
       </c>
       <c r="D49" t="n">
-        <v>100.53</v>
+        <v>101.21</v>
       </c>
       <c r="E49" t="n">
-        <v>101.39</v>
+        <v>105.83</v>
       </c>
       <c r="F49" t="n">
-        <v>1.34</v>
+        <v>4.44</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0134</v>
+        <v>0.0438</v>
       </c>
       <c r="H49" t="n">
-        <v>4.42</v>
+        <v>5.54</v>
       </c>
       <c r="I49" t="n">
-        <v>92.5</v>
+        <v>96.11</v>
       </c>
       <c r="J49" t="n">
-        <v>93.36</v>
+        <v>96.3</v>
       </c>
       <c r="K49" t="n">
-        <v>97.06</v>
+        <v>99.18000000000001</v>
       </c>
       <c r="L49" t="n">
-        <v>100.76</v>
+        <v>102.06</v>
       </c>
       <c r="M49" t="n">
-        <v>103.04</v>
+        <v>103.6</v>
       </c>
       <c r="N49" t="n">
-        <v>105.32</v>
+        <v>105.13</v>
       </c>
       <c r="O49" t="n">
-        <v>110.44</v>
+        <v>109.37</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4586,9 +4584,9 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T49" s="8" t="inlineStr">
@@ -4596,8 +4594,10 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4612,74 +4612,74 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>102.01</v>
+        <v>105.48</v>
       </c>
       <c r="C50" t="n">
-        <v>106.75</v>
+        <v>105.63</v>
       </c>
       <c r="D50" t="n">
-        <v>101.21</v>
+        <v>100.97</v>
       </c>
       <c r="E50" t="n">
-        <v>105.83</v>
+        <v>102.43</v>
       </c>
       <c r="F50" t="n">
-        <v>4.44</v>
+        <v>-3.4</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0438</v>
+        <v>-0.0321</v>
       </c>
       <c r="H50" t="n">
-        <v>5.54</v>
+        <v>4.66</v>
       </c>
       <c r="I50" t="n">
-        <v>96.11</v>
+        <v>95.67</v>
       </c>
       <c r="J50" t="n">
-        <v>96.3</v>
+        <v>101.22</v>
       </c>
       <c r="K50" t="n">
-        <v>99.18000000000001</v>
+        <v>103.06</v>
       </c>
       <c r="L50" t="n">
-        <v>102.06</v>
+        <v>104.91</v>
       </c>
       <c r="M50" t="n">
-        <v>103.6</v>
+        <v>108.6</v>
       </c>
       <c r="N50" t="n">
-        <v>105.13</v>
+        <v>112.3</v>
       </c>
       <c r="O50" t="n">
-        <v>109.37</v>
+        <v>112.29</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4689,72 +4689,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>105.48</v>
+        <v>102.18</v>
       </c>
       <c r="C51" t="n">
-        <v>105.63</v>
+        <v>102.47</v>
       </c>
       <c r="D51" t="n">
-        <v>100.97</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="E51" t="n">
-        <v>102.43</v>
+        <v>101.91</v>
       </c>
       <c r="F51" t="n">
-        <v>-3.4</v>
+        <v>-0.52</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0321</v>
+        <v>-0.0051</v>
       </c>
       <c r="H51" t="n">
-        <v>4.66</v>
+        <v>3.37</v>
       </c>
       <c r="I51" t="n">
-        <v>95.67</v>
+        <v>96.31</v>
       </c>
       <c r="J51" t="n">
-        <v>101.22</v>
+        <v>97.34</v>
       </c>
       <c r="K51" t="n">
-        <v>103.06</v>
+        <v>100.1</v>
       </c>
       <c r="L51" t="n">
-        <v>104.91</v>
+        <v>102.86</v>
       </c>
       <c r="M51" t="n">
-        <v>108.6</v>
+        <v>104.76</v>
       </c>
       <c r="N51" t="n">
-        <v>112.3</v>
+        <v>106.65</v>
       </c>
       <c r="O51" t="n">
-        <v>112.29</v>
+        <v>110.29</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4780,50 +4782,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>102.18</v>
+        <v>101.06</v>
       </c>
       <c r="C52" t="n">
-        <v>102.47</v>
+        <v>103.48</v>
       </c>
       <c r="D52" t="n">
+        <v>99.19</v>
+      </c>
+      <c r="E52" t="n">
+        <v>100.3</v>
+      </c>
+      <c r="F52" t="n">
+        <v>-1.61</v>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>-0.0158</v>
+      </c>
+      <c r="H52" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="I52" t="n">
+        <v>95.73</v>
+      </c>
+      <c r="J52" t="n">
         <v>99.09999999999999</v>
       </c>
-      <c r="E52" t="n">
-        <v>101.91</v>
-      </c>
-      <c r="F52" t="n">
-        <v>-0.52</v>
-      </c>
-      <c r="G52" s="5" t="n">
-        <v>-0.0051</v>
-      </c>
-      <c r="H52" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="I52" t="n">
-        <v>96.31</v>
-      </c>
-      <c r="J52" t="n">
-        <v>97.34</v>
-      </c>
       <c r="K52" t="n">
-        <v>100.1</v>
+        <v>100.23</v>
       </c>
       <c r="L52" t="n">
-        <v>102.86</v>
+        <v>101.35</v>
       </c>
       <c r="M52" t="n">
-        <v>104.76</v>
+        <v>103.6</v>
       </c>
       <c r="N52" t="n">
-        <v>106.65</v>
+        <v>105.84</v>
       </c>
       <c r="O52" t="n">
-        <v>110.29</v>
+        <v>105.84</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4833,12 +4835,12 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4857,70 +4859,74 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>101.06</v>
+        <v>101</v>
       </c>
       <c r="C53" t="n">
-        <v>103.48</v>
+        <v>101.08</v>
       </c>
       <c r="D53" t="n">
-        <v>99.19</v>
+        <v>94.22</v>
       </c>
       <c r="E53" t="n">
-        <v>100.3</v>
+        <v>95.78</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.61</v>
+        <v>-4.52</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0158</v>
+        <v>-0.0451</v>
       </c>
       <c r="H53" t="n">
-        <v>4.29</v>
+        <v>6.86</v>
       </c>
       